--- a/tame_output/ON/bt/strategyON_20241003.xlsx
+++ b/tame_output/ON/bt/strategyON_20241003.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>38.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.4%</t>
+          <t>419.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-627.3%</t>
+          <t>-627.9%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2104"/>
+  <dimension ref="A1:G2105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49955,6 +49955,29 @@
         <v>5.679792613099274</v>
       </c>
     </row>
+    <row r="2105">
+      <c r="A2105" s="2" t="n">
+        <v>45567</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>3.664839169263689</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>4.922845401496135</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>-4.663073820431435</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>3.059672761084521</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>1.26157868600523</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>5.679792613099274</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tame_output/ON/bt/strategyON_20241003.xlsx
+++ b/tame_output/ON/bt/strategyON_20241003.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.5%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-627.9%</t>
+          <t>-615.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-65.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.8%</t>
+          <t>-202.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-97.8%</t>
+          <t>-85.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>125.7%</t>
+          <t>128.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>117.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>122.0%</t>
+          <t>129.5%</t>
         </is>
       </c>
     </row>
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612275</v>
+        <v>3.346417924612274</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569613</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932765</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917047</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777667</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161971</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321628</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749882691378386</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.71581989500697</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787383</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585932</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.65633273360975</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251941</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916195</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830323</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332687</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108852</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121461</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382914</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013422</v>
+        <v>3.64525678001342</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498964</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800094</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660846</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395083</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791145</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620431</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285644</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399465</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256367</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600700996</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687008</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790798</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437326</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298392</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960217994</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.73608941335353</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113273</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113682</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016436</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.794705093307666</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863547</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394108</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456726</v>
+        <v>3.715607446456724</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883673</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236292</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942768</v>
+        <v>3.705201079427678</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610377</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
@@ -49270,7 +49270,7 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.71554441166745</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889187</v>
+        <v>3.673978374889185</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409561</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452567</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762281</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884075</v>
+        <v>3.800870306884073</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129646</v>
+        <v>3.671015692129644</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052349</v>
+        <v>3.904173816052348</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813493</v>
+        <v>3.740179607813491</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537942</v>
+        <v>3.76505079653794</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771814</v>
+        <v>3.758409170771812</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.80134059710972</v>
+        <v>3.801340597109718</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843994</v>
+        <v>3.798465546843993</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351855</v>
+        <v>3.772186508351854</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
@@ -49592,7 +49592,7 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551265</v>
+        <v>3.763392838551264</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
@@ -49615,7 +49615,7 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041106</v>
+        <v>3.805590565041104</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
@@ -49638,7 +49638,7 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497396</v>
+        <v>3.832164354497394</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
@@ -49661,7 +49661,7 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492286</v>
+        <v>3.858310890492285</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
@@ -49684,7 +49684,7 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436468</v>
+        <v>3.844935596436466</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
@@ -49707,7 +49707,7 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039477</v>
+        <v>3.848376866039475</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
@@ -49730,7 +49730,7 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524471</v>
+        <v>3.868153115524469</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
@@ -49753,7 +49753,7 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867945</v>
+        <v>3.849040239867943</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
@@ -49776,7 +49776,7 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232969</v>
+        <v>3.870204928232967</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179672</v>
+        <v>3.855534437179671</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.234446221019734</v>
+        <v>-5.107969439333625</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.848967000555854</v>
+        <v>2.899557713230298</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9241159303277278</v>
+        <v>1.050592712013837</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.497571471474132</v>
+        <v>5.573457540485798</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967719</v>
+        <v>3.884687848967717</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.186438097176041</v>
+        <v>-5.059961315489932</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.831079666883684</v>
+        <v>2.881670379558127</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9241159303277278</v>
+        <v>1.050592712013837</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.460480888264485</v>
+        <v>5.53636695727615</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018607</v>
+        <v>3.895362357018605</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.107612439992451</v>
+        <v>-4.981135658306342</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.86654218331507</v>
+        <v>2.917132895989514</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.002941587511318</v>
+        <v>1.129418369197427</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.511708536132589</v>
+        <v>5.587594605144255</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.89161098107513</v>
+        <v>3.891610981075128</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.915677638738577</v>
+        <v>-4.789200857052468</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.938215196423656</v>
+        <v>2.9888059090981</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.002941587511318</v>
+        <v>1.129418369197427</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.506607628739626</v>
+        <v>5.582493697751292</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435436</v>
+        <v>3.872432493435435</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.79750426072065</v>
+        <v>-4.671027479034541</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.980838457019923</v>
+        <v>3.031429169694366</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.121114965529245</v>
+        <v>1.247591747215354</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.572865564939478</v>
+        <v>5.648751633951144</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917725</v>
+        <v>3.859571723917723</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.684089577937919</v>
+        <v>-4.557612796251809</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.055292922996042</v>
+        <v>3.105883635670486</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.234529648311977</v>
+        <v>1.361006429998086</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.670002967472143</v>
+        <v>5.74588903648381</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013631</v>
+        <v>3.828006274013629</v>
       </c>
       <c r="C2104" t="n">
         <v>4.922845401496135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.657040540244665</v>
+        <v>-4.530563758558555</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.059672761084521</v>
+        <v>3.110263473758964</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.26157868600523</v>
+        <v>1.388055467691339</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.679792613099274</v>
+        <v>5.755678682110939</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.664839169263689</v>
+        <v>3.889408746563149</v>
       </c>
       <c r="C2105" t="n">
         <v>4.922845401496135</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.663073820431435</v>
+        <v>-4.536597038745326</v>
       </c>
       <c r="E2105" t="n">
-        <v>3.059672761084521</v>
+        <v>3.110263473758964</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.26157868600523</v>
+        <v>1.388055467691339</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.679792613099274</v>
+        <v>5.755678682110939</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241003.xlsx
+++ b/tame_output/ON/bt/strategyON_20241003.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>114.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>180.7%</t>
+          <t>182.0%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>418.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.2%</t>
+          <t>-641.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-65.2%</t>
+          <t>-77.8%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-202.7%</t>
+          <t>-203.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-85.2%</t>
+          <t>-111.7%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128.6%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>117.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>129.5%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2105"/>
+  <dimension ref="A1:G2106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612274</v>
+        <v>3.346417924612275</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498964</v>
+        <v>3.666747201498965</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660846</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -49385,16 +49385,16 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884073</v>
+        <v>3.634813277125764</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.729487500426267</v>
+        <v>-5.734252564059027</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.042609036828746</v>
+        <v>2.040703011375643</v>
       </c>
       <c r="F2080" t="n">
         <v>0.5373852256453805</v>
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129644</v>
+        <v>3.647901163120256</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.334760461313001</v>
+        <v>4.351781874534649</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.728539077308229</v>
+        <v>-5.860536118116717</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.042988406075962</v>
+        <v>2.007211002974214</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4111016715876899</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.65719159670023</v>
+        <v>4.598442877487264</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052348</v>
+        <v>3.881059287042959</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.347488069294093</v>
+        <v>4.364509482515741</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.828808895267249</v>
+        <v>-5.960805936075738</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.015608086873446</v>
+        <v>1.979830683771698</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4111016715876899</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.669919204681322</v>
+        <v>4.611170485468355</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813491</v>
+        <v>3.717065078804103</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.349434067718481</v>
+        <v>4.366455480940129</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.822816648478438</v>
+        <v>-5.954813689286927</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.019950984013358</v>
+        <v>1.98417358091161</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4111016715876899</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.67186520310571</v>
+        <v>4.613116483892743</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.76505079653794</v>
+        <v>3.741936267528551</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.34308820373625</v>
+        <v>4.360109616957898</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.73425868734767</v>
+        <v>-5.866255728156159</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.049028304483434</v>
+        <v>2.013250901381686</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4111016715876899</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.665519339123478</v>
+        <v>4.606770619910511</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771812</v>
+        <v>3.735294641762423</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.342396881175246</v>
+        <v>4.359418294396893</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.716499609844596</v>
+        <v>-5.848496650653085</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.055440612923659</v>
+        <v>2.019663209821911</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4111016715876899</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.664828016562474</v>
+        <v>4.606079297349508</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109718</v>
+        <v>3.778226068100329</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.355179067083832</v>
+        <v>4.37220048030548</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.616869458795528</v>
+        <v>-5.748866499604017</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.108074859251873</v>
+        <v>2.072297456150125</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.5107318226367574</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.737388293100501</v>
+        <v>4.678639573887535</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843993</v>
+        <v>3.775351017834604</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.544333332582559</v>
+        <v>4.561354745804207</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.666268967484539</v>
+        <v>-5.798266008293028</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.277469321274995</v>
+        <v>2.241691918173247</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.5209906560685021</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.932697858658274</v>
+        <v>4.873949139445308</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351854</v>
+        <v>3.749071979342465</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.531522005685421</v>
+        <v>4.548543418907069</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.459584493842163</v>
+        <v>-5.591581534650652</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.347331783834808</v>
+        <v>2.31155438073306</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.7276751297108778</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.043897215946562</v>
+        <v>4.985148496733595</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551264</v>
+        <v>3.740278309541875</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.533523519339526</v>
+        <v>4.550544932561174</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.493741388839689</v>
+        <v>-5.625738429648178</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.335670539489902</v>
+        <v>2.299893136388154</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.6440913601700653</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.995748467876179</v>
+        <v>4.936999748663213</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041104</v>
+        <v>3.782476036031715</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.887020633329193</v>
+        <v>4.904042046550841</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.401151909778233</v>
+        <v>-5.533148950586722</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.726203445104152</v>
+        <v>2.690426042002404</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.6440913601700653</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.349245581865847</v>
+        <v>5.290496862652881</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497394</v>
+        <v>3.809049825488005</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.891583744896296</v>
+        <v>4.908605158117945</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.474312513551378</v>
+        <v>-5.606309554359867</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.701502315161997</v>
+        <v>2.66572491206025</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.6160701601358223</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.336995973412405</v>
+        <v>5.278247254199439</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492285</v>
+        <v>3.835196361482896</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.941413686219824</v>
+        <v>4.958435099441473</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.422096203755036</v>
+        <v>-5.554093244563525</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.772218780404061</v>
+        <v>2.736441377302314</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.6160701601358223</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.386825914735931</v>
+        <v>5.328077195522966</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436466</v>
+        <v>3.821821067427077</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.950227656429835</v>
+        <v>4.967249069651483</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.39019868666979</v>
+        <v>-5.522195727478279</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.793791757448171</v>
+        <v>2.758014354346424</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.6479676772210681</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.41477839519709</v>
+        <v>5.356029675984125</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039475</v>
+        <v>3.825262337030086</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.945865240469032</v>
+        <v>4.96288665369068</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.404954010869931</v>
+        <v>-5.53695105167842</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.783527211807312</v>
+        <v>2.747749808705565</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.6479676772210681</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.410415979236287</v>
+        <v>5.351667260023321</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524469</v>
+        <v>3.845038586515081</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.936789743885312</v>
+        <v>4.95381115710696</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.355489387500019</v>
+        <v>-5.487486428308508</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.794237564571556</v>
+        <v>2.758460161469809</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8237158546486703</v>
+        <v>0.6974323005909797</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.431019256674514</v>
+        <v>5.372270537461548</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867943</v>
+        <v>3.825925710858554</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.933197411600246</v>
+        <v>4.950218824821895</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.192381395346404</v>
+        <v>-5.324378436154893</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.855888429147937</v>
+        <v>2.820111026046189</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.860540292744595</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.525291719681618</v>
+        <v>5.466543000468652</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232967</v>
+        <v>3.847090399223578</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.942244448291374</v>
+        <v>4.959265861513023</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.171738304545176</v>
+        <v>-5.303735345353665</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.873192702159556</v>
+        <v>2.837415299057809</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.860540292744595</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.534338756372746</v>
+        <v>5.475590037159781</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179671</v>
+        <v>3.832419908170282</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.943101913277496</v>
+        <v>4.960123326499144</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.107969439333625</v>
+        <v>-5.366443261828223</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.899557713230298</v>
+        <v>2.813189597454107</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.050592712013837</v>
+        <v>0.7978323762700372</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.573457540485798</v>
+        <v>5.438822752261167</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967717</v>
+        <v>3.861573319958328</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.906011330067848</v>
+        <v>4.923032743289497</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.059961315489932</v>
+        <v>-5.31843513798453</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.881670379558127</v>
+        <v>2.795302263781937</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.050592712013837</v>
+        <v>0.7978323762700372</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.53636695727615</v>
+        <v>5.401732169051519</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018605</v>
+        <v>3.872247828009217</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.909943583625799</v>
+        <v>4.926964996847447</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.981135658306342</v>
+        <v>-5.23960948080094</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.917132895989514</v>
+        <v>2.830764780213323</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.129418369197427</v>
+        <v>0.8766580334536277</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.587594605144255</v>
+        <v>5.452959816919624</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075128</v>
+        <v>3.868496452065739</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.904842676232835</v>
+        <v>4.921864089454484</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.789200857052468</v>
+        <v>-5.047674679547066</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.9888059090981</v>
+        <v>2.902437793321909</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.129418369197427</v>
+        <v>0.8766580334536277</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.582493697751292</v>
+        <v>5.447858909526661</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435435</v>
+        <v>3.849317964426046</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.900196585621931</v>
+        <v>4.917217998843579</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.671027479034541</v>
+        <v>-4.92950130152914</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.031429169694366</v>
+        <v>2.945061053918176</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.247591747215354</v>
+        <v>0.9948314114715551</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.648751633951144</v>
+        <v>5.514116845726512</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917723</v>
+        <v>3.836457194908334</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.929285178484958</v>
+        <v>4.946306591706606</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.557612796251809</v>
+        <v>-4.816086618746408</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.105883635670486</v>
+        <v>3.019515519894295</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.361006429998086</v>
+        <v>1.108246094254286</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.74588903648381</v>
+        <v>5.611254248259178</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013629</v>
+        <v>3.805495133363348</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.922845401496135</v>
+        <v>4.939866814717783</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.530563758558555</v>
+        <v>-4.789037581053154</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.110263473758964</v>
+        <v>3.023895357982774</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.388055467691339</v>
+        <v>1.13529513194754</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.755678682110939</v>
+        <v>5.621043893886307</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,45 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.889408746563149</v>
+        <v>3.797617459253714</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.922845401496135</v>
+        <v>4.905355132088824</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.536597038745326</v>
+        <v>-4.801285439472421</v>
       </c>
       <c r="E2105" t="n">
-        <v>3.110263473758964</v>
+        <v>2.984484531986108</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.388055467691339</v>
+        <v>1.123047273528273</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.755678682110939</v>
+        <v>5.579183496205789</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="2" t="n">
+        <v>45568</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>3.640569789667616</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>4.93580700368736</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>-4.801285439472421</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>2.984484531986108</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>1.123047273528273</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>4.928870800673728</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241003.xlsx
+++ b/tame_output/ON/bt/strategyON_20241003.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>114.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>182.0%</t>
+          <t>184.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>418.9%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-641.7%</t>
+          <t>-616.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-81.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-203.0%</t>
+          <t>-203.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-111.7%</t>
+          <t>-85.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>49.5%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -46286,10 +46286,10 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.887575986669719</v>
+        <v>-3.818222177837304</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.0359982464938</v>
+        <v>1.063739770026767</v>
       </c>
       <c r="F1945" t="n">
         <v>0.3998306289428718</v>
@@ -46309,10 +46309,10 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.79476550521886</v>
+        <v>-3.725411696386444</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.00239513096551</v>
+        <v>1.030136654498476</v>
       </c>
       <c r="F1946" t="n">
         <v>0.4926411103937312</v>
@@ -46332,10 +46332,10 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.839154974548287</v>
+        <v>-3.769801165715872</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9865128191583397</v>
+        <v>1.014254342691306</v>
       </c>
       <c r="F1947" t="n">
         <v>0.4482516410643035</v>
@@ -46355,10 +46355,10 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.81865128066279</v>
+        <v>-3.749297471830375</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9897900052242616</v>
+        <v>1.017531528757228</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4687553349498008</v>
@@ -46378,10 +46378,10 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.902323377375122</v>
+        <v>-3.832969568542707</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.961812462369996</v>
+        <v>0.9895539859029621</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4687553349498008</v>
@@ -46401,10 +46401,10 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.930103775276475</v>
+        <v>-3.86074996644406</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9621975049779938</v>
+        <v>0.9899390285109599</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4409749370484478</v>
@@ -46424,10 +46424,10 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.048484448006613</v>
+        <v>-3.979130639174198</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7532009558865917</v>
+        <v>0.7809424794195579</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3737570848974716</v>
@@ -46447,10 +46447,10 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.157098526449944</v>
+        <v>-4.087744717617529</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.829904985228465</v>
+        <v>0.8576465087614311</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3737570848974716</v>
@@ -46470,10 +46470,10 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.121689488201802</v>
+        <v>-4.052335679369386</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.858581626630045</v>
+        <v>0.8863231501630113</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3737570848974716</v>
@@ -46493,10 +46493,10 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.130150656857262</v>
+        <v>-4.060796848024847</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8526166005102294</v>
+        <v>0.8803581240431957</v>
       </c>
       <c r="F1954" t="n">
         <v>0.3652959162420105</v>
@@ -46516,10 +46516,10 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.953034326822096</v>
+        <v>-3.883680517989681</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9201921613695982</v>
+        <v>0.9479336849025646</v>
       </c>
       <c r="F1955" t="n">
         <v>0.3652959162420105</v>
@@ -46539,10 +46539,10 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.998126571655642</v>
+        <v>-3.928772762823226</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9028386551980931</v>
+        <v>0.9305801787310592</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3033998730726207</v>
@@ -46562,10 +46562,10 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.818751150416874</v>
+        <v>-3.749397341584459</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9683757990000146</v>
+        <v>0.9961173225329807</v>
       </c>
       <c r="F1957" t="n">
         <v>0.4601766312433394</v>
@@ -46585,10 +46585,10 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.86376536393748</v>
+        <v>-3.794411555105065</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9311775689233617</v>
+        <v>0.958919092456328</v>
       </c>
       <c r="F1958" t="n">
         <v>0.4298277359287348</v>
@@ -46608,10 +46608,10 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.951776550496178</v>
+        <v>-3.882422741663762</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9016646566388287</v>
+        <v>0.929406180171795</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3643512280695618</v>
@@ -46631,10 +46631,10 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.052974331933351</v>
+        <v>-3.983620523100935</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8603894659604607</v>
+        <v>0.8881309894934273</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2959424145242426</v>
@@ -46654,10 +46654,10 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.046463365319038</v>
+        <v>-3.977109556486622</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8605938141605025</v>
+        <v>0.8883353376934691</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2959424145242426</v>
@@ -46677,10 +46677,10 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.027425237611741</v>
+        <v>-3.958071428779325</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8647337844516665</v>
+        <v>0.8924753079846328</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2377588031930481</v>
@@ -46700,10 +46700,10 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.079941039886561</v>
+        <v>-4.010587231054145</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9630218651759286</v>
+        <v>0.9907633887088951</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2377588031930481</v>
@@ -46723,10 +46723,10 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.083349351321141</v>
+        <v>-4.013995542488725</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9624918695882303</v>
+        <v>0.9902333931211968</v>
       </c>
       <c r="F1964" t="n">
         <v>0.2702753722024255</v>
@@ -46746,10 +46746,10 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.063993215427294</v>
+        <v>-3.994639406594878</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9762428543426951</v>
+        <v>1.003984377875662</v>
       </c>
       <c r="F1965" t="n">
         <v>0.2702753722024255</v>
@@ -46769,10 +46769,10 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.137322744165386</v>
+        <v>-4.067968935332971</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8448612641246576</v>
+        <v>0.8726027876576239</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2706700346220474</v>
@@ -46792,10 +46792,10 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.221143965440085</v>
+        <v>-4.151790156607669</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8141263971462591</v>
+        <v>0.8418679206792254</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2706700346220474</v>
@@ -46815,10 +46815,10 @@
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.2149912593873</v>
+        <v>-4.145637450554885</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8172498279590312</v>
+        <v>0.8449913514919976</v>
       </c>
       <c r="F1968" t="n">
         <v>0.2768227406748317</v>
@@ -46838,10 +46838,10 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.231800557537802</v>
+        <v>-4.162446748705387</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8096065854389407</v>
+        <v>0.837348108971907</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2600134425243301</v>
@@ -46861,10 +46861,10 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.16950255876168</v>
+        <v>-4.100148749929264</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9008613387462105</v>
+        <v>0.9286028622791769</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3053077067987721</v>
@@ -46884,10 +46884,10 @@
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.967712361096522</v>
+        <v>-3.898358552264106</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7838694195264009</v>
+        <v>0.811610943059367</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5033258989679266</v>
@@ -46907,10 +46907,10 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.018599073782717</v>
+        <v>-3.949245264950301</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8338049667740981</v>
+        <v>0.8615464903070644</v>
       </c>
       <c r="F1972" t="n">
         <v>0.452439186281732</v>
@@ -46930,10 +46930,10 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.93198833113291</v>
+        <v>-3.862634522300494</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8830769999500647</v>
+        <v>0.9108185234830311</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5310649174868902</v>
@@ -46953,10 +46953,10 @@
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.992197629138194</v>
+        <v>-3.922843820305778</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8575292615726227</v>
+        <v>0.8852707851055888</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4708556194816057</v>
@@ -46976,10 +46976,10 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.943010980453843</v>
+        <v>-3.873657171621427</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8756955390862917</v>
+        <v>0.903437062619258</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
@@ -46999,10 +46999,10 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.898637848815274</v>
+        <v>-3.829284039982858</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8933076591771554</v>
+        <v>0.9210491827101217</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
@@ -47022,10 +47022,10 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.863906527496773</v>
+        <v>-3.794552718664357</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9015939818431462</v>
+        <v>0.9293355053761125</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.816250796935718</v>
+        <v>-3.746896988103302</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.927038031095373</v>
+        <v>0.9547795546283393</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569613</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.715732638436963</v>
+        <v>-3.646378829604547</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9721376678695997</v>
+        <v>0.999879191402566</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.69982730900461</v>
+        <v>-3.630473500172195</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9652544721184131</v>
+        <v>0.9929959956513792</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932765</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.654988907396212</v>
+        <v>-3.585635098563797</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9872875353724009</v>
+        <v>1.015029058905367</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917047</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.67448736363822</v>
+        <v>-3.605133554805805</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9836490925066754</v>
+        <v>1.011390616039642</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.63028452655232</v>
+        <v>-3.560930717719904</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.007209829868873</v>
+        <v>1.034951353401839</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.637844192389367</v>
+        <v>-3.568490383556951</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.002595964003302</v>
+        <v>1.030337487536268</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.479552774850095</v>
+        <v>-3.410198966017679</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.11716029620205</v>
+        <v>1.144901819735016</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.271910771215619</v>
+        <v>-3.202556962383203</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.198657802250094</v>
+        <v>1.22639932578306</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.220878678493091</v>
+        <v>-3.151524869660675</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.214018867577375</v>
+        <v>1.241760391110341</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.155654497365885</v>
+        <v>-3.086300688533469</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.257295944120962</v>
+        <v>1.285037467653928</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
@@ -47298,10 +47298,10 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.118227477294751</v>
+        <v>-3.048873668462335</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.268227724448696</v>
+        <v>1.295969247981662</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.116869492321205</v>
+        <v>-3.04751568348879</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.270027710769355</v>
+        <v>1.297769234302321</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.088456229221322</v>
+        <v>-3.019102420388906</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.441950787030519</v>
+        <v>1.469692310563485</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.013673968196309</v>
+        <v>-2.944320159363893</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.591976600658341</v>
+        <v>1.619718124191307</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
@@ -47390,10 +47390,10 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.987589883932501</v>
+        <v>-2.918236075100086</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.594118210377723</v>
+        <v>1.621859733910689</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.899711970823381</v>
+        <v>-2.830358161990965</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.627462571205151</v>
+        <v>1.655204094738117</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.890819509430098</v>
+        <v>-2.821465700597682</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.648573961489256</v>
+        <v>1.676315485022222</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.059295626399976</v>
+        <v>-2.98994181756756</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.573038562105888</v>
+        <v>1.600780085638855</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.613039433770536</v>
+        <v>-2.54368562493812</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.732810736345526</v>
+        <v>1.760552259878492</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.590318330087383</v>
+        <v>-2.520964521254967</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.732563200315692</v>
+        <v>1.760304723848658</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777667</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.719520143381426</v>
+        <v>-2.65016633454901</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.839788600849244</v>
+        <v>1.86753012438221</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.745394541855451</v>
+        <v>-2.676040733023036</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.86651666395328</v>
+        <v>1.894258187486246</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.738339851640278</v>
+        <v>-2.668986042807862</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.866013896028895</v>
+        <v>1.893755419561861</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9750732742312349</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.71138862731379</v>
+        <v>-2.642034818481374</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.886800539404231</v>
+        <v>1.914542062937198</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9899536202589541</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.732932855144577</v>
+        <v>-2.663579046312161</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.062285980416876</v>
+        <v>2.090027503949843</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9899536202589541</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.755340972949449</v>
+        <v>-2.685987164117033</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.045439428197921</v>
+        <v>2.073180951730887</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9899536202589541</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.783565208527049</v>
+        <v>-2.714211399694634</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.036203733516518</v>
+        <v>2.063945257049484</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007930372710263</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.793006134415579</v>
+        <v>-2.723652325583164</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.088681080882953</v>
+        <v>2.116422604415919</v>
       </c>
       <c r="F2006" t="n">
         <v>1.130357490253654</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.999245072204013</v>
+        <v>-2.929891263371597</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.009076600312881</v>
+        <v>2.036818123845847</v>
       </c>
       <c r="F2007" t="n">
         <v>0.9241185524652205</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.075575049804919</v>
+        <v>-3.006221240972503</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.976656422166293</v>
+        <v>2.004397945699259</v>
       </c>
       <c r="F2008" t="n">
         <v>0.9241185524652205</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.230531835205048</v>
+        <v>-3.161178026372632</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.909493937609104</v>
+        <v>1.93723546114207</v>
       </c>
       <c r="F2009" t="n">
         <v>0.7691617670650912</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.392100260732303</v>
+        <v>-3.322746451899887</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.843300577608354</v>
+        <v>1.871042101141321</v>
       </c>
       <c r="F2010" t="n">
         <v>0.6423788432672118</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.500400922602422</v>
+        <v>-3.431047113770007</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.813053719726225</v>
+        <v>1.840795243259191</v>
       </c>
       <c r="F2011" t="n">
         <v>0.6423788432672118</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378386</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.659951995365939</v>
+        <v>-3.590598186533524</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.741238487403758</v>
+        <v>1.768980010936724</v>
       </c>
       <c r="F2012" t="n">
         <v>0.4901011764054604</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.71581989500697</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.687852782475412</v>
+        <v>-3.618498973642997</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.728602213686971</v>
+        <v>1.756343737219937</v>
       </c>
       <c r="F2013" t="n">
         <v>0.4555042522625256</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787383</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.810378885178306</v>
+        <v>-3.741025076345891</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.676356216583012</v>
+        <v>1.704097740115978</v>
       </c>
       <c r="F2014" t="n">
         <v>0.3329781495596317</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585932</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.040893381363895</v>
+        <v>-3.971539572531479</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.650856377699281</v>
+        <v>1.678597901232247</v>
       </c>
       <c r="F2015" t="n">
         <v>0.102463653374043</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.389638466588338</v>
+        <v>-4.320284657755923</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.65167006261135</v>
+        <v>1.679411586144316</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.006284300544854848</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237091</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.543624884364479</v>
+        <v>-4.474271075532063</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.659055764646534</v>
+        <v>1.6867972881795</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.006284300544854848</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.748224319227488</v>
+        <v>-4.678870510395072</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.563267192821451</v>
+        <v>1.591008716354418</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.006284300544854848</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65633273360975</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.000699473235212</v>
+        <v>-4.931345664402796</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.474147620273775</v>
+        <v>1.501889143806742</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.006284300544854848</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973153</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.293595229714624</v>
+        <v>-5.224241420882208</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.358199852200954</v>
+        <v>1.385941375733921</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.006284300544854848</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251941</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.480259357849432</v>
+        <v>-5.410905549017016</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.287655943174352</v>
+        <v>1.315397466707319</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.03302327136941474</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916195</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.626280044763394</v>
+        <v>-5.556926235930979</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.224325521144957</v>
+        <v>1.252067044677923</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.04210636316327171</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830323</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.71799405387298</v>
+        <v>-5.648640245040564</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.349843974200167</v>
+        <v>1.377585497733133</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.04210636316327171</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.749645712932949</v>
+        <v>-5.680291904100534</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.332029948539993</v>
+        <v>1.35977147207296</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.04727482040771191</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.818711767505886</v>
+        <v>-5.74935795867347</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.31463294427931</v>
+        <v>1.342374467812276</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.1096456979013219</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332687</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.920687889754293</v>
+        <v>-5.851334080921878</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.282768133835849</v>
+        <v>1.310509657368816</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.2116218201497295</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.810681606277072</v>
+        <v>-5.741327797444656</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.318923534470913</v>
+        <v>1.34666505800388</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.1884172482324543</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.823211311388951</v>
+        <v>-5.753857502556535</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.318161663148136</v>
+        <v>1.345903186681102</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.2022437476989773</v>
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.500797177916668</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.521764585917113</v>
+        <v>-5.452410777084697</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.446001236219407</v>
+        <v>1.31947644276904</v>
       </c>
       <c r="F2029" t="n">
         <v>0.09920297777285991</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.714585281563716</v>
+        <v>3.560318964580384</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.501768355669378</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.546354830152297</v>
+        <v>-5.477001021319881</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.437136316278044</v>
+        <v>1.310611522827678</v>
       </c>
       <c r="F2030" t="n">
         <v>0.09920297777285991</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.715556459316427</v>
+        <v>3.561290142333094</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.502611260049134</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.495316454145777</v>
+        <v>-5.425962645313361</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.458394571060408</v>
+        <v>1.331869777610041</v>
       </c>
       <c r="F2031" t="n">
         <v>0.09920297777285991</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.716399363696183</v>
+        <v>3.56213304671285</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.521649358923279</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.466467777322316</v>
+        <v>-5.397113968489901</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.488972140663937</v>
+        <v>1.362447347213571</v>
       </c>
       <c r="F2032" t="n">
         <v>0.1280516545963202</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.752746668664404</v>
+        <v>3.598480351681071</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700474</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.337833355047214</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.369832865303676</v>
+        <v>-5.300479056471261</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.343810101595328</v>
+        <v>1.217285308144961</v>
       </c>
       <c r="F2033" t="n">
         <v>0.2246865666149601</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.626911611999523</v>
+        <v>3.47264529501619</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.341335399121178</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.300794854355209</v>
+        <v>-5.231441045522793</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.374927350048679</v>
+        <v>1.248402556598313</v>
       </c>
       <c r="F2034" t="n">
         <v>0.2937245775634282</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.671836462642568</v>
+        <v>3.517570145659235</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833454</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.32576221819726</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.28200775398627</v>
+        <v>-5.212653945153854</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.366869009272337</v>
+        <v>1.240344215821971</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3125116779323667</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.667535541940013</v>
+        <v>3.513269224956681</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077624</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.32494992863369</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.204909152444397</v>
+        <v>-5.135555343611982</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.396896160325516</v>
+        <v>1.270371366875149</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3125116779323667</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.666723252376443</v>
+        <v>3.51245693539311</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147906</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.334818707758763</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.215294347334287</v>
+        <v>-5.145940538501871</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.402610861494633</v>
+        <v>1.276086068044266</v>
       </c>
       <c r="F2037" t="n">
         <v>0.3021264830424774</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.670360914567582</v>
+        <v>3.516094597584249</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.405655713535188</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.233882506056512</v>
+        <v>-5.164528697224096</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.466012603782168</v>
+        <v>1.339487810331801</v>
       </c>
       <c r="F2038" t="n">
         <v>0.283538324320252</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.730045025110672</v>
+        <v>3.575778708127339</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.402524724353486</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.234181052752548</v>
+        <v>-5.164827243920132</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.462762195922052</v>
+        <v>1.336237402471685</v>
       </c>
       <c r="F2039" t="n">
         <v>0.2832397776242161</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.726734907911349</v>
+        <v>3.572468590928016</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108852</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.407055619292878</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.13335791906212</v>
+        <v>-5.064004110229704</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.507622344337614</v>
+        <v>1.381097550887248</v>
       </c>
       <c r="F2040" t="n">
         <v>0.2957039931085699</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.738744332141353</v>
+        <v>3.58447801515802</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121461</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.407184872771421</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.942576558309712</v>
+        <v>-4.873222749477296</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.584064142117121</v>
+        <v>1.457539348666754</v>
       </c>
       <c r="F2041" t="n">
         <v>0.4864853538609773</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.85334240207134</v>
+        <v>3.699076085088008</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.387021718509017</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.835613200460291</v>
+        <v>-4.766259391627875</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.606686330994486</v>
+        <v>1.480161537544119</v>
       </c>
       <c r="F2042" t="n">
         <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.868258012584818</v>
+        <v>3.713991695601485</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912979</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.421988655121076</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.780282612558528</v>
+        <v>-4.710928803726112</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.663785502767249</v>
+        <v>1.537260709316883</v>
       </c>
       <c r="F2043" t="n">
         <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.936423301937934</v>
+        <v>3.782156984954601</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539888</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.415675223022514</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.768228485645565</v>
+        <v>-4.69887467681315</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.662293721433872</v>
+        <v>1.535768927983506</v>
       </c>
       <c r="F2044" t="n">
         <v>0.6123346766355037</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.937342345987148</v>
+        <v>3.783076029003816</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811003</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.417555853206649</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.845583975773534</v>
+        <v>-4.776230166941119</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.63323215556682</v>
+        <v>1.506707362116454</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5349791865075343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.892809682094503</v>
+        <v>3.73854336511117</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382914</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.430406879084532</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.777535413082004</v>
+        <v>-4.708181604249589</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.673302606521315</v>
+        <v>1.546777813070948</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6030277491990641</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.946489845587303</v>
+        <v>3.792223528603971</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64525678001342</v>
+        <v>3.645256780013422</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.450609549258126</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.009135806251505</v>
+        <v>-4.93978199741909</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.600865119427109</v>
+        <v>1.474340325976742</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6030277491990641</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.966692515760897</v>
+        <v>3.812426198777565</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498965</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.434215785325008</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.059187351780725</v>
+        <v>-4.989833542948309</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.564450737282303</v>
+        <v>1.437925943831937</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6030277491990641</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.95029875182778</v>
+        <v>3.796032434844447</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800094</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.394467698918475</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.23429418435717</v>
+        <v>-5.164940375524754</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.454659917845192</v>
+        <v>1.328135124394825</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6030277491990641</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.910550665421246</v>
+        <v>3.756284348437914</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.401490317915415</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.038194030926647</v>
+        <v>-4.968840222094231</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.540122598214341</v>
+        <v>1.413597804763974</v>
       </c>
       <c r="F2050" t="n">
         <v>0.799127902629587</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.0352333764765</v>
+        <v>3.880967059493167</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395083</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.500661317488319</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.885168638813362</v>
+        <v>-4.815814829980947</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.700503754632559</v>
+        <v>1.573978961182193</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9521532947428711</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.226219611317375</v>
+        <v>4.071953294334042</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791145</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>3.688127542396612</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.913475952686633</v>
+        <v>-4.844122143854217</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.876647053991543</v>
+        <v>1.750122260541177</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9521532947428711</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.413685836225667</v>
+        <v>4.259419519242335</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620431</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>3.657530493750695</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.080069177800155</v>
+        <v>-5.010715368967739</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.779412715300217</v>
+        <v>1.652887921849851</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7855600696293488</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.283132852511637</v>
+        <v>4.128866535528304</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285644</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>3.661206896412412</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.057033384438589</v>
+        <v>-4.987679575606173</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.792303435306561</v>
+        <v>1.665778641856195</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7855600696293488</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.286809255173354</v>
+        <v>4.132542938190022</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399465</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>3.658824951535907</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.027787403982892</v>
+        <v>-4.958433595150477</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.801619882612335</v>
+        <v>1.675095089161969</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7855600696293488</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.28442731029685</v>
+        <v>4.130160993313517</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256367</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>3.656118190693542</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.134712951860744</v>
+        <v>-5.065359143028328</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.75614290261883</v>
+        <v>1.629618109168463</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6786345217514974</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.217565220727774</v>
+        <v>4.063298903744442</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700996</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>3.657546992836777</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.279731510367992</v>
+        <v>-5.210377701535577</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.699564281359164</v>
+        <v>1.573039487908798</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5336159632442489</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.131982887766659</v>
+        <v>3.977716570783326</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687008</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>3.75747823209453</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.39807327615271</v>
+        <v>-5.328719467320294</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.75215881430303</v>
+        <v>1.625634020852664</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5443020018071389</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.238325750162146</v>
+        <v>4.084059433178814</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790798</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>3.755263929220469</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.449483698473418</v>
+        <v>-5.380129889641002</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.729380342500686</v>
+        <v>1.60285554905032</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5443020018071389</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.236111447288085</v>
+        <v>4.081845130304752</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437326</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>3.755167057294758</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.528903149681169</v>
+        <v>-5.459549340848754</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.697515690091875</v>
+        <v>1.570990896641509</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5443020018071389</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.236014575362375</v>
+        <v>4.081748258379042</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298392</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>3.755160950852801</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.624366147598387</v>
+        <v>-5.555012338765971</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.659324384483031</v>
+        <v>1.532799591032664</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5443020018071389</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.236008468920417</v>
+        <v>4.081742151937084</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217994</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>3.753257347415412</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.559990236747672</v>
+        <v>-5.490636427915256</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.683171145385927</v>
+        <v>1.556646351935561</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6086779126578541</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.272730411993457</v>
+        <v>4.118464095010125</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73608941335353</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>3.758991165163138</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.615359398879866</v>
+        <v>-5.54600559004745</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.666757298280777</v>
+        <v>1.54023250483041</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6086779126578541</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.278464229741184</v>
+        <v>4.124197912757851</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113273</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>3.758529528506071</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.633577865877474</v>
+        <v>-5.564224057045059</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.659008274824666</v>
+        <v>1.532483481374299</v>
       </c>
       <c r="F2064" t="n">
         <v>0.5835714754020119</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.26293873073061</v>
+        <v>4.108672413747279</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113682</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>3.778403921356389</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.594894430533544</v>
+        <v>-5.525540621701128</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.694356041812557</v>
+        <v>1.56783124836219</v>
       </c>
       <c r="F2065" t="n">
         <v>0.5835714754020119</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.282813123580929</v>
+        <v>4.128546806597597</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016435</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>3.762104621881117</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.488859435328235</v>
+        <v>-5.419505626495819</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.720470740419408</v>
+        <v>1.593945946969042</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5835714754020119</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.266513824105657</v>
+        <v>4.112247507122325</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307666</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>3.764535571345163</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.305647772195139</v>
+        <v>-5.313227829267422</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.796186355136692</v>
+        <v>1.638888015324446</v>
       </c>
       <c r="F2067" t="n">
         <v>0.5835714754020119</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.268944773569703</v>
+        <v>4.11467845658637</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863547</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.901746294407872</v>
+        <v>3.74747997742454</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.233926325181288</v>
+        <v>-5.241506382253571</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.807819340021609</v>
+        <v>1.650521000209364</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6552929224158626</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.294922047857391</v>
+        <v>4.140655730874058</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394108</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.848662040329044</v>
+        <v>3.694395723345712</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.211553299573582</v>
+        <v>-5.219133356645865</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.763684296185863</v>
+        <v>1.606385956373618</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6665486735287641</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.248591244446303</v>
+        <v>4.094324927462971</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456724</v>
+        <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.0338602452144</v>
+        <v>3.879593928231067</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.244569595484327</v>
+        <v>-5.25214965255661</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.935675982706921</v>
+        <v>1.778377642894675</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5971112968620125</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.392127023331607</v>
+        <v>4.237860706348274</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883673</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.025781471042649</v>
+        <v>3.871515154059316</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.233041959834718</v>
+        <v>-5.240622016907001</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.932208262795013</v>
+        <v>1.774909922982768</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6561119550633749</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.419448644080674</v>
+        <v>4.265182327097341</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236292</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.029449583564437</v>
+        <v>3.875183266581105</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.330383461177087</v>
+        <v>-5.33796351824937</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.896939774779855</v>
+        <v>1.739641434967609</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6116917728978866</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.396464647303169</v>
+        <v>4.242198330319837</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427678</v>
+        <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.030700665757275</v>
+        <v>3.876434348773943</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.416239490517054</v>
+        <v>-5.423819547589336</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.863848445236706</v>
+        <v>1.706550105424461</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5693157036717515</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.372290087960327</v>
+        <v>4.218023770976995</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610377</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.013119867577777</v>
+        <v>3.858853550594445</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.425076287933173</v>
+        <v>-5.432656345005456</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.84273292809076</v>
+        <v>1.685434588278515</v>
       </c>
       <c r="F2074" t="n">
         <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.350243986196018</v>
+        <v>4.195977669212686</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71554441166745</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.023284378622827</v>
+        <v>3.869018061639495</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.516458850498632</v>
+        <v>-5.524038907570914</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.816344414109626</v>
+        <v>1.659046074297381</v>
       </c>
       <c r="F2075" t="n">
         <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.338469566409461</v>
+        <v>4.184203249426129</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889185</v>
+        <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.125412636447095</v>
+        <v>3.971146319463763</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.504752132511626</v>
+        <v>-5.512332189583908</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.923155359128697</v>
+        <v>1.765857019316452</v>
       </c>
       <c r="F2076" t="n">
         <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.447621855025933</v>
+        <v>4.293355538042601</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409561</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.1284449751785</v>
+        <v>3.974178658195168</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.575664206253903</v>
+        <v>-5.583244263326186</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.897822868363191</v>
+        <v>1.740524528550945</v>
       </c>
       <c r="F2077" t="n">
         <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.450654193757337</v>
+        <v>4.296387876774006</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452567</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.341349808456558</v>
+        <v>4.187083491473226</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.585980304420255</v>
+        <v>-5.593560361492538</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.106601262374708</v>
+        <v>1.949302922562463</v>
       </c>
       <c r="F2078" t="n">
         <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.663559027035395</v>
+        <v>4.509292710052064</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762281</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.340528475368647</v>
+        <v>4.186262158385316</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.585886336402882</v>
+        <v>-5.593466393475166</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.105817516493747</v>
+        <v>1.948519176681502</v>
       </c>
       <c r="F2079" t="n">
         <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.662959610755876</v>
+        <v>4.508693293772544</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.634813277125764</v>
+        <v>3.800870306884075</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.334760461313001</v>
+        <v>4.180494144329669</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.734252564059027</v>
+        <v>-5.737067557498551</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.040703011375643</v>
+        <v>1.885310697016501</v>
       </c>
       <c r="F2080" t="n">
         <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.65719159670023</v>
+        <v>4.502925279716898</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647901163120256</v>
+        <v>3.671015692129646</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.351781874534649</v>
+        <v>4.180494144329669</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.860536118116717</v>
+        <v>-5.736119134380512</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.007211002974214</v>
+        <v>1.885690066263717</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.4111016715876899</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.598442877487264</v>
+        <v>4.502925279716898</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881059287042959</v>
+        <v>3.904173816052349</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.364509482515741</v>
+        <v>4.193221752310762</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.960805936075738</v>
+        <v>-5.836388952339533</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.979830683771698</v>
+        <v>1.8583097470612</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.4111016715876899</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.611170485468355</v>
+        <v>4.51565288769799</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717065078804103</v>
+        <v>3.740179607813493</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.366455480940129</v>
+        <v>4.195167750735149</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.954813689286927</v>
+        <v>-5.830396705550721</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.98417358091161</v>
+        <v>1.862652644201113</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.4111016715876899</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.613116483892743</v>
+        <v>4.517598886122378</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741936267528551</v>
+        <v>3.765050796537942</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.360109616957898</v>
+        <v>4.188821886752918</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.866255728156159</v>
+        <v>-5.741838744419954</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.013250901381686</v>
+        <v>1.891729964671188</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.4111016715876899</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.606770619910511</v>
+        <v>4.511253022140147</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735294641762423</v>
+        <v>3.758409170771814</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.359418294396893</v>
+        <v>4.188130564191914</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.848496650653085</v>
+        <v>-5.72407966691688</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.019663209821911</v>
+        <v>1.898142273111414</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.4111016715876899</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.606079297349508</v>
+        <v>4.510561699579142</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778226068100329</v>
+        <v>3.80134059710972</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.37220048030548</v>
+        <v>4.200912750100501</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.748866499604017</v>
+        <v>-5.624449515867812</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.072297456150125</v>
+        <v>1.950776519439628</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.5107318226367574</v>
+        <v>0.637015376694448</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.678639573887535</v>
+        <v>4.58312197611717</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775351017834604</v>
+        <v>3.798465546843994</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.561354745804207</v>
+        <v>4.390067015599227</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.798266008293028</v>
+        <v>-5.673849024556823</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.241691918173247</v>
+        <v>2.12017098146275</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.5209906560685021</v>
+        <v>0.6472742101261927</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.873949139445308</v>
+        <v>4.778431541674943</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749071979342465</v>
+        <v>3.772186508351855</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.548543418907069</v>
+        <v>4.377255688702089</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.591581534650652</v>
+        <v>-5.467164550914447</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.31155438073306</v>
+        <v>2.190033444022562</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.7276751297108778</v>
+        <v>0.8539586837685683</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.985148496733595</v>
+        <v>4.88963089896323</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740278309541875</v>
+        <v>3.763392838551265</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.550544932561174</v>
+        <v>4.379257202356194</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.625738429648178</v>
+        <v>-5.501321445911973</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.299893136388154</v>
+        <v>2.178372199677657</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.6440913601700653</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.936999748663213</v>
+        <v>4.841482150892848</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782476036031715</v>
+        <v>3.805590565041106</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.904042046550841</v>
+        <v>4.732754316345861</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.533148950586722</v>
+        <v>-5.408731966850516</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.690426042002404</v>
+        <v>2.568905105291907</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.6440913601700653</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.290496862652881</v>
+        <v>5.194979264882515</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809049825488005</v>
+        <v>3.832164354497396</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.908605158117945</v>
+        <v>4.737317427912965</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.606309554359867</v>
+        <v>-5.481892570623661</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.66572491206025</v>
+        <v>2.544203975349752</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.6160701601358223</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.278247254199439</v>
+        <v>5.182729656429073</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835196361482896</v>
+        <v>3.858310890492286</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.958435099441473</v>
+        <v>4.787147369236492</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.554093244563525</v>
+        <v>-5.429676260827319</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.736441377302314</v>
+        <v>2.614920440591816</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.6160701601358223</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.328077195522966</v>
+        <v>5.2325595977526</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821821067427077</v>
+        <v>3.844935596436468</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.967249069651483</v>
+        <v>4.795961339446503</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.522195727478279</v>
+        <v>-5.397778743742074</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.758014354346424</v>
+        <v>2.636493417635926</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.6479676772210681</v>
+        <v>0.7742512312787586</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.356029675984125</v>
+        <v>5.260512078213758</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825262337030086</v>
+        <v>3.848376866039477</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.96288665369068</v>
+        <v>4.7915989234857</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.53695105167842</v>
+        <v>-5.412534067942214</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.747749808705565</v>
+        <v>2.626228871995066</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.6479676772210681</v>
+        <v>0.7742512312787586</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.351667260023321</v>
+        <v>5.256149662252955</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845038586515081</v>
+        <v>3.868153115524471</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.95381115710696</v>
+        <v>4.78252342690198</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.487486428308508</v>
+        <v>-5.363069444572303</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.758460161469809</v>
+        <v>2.636939224759311</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.6974323005909797</v>
+        <v>0.8237158546486703</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.372270537461548</v>
+        <v>5.276752939691182</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825925710858554</v>
+        <v>3.849040239867945</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.950218824821895</v>
+        <v>4.778931094616914</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.324378436154893</v>
+        <v>-5.199961452418687</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.820111026046189</v>
+        <v>2.698590089335692</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.860540292744595</v>
+        <v>0.9868238468022855</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.466543000468652</v>
+        <v>5.371025402698286</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847090399223578</v>
+        <v>3.870204928232969</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.959265861513023</v>
+        <v>4.787978131308043</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.303735345353665</v>
+        <v>-5.17931836161746</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.837415299057809</v>
+        <v>2.71589436234731</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.860540292744595</v>
+        <v>0.9868238468022855</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.475590037159781</v>
+        <v>5.380072439389414</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832419908170282</v>
+        <v>3.855534437179672</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.960123326499144</v>
+        <v>4.788835596294164</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.366443261828223</v>
+        <v>-5.115549496405909</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.813189597454107</v>
+        <v>2.742259373418052</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.7978323762700372</v>
+        <v>1.050592712013837</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.438822752261167</v>
+        <v>5.419191223502466</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861573319958328</v>
+        <v>3.884687848967719</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.923032743289497</v>
+        <v>4.751745013084516</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.31843513798453</v>
+        <v>-5.067541372562216</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.795302263781937</v>
+        <v>2.724372039745882</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.7978323762700372</v>
+        <v>1.050592712013837</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.401732169051519</v>
+        <v>5.382100640292818</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872247828009217</v>
+        <v>3.895362357018607</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.926964996847447</v>
+        <v>4.755677266642467</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.23960948080094</v>
+        <v>-4.988715715378626</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.830764780213323</v>
+        <v>2.759834556177268</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.8766580334536277</v>
+        <v>1.129418369197427</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.452959816919624</v>
+        <v>5.433328288160923</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868496452065739</v>
+        <v>3.89161098107513</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.921864089454484</v>
+        <v>4.750576359249504</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.047674679547066</v>
+        <v>-4.796780914124752</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.902437793321909</v>
+        <v>2.831507569285855</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.8766580334536277</v>
+        <v>1.129418369197427</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.447858909526661</v>
+        <v>5.42822738076796</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.849317964426046</v>
+        <v>3.872432493435436</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.917217998843579</v>
+        <v>4.745930268638599</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.92950130152914</v>
+        <v>-4.678607536106824</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.945061053918176</v>
+        <v>2.874130829882121</v>
       </c>
       <c r="F2102" t="n">
-        <v>0.9948314114715551</v>
+        <v>1.247591747215354</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.514116845726512</v>
+        <v>5.494485316967812</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.836457194908334</v>
+        <v>3.859571723917725</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.946306591706606</v>
+        <v>4.775018861501626</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.816086618746408</v>
+        <v>-4.565192853324093</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.019515519894295</v>
+        <v>2.948585295858241</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.108246094254286</v>
+        <v>1.361006429998086</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.611254248259178</v>
+        <v>5.591622719500478</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.805495133363348</v>
+        <v>3.828006274013631</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.939866814717783</v>
+        <v>4.768579084512803</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.789037581053154</v>
+        <v>-4.538143815630839</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.023895357982774</v>
+        <v>2.952965133946719</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.13529513194754</v>
+        <v>1.388055467691339</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.621043893886307</v>
+        <v>5.601412365127607</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.797617459253714</v>
+        <v>3.823987445263775</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.905355132088824</v>
+        <v>4.768579084512803</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.801285439472421</v>
+        <v>-4.544177095817609</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.984484531986108</v>
+        <v>2.950551821872011</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.123047273528273</v>
+        <v>1.388055467691339</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.579183496205789</v>
+        <v>5.601412365127607</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.640569789667616</v>
+        <v>3.857438083035479</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.93580700368736</v>
+        <v>4.962374898471428</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.801285439472421</v>
+        <v>-4.544177095817609</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.984484531986108</v>
+        <v>2.950551821872011</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.123047273528273</v>
+        <v>1.388055467691339</v>
       </c>
       <c r="G2106" t="n">
-        <v>4.928870800673728</v>
+        <v>4.955438695457796</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241003.xlsx
+++ b/tame_output/ON/bt/strategyON_20241003.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.0%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>184.6%</t>
+          <t>193.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-607.5%</t>
+          <t>-595.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-48.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.8%</t>
+          <t>426.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-616.0%</t>
+          <t>-612.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-243.4%</t>
+          <t>-238.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>129.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-81.2%</t>
+          <t>-64.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-203.6%</t>
+          <t>-262.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-85.2%</t>
+          <t>-108.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>58.2%</t>
         </is>
       </c>
     </row>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296833</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6545912063460799</v>
+        <v>-0.5330713720359961</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.859135855474547</v>
+        <v>2.90774378919858</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6432019696912785</v>
+        <v>-0.5216821353811947</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.861516346255708</v>
+        <v>2.910124279979741</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.8956798641106845</v>
+        <v>-0.7741600298006006</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.758452079993008</v>
+        <v>2.807060013717042</v>
       </c>
       <c r="F1847" t="n">
         <v>1.291969947040633</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.185811530716116</v>
+        <v>-1.064291696406032</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.642265629949757</v>
+        <v>2.690873563673791</v>
       </c>
       <c r="F1848" t="n">
         <v>1.316051741780813</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.393815589069193</v>
+        <v>-1.272295754759109</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.563956151162452</v>
+        <v>2.612564084886485</v>
       </c>
       <c r="F1849" t="n">
         <v>1.316051741780813</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.455994000230163</v>
+        <v>-1.334474165920079</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.534166243036052</v>
+        <v>2.582774176760085</v>
       </c>
       <c r="F1850" t="n">
         <v>1.253873330619843</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.822062727374816</v>
+        <v>-1.700542893064732</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.38082305148464</v>
+        <v>2.429430985208673</v>
       </c>
       <c r="F1851" t="n">
         <v>0.88780460347519</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.0305535088265</v>
+        <v>-1.909033674516417</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.317765028642734</v>
+        <v>2.366372962366768</v>
       </c>
       <c r="F1852" t="n">
         <v>0.6793138220235055</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.277754693591722</v>
+        <v>-2.156234859281638</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.226983305145214</v>
+        <v>2.275591238869248</v>
       </c>
       <c r="F1853" t="n">
         <v>0.699467175522318</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.770139721615819</v>
+        <v>-2.648619887305735</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.031135685979308</v>
+        <v>2.079743619703342</v>
       </c>
       <c r="F1854" t="n">
         <v>0.2070821474982212</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.02844348929949</v>
+        <v>-2.906923654989406</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.926356717718702</v>
+        <v>1.974964651442736</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.278314169314071</v>
+        <v>-3.156794335003987</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.828177569167486</v>
+        <v>1.87678550289152</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.484825946201093</v>
+        <v>-3.363306111891009</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.741678917068935</v>
+        <v>1.790286850792969</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.804170021281594</v>
+        <v>-3.68265018697151</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.615714213736994</v>
+        <v>1.664322147461028</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.190379852557369</v>
+        <v>-4.068860018247285</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.447563168694089</v>
+        <v>1.496171102418122</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.458931643255243</v>
+        <v>-4.337411808945159</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.32842722741703</v>
+        <v>1.377035161141064</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.1179447876207835</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.794594290485695</v>
+        <v>-4.673074456175612</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.192742760180814</v>
+        <v>1.241350693904848</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.1858757731096883</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.871038620688567</v>
+        <v>-4.749518786378483</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.168652588333907</v>
+        <v>1.217260522057941</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.1054302640160264</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.236166003327313</v>
+        <v>-5.11464616901723</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.02185615028424</v>
+        <v>1.070464084008274</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.4017410483150389</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.644754780507992</v>
+        <v>-5.523234946197908</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.857182183426727</v>
+        <v>0.9057901171507612</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.8103298254957174</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.758515192530857</v>
+        <v>-5.636995358220773</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.806863451089042</v>
+        <v>0.8554713848130757</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.8103298254957174</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.174907066817855</v>
+        <v>-6.05338723250777</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6383007519831203</v>
+        <v>0.686908685707154</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.8103298254957174</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.536080696634842</v>
+        <v>-6.414560862324758</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5040899907250038</v>
+        <v>0.552697924449038</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.8103298254957174</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.879339216277861</v>
+        <v>-6.757819381967777</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3628861480134917</v>
+        <v>0.4114940817375259</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.927542033520205</v>
+        <v>-6.806022199210121</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3420099411715549</v>
+        <v>0.3906178748955891</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.094350693494567</v>
+        <v>-6.972830859184483</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2790654531110186</v>
+        <v>0.3276733868350523</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.852613149208854</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.28107040180387</v>
+        <v>-7.159550567493786</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2003512652528943</v>
+        <v>0.2489591989769284</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.852613149208854</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.664071790546501</v>
+        <v>-7.542551956236417</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.04704860843425784</v>
+        <v>0.09565654215829156</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.852613149208854</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.66855823574789</v>
+        <v>-7.547038401437805</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.04782554632513225</v>
+        <v>0.09643348004916641</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8570995944102426</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.028088558251891</v>
+        <v>-7.906568723941807</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.09063627937841856</v>
+        <v>-0.04202834565438396</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8570995944102426</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.078437621706113</v>
+        <v>-7.956917787396029</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1028598848029296</v>
+        <v>-0.05425195107889547</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.9074486578644647</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-8.054537064817426</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>-0.0902579114256854</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.005067935285861</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-8.108608564325785</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>-0.1089929549074564</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.059139434794221</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-8.112184350417532</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>-0.1049100722255134</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.084668356710713</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.145837188926006</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>-0.1138886531444667</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.185081724627751</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.284923303544863</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.1541513974985884</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.324167839246607</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.460047720931406</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.2096459437056888</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.499292256633151</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.694499814945896</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.3106459462130808</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.499292256633151</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-8.798874545972343</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.3590680293976356</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.603666987659597</v>
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-8.883341588548403</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.3917390565895031</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.701300418078284</v>
+        <v>-1.696570239011216</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.141173752296635</v>
+        <v>2.144011859736876</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-9.009378381916692</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.4394600453077042</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.671318616201474</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.159018454611595</v>
+        <v>2.161856562051836</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-8.952306610020761</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.4126410008629313</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.671318616201474</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.163008790297996</v>
+        <v>2.165846897738237</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.093978451744881</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.4707849644513211</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.671318616201474</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.161533563399254</v>
+        <v>2.164371670839495</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-9.044387607320047</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.4358952165165149</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.626457950843708</v>
+        <v>-1.62172777177664</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.206341480219027</v>
+        <v>2.209179587659268</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-8.895469272848191</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.3893790163744555</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.595208360108535</v>
+        <v>-1.590478181041467</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.212040101013448</v>
+        <v>2.214878208453689</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.66962412012878</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.2894618822504826</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.548551505454303</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.249613286842195</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.545045463791189</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.2384912751593871</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.548551505454303</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.250752431398254</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.520008782222678</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.2258428283698755</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.523222417903567</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.268583658090803</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.447875606934797</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.1912558540160862</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.523222417903567</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.27431736232944</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.644238203941597</v>
+        <v>-8.444671946508992</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2795381552126726</v>
+        <v>-0.1997116522396292</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.520018757477761</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.263664188750818</v>
+        <v>2.266502296191058</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.550779169956373</v>
+        <v>-8.351212912523767</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2520380229314902</v>
+        <v>-0.1722115199584473</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.520018757477761</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.25378070743791</v>
+        <v>2.256618814878151</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.540125988402941</v>
+        <v>-8.340559730970336</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2496113108094913</v>
+        <v>-0.1697848078364483</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.520018757477761</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.251946146938536</v>
+        <v>2.254784254378777</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.442218949726451</v>
+        <v>-8.242652692293845</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.210748810312356</v>
+        <v>-0.1309223073393126</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.456763186684273</v>
+        <v>-1.452033007617205</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.292437281881409</v>
+        <v>2.29527538932165</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.418265408750493</v>
+        <v>-8.218699151317887</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2004988877764791</v>
+        <v>-0.1206723848034361</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.432809645708315</v>
+        <v>-1.428079466641247</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.307477912612478</v>
+        <v>2.310316020052718</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.154205470427696</v>
+        <v>-7.954639212995091</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1081352286091124</v>
+        <v>-0.0283087256360699</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.164019528318451</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.452653559444403</v>
+        <v>2.455491666884644</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.447125846922858</v>
+        <v>-7.247559589490253</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.171909587132522</v>
+        <v>0.2517360901055645</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.164019528318451</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.449866525784102</v>
+        <v>2.452704633224343</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.406941548556667</v>
+        <v>-7.207375291124062</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1883269303668396</v>
+        <v>0.2681534333398821</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.128565409019328</v>
+        <v>-1.12383522995226</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.474320728691658</v>
+        <v>2.477158836131899</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.243541677617305</v>
+        <v>-7.0439754201847</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2530536999633415</v>
+        <v>0.332880202936384</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9651655380799653</v>
+        <v>-0.9604353590128976</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.571727472476033</v>
+        <v>2.574565579916273</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.08542429823853</v>
+        <v>-6.885858040805925</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3242250805527038</v>
+        <v>0.4040515835257468</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8070481587011898</v>
+        <v>-0.8023179796341221</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.67452232894115</v>
+        <v>2.677360436381391</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.935757907231014</v>
+        <v>-6.73619164979841</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.381199426642751</v>
+        <v>0.4610259296157935</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7141446674586539</v>
+        <v>-0.7094144883915862</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.727372213373712</v>
+        <v>2.730210320813953</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.803482433600128</v>
+        <v>-6.603916176167523</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3353704021022601</v>
+        <v>0.4151969050753026</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5818691938277673</v>
+        <v>-0.5771390147606995</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.707998283559399</v>
+        <v>2.71083639099964</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.631621218035225</v>
+        <v>-6.43205496060262</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4069299490158578</v>
+        <v>0.4867564519889003</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4100079782628644</v>
+        <v>-0.4052777991957967</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.813930073585978</v>
+        <v>2.816768181026218</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.546656551305906</v>
+        <v>-6.3470902938733</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4538221569312442</v>
+        <v>0.5336486599042871</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3250433115335448</v>
+        <v>-0.3203131324664771</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.877815214847228</v>
+        <v>2.880653322287469</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.652246541079011</v>
+        <v>-6.452680283646405</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2836102314227835</v>
+        <v>0.3634367343958269</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4306333013066492</v>
+        <v>-0.4259031222395814</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.686485291384147</v>
+        <v>2.689323398824388</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.584011956453583</v>
+        <v>-6.384445699020977</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3594484071500412</v>
+        <v>0.4392749101230842</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4122179784341132</v>
+        <v>-0.4074877993670454</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.746078826984755</v>
+        <v>2.748916934424996</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.436071915045984</v>
+        <v>-6.236505657613378</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3020036150746739</v>
+        <v>0.3818301180477168</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3918970625255556</v>
+        <v>-0.3871668834584879</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.641650567891482</v>
+        <v>2.644488675331723</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.383102392791995</v>
+        <v>-6.18353613535939</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.314477437722791</v>
+        <v>0.394303940695834</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.334197361204499</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.664718294990398</v>
+        <v>2.667556402430638</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.217314196831705</v>
+        <v>-6.017747939399099</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.373832104011814</v>
+        <v>0.4536586069848569</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.334197361204499</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.657757682895304</v>
+        <v>2.660595790335545</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.183950990352936</v>
+        <v>-5.98438473292033</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4016397409844648</v>
+        <v>0.4814662439575077</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.334197361204499</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.672220037276448</v>
+        <v>2.675058144716688</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.075691853230414</v>
+        <v>-5.876125595797808</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4394755162926685</v>
+        <v>0.5193020192657114</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.334197361204499</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.666752157735643</v>
+        <v>2.669590265175883</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.952400718413283</v>
+        <v>-5.752834460980678</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4862900642300976</v>
+        <v>0.5661165672031405</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2156364054544362</v>
+        <v>-0.2109062263873685</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.738224932636498</v>
+        <v>2.741063040076738</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.899703851281992</v>
+        <v>-5.700137593849386</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5150697893199392</v>
+        <v>0.5948962922929826</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.1582093592560773</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.777544031152598</v>
+        <v>2.780382138592838</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.655938409298548</v>
+        <v>-5.456372151865942</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6083566744603677</v>
+        <v>0.6881831774334106</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.1582093592560773</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.773324739499648</v>
+        <v>2.776162846939889</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.566162736922076</v>
+        <v>-5.36659647948947</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6463912573309725</v>
+        <v>0.7262177603040159</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.0966099143417673</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.81240872036825</v>
+        <v>2.815246827808491</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.316312342973001</v>
+        <v>-5.116746085540395</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7390734898943045</v>
+        <v>0.8188999928673475</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.0966099143417673</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.805150795351952</v>
+        <v>2.807988902792193</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.140420250505569</v>
+        <v>-4.940853993072963</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8130294504019262</v>
+        <v>0.8928559533749691</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.0966099143417673</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.808749918872601</v>
+        <v>2.811588026312842</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.968973787483105</v>
+        <v>-4.7694075300505</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8949355416654652</v>
+        <v>0.9747620446385084</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.07010636961362809</v>
+        <v>0.07483654868069584</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.924945302740633</v>
+        <v>2.927783410180873</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.888951500373985</v>
+        <v>-4.689385242941379</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9259649341254106</v>
+        <v>1.005791437098454</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1501286567227491</v>
+        <v>0.1548588357898168</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.971979152622402</v>
+        <v>2.974817260062643</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.82531575814005</v>
+        <v>-4.625749500707444</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9561140320733017</v>
+        <v>1.035940535046345</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.2184945780237513</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.01485539901708</v>
+        <v>3.017693506457321</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.731618439923655</v>
+        <v>-4.532052182491049</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9747872181436554</v>
+        <v>1.054613721116698</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.2184945780237513</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.996049657800876</v>
+        <v>2.998887765241117</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.742121062988944</v>
+        <v>-4.542554805556338</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9723292455424173</v>
+        <v>1.05215574851546</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.2079919549584625</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.99149116058658</v>
+        <v>2.99432926802682</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.629634802320069</v>
+        <v>-4.430068544887463</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.021253063644787</v>
+        <v>1.10107956661783</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.2079919549584625</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.9954204744214</v>
+        <v>2.998258581861641</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.611921115442204</v>
+        <v>-4.412354858009598</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.029017122313273</v>
+        <v>1.108843625286316</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2111732838553793</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.99800785567689</v>
+        <v>3.000845963117131</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.488446844129186</v>
+        <v>-4.28888058669658</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.075404902058474</v>
+        <v>1.155231405031517</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2111732838553793</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.995005926896884</v>
+        <v>2.997844034337124</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.43051101213097</v>
+        <v>-4.230944754698364</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.100158271868374</v>
+        <v>1.179984774841418</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2367351585381285</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.011922088717147</v>
+        <v>3.014760196157388</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.297643323067692</v>
+        <v>-4.098077065635087</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.169199530295509</v>
+        <v>1.249026033268552</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2367351585381285</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.02781627151897</v>
+        <v>3.030654378959211</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.177470239703194</v>
+        <v>-3.977903982270588</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.21841460808161</v>
+        <v>1.298241111054653</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3521780628355597</v>
+        <v>0.3569082419026275</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.101065965977972</v>
+        <v>3.103904073418212</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.042216878373217</v>
+        <v>-3.842650620940611</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.282604055175041</v>
+        <v>1.362430558148084</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4874314241655369</v>
+        <v>0.4921616032326046</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.192306085337398</v>
+        <v>3.195144192777639</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.102091705730909</v>
+        <v>-3.902525448298303</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24469161563339</v>
+        <v>1.324518118606433</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4322867758749125</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.142418680324209</v>
+        <v>3.145256787764449</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.982271474820072</v>
+        <v>-3.782705217387466</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.307908877231933</v>
+        <v>1.387735380204976</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4322867758749125</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.157707849558417</v>
+        <v>3.160545956998658</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.984741181281878</v>
+        <v>-3.785174923849272</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.214565193969652</v>
+        <v>1.294391696942696</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4250868903460386</v>
+        <v>0.4298170694131063</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.063870225003775</v>
+        <v>3.066708332444016</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.053111367605887</v>
+        <v>-3.853545110173282</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10647898092535</v>
+        <v>1.186305483898393</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4390927684493213</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.988697505910805</v>
+        <v>2.991535613351046</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.164983647232038</v>
+        <v>-3.965417389799432</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.052166777706781</v>
+        <v>1.131993280679824</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4390927684493213</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.979134214542697</v>
+        <v>2.981972321982937</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.14900898174577</v>
+        <v>-3.949442724313164</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.025131168825316</v>
+        <v>1.104957671798358</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4390927684493213</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.945708739466724</v>
+        <v>2.948546846906964</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.973534721953301</v>
+        <v>-3.773968464520695</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.099888104734091</v>
+        <v>1.179714607707134</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4390927684493213</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.950275971458512</v>
+        <v>2.953114078898752</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.965610347368387</v>
+        <v>-3.766044089935781</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.078799883329264</v>
+        <v>1.158626386302307</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4390927684493213</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.926018000219719</v>
+        <v>2.928856107659959</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.959332144798538</v>
+        <v>-3.759765887365932</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.009849477758653</v>
+        <v>1.089675980731696</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4453709710191703</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.858323235163078</v>
+        <v>2.861161342603319</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.899479525594815</v>
+        <v>-3.699913268162209</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.043962911872275</v>
+        <v>1.123789414845318</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4453709710191703</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.86849562159521</v>
+        <v>2.871333729035451</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.813236062568437</v>
+        <v>-3.613669805135832</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.073406567656686</v>
+        <v>1.153233070629729</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4453709710191703</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.863441892169071</v>
+        <v>2.866279999609311</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.858542881967417</v>
+        <v>-3.658976624534811</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.04705961534162</v>
+        <v>1.126886118314663</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4045608080099395</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.830731569808058</v>
+        <v>2.833569677248299</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.818222177837304</v>
+        <v>-3.688009729237113</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.063739770026767</v>
+        <v>1.115824749466844</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.4045608080099395</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.831283442841159</v>
+        <v>2.8341215502814</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.725411696386444</v>
+        <v>-3.595199247786254</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.030136654498476</v>
+        <v>1.082221633938553</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4926411103937312</v>
+        <v>0.4973712894607989</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.816242423603041</v>
+        <v>2.819080531043281</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.769801165715872</v>
+        <v>-3.639588717115681</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.014254342691306</v>
+        <v>1.066339322131383</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4482516410643035</v>
+        <v>0.4529818201313712</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.791482217929985</v>
+        <v>2.794320325370225</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.749297471830375</v>
+        <v>-3.619085023230184</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.017531528757228</v>
+        <v>1.069616508197305</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.4734855140168686</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.798860142773006</v>
+        <v>2.801698250213247</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.832969568542707</v>
+        <v>-3.702757119942516</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9895539859029621</v>
+        <v>1.041638965343039</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.4734855140168686</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.804351438603673</v>
+        <v>2.807189546043914</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.86074996644406</v>
+        <v>-3.730537517843869</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9899390285109599</v>
+        <v>1.042024007951037</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4409749370484478</v>
+        <v>0.4457051161155155</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.799180401631401</v>
+        <v>2.802018509071641</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.979130639174198</v>
+        <v>-3.848918190574008</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7809424794195579</v>
+        <v>0.8330274588596347</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.3784872639645393</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.597205410341468</v>
+        <v>2.600043517781709</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.087744717617529</v>
+        <v>-3.957532269017339</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8576465087614311</v>
+        <v>0.909731488201508</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.3784872639645393</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.717355071060674</v>
+        <v>2.720193178500915</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.052335679369386</v>
+        <v>-3.922123230769196</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8863231501630113</v>
+        <v>0.9384081296030882</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.3784872639645393</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.731868097162997</v>
+        <v>2.734706204603238</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.060796848024847</v>
+        <v>-3.930584399424657</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8803581240431957</v>
+        <v>0.9324431034832723</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.3700260953090783</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.724210837312089</v>
+        <v>2.72704894475233</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.883680517989681</v>
+        <v>-3.753468069389491</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9479336849025646</v>
+        <v>1.000018664342641</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.3700260953090783</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.720939866157391</v>
+        <v>2.723777973597632</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.928772762823226</v>
+        <v>-3.798560314223036</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9305801787310592</v>
+        <v>0.9826651581711361</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3033998730726207</v>
+        <v>0.3081300521396885</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.684485632017671</v>
+        <v>2.687323739457911</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.749397341584459</v>
+        <v>-3.619184892984268</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9961173225329807</v>
+        <v>1.048202301973058</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4601766312433394</v>
+        <v>0.4649068103104071</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.772338662226516</v>
+        <v>2.775176769666757</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.794411555105065</v>
+        <v>-3.664199106504875</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.958919092456328</v>
+        <v>1.011004071896405</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4298277359287348</v>
+        <v>0.4345579149958025</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.734936780369343</v>
+        <v>2.737774887809584</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.882422741663762</v>
+        <v>-3.752210293063572</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.929406180171795</v>
+        <v>0.9814911596118716</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3643512280695618</v>
+        <v>0.3690814071366296</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.701342437992785</v>
+        <v>2.704180545433026</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.983620523100935</v>
+        <v>-3.853408074500745</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8881309894934273</v>
+        <v>0.9402159689335039</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.3006725935913104</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.659501071762095</v>
+        <v>2.662339179202335</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.977109556486622</v>
+        <v>-3.846897107886432</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8883353376934691</v>
+        <v>0.9404203171335457</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.3006725935913104</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.657101033316412</v>
+        <v>2.659939140756652</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.958071428779325</v>
+        <v>-3.827858980179135</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8924753079846328</v>
+        <v>0.9445602874247097</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.2424889822601158</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.61871558572594</v>
+        <v>2.62155369316618</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131247</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.010587231054145</v>
+        <v>-3.880374782453955</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9907633887088951</v>
+        <v>1.042848368148972</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.2424889822601158</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.73800998736013</v>
+        <v>2.740848094800371</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.013995542488725</v>
+        <v>-3.883783093888534</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9902333931211968</v>
+        <v>1.042318372561274</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.2750055512694932</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.75835325775189</v>
+        <v>2.761191365192131</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.994639406594878</v>
+        <v>-3.864426957994687</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.003984377875662</v>
+        <v>1.056069357315738</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.2750055512694932</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.764361788148816</v>
+        <v>2.767199895589057</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.067968935332971</v>
+        <v>-3.93775648673278</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8726027876576239</v>
+        <v>0.9246877670977007</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.2754002136891152</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.662548806877789</v>
+        <v>2.66538691431803</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.151790156607669</v>
+        <v>-4.021577708007478</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8418679206792254</v>
+        <v>0.8939529001193025</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.2754002136891152</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.66534242840927</v>
+        <v>2.668180535849511</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.145637450554885</v>
+        <v>-4.015425001954694</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8449913514919976</v>
+        <v>0.8970763309320746</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2768227406748317</v>
+        <v>0.2815529197418994</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.669696400432599</v>
+        <v>2.67253450787284</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.162446748705387</v>
+        <v>-4.032234300105196</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.837348108971907</v>
+        <v>0.8894330884119841</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2600134425243301</v>
+        <v>0.2647436215913978</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.658691298282408</v>
+        <v>2.661529405722649</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.100148749929264</v>
+        <v>-3.969936301329074</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9286028622791769</v>
+        <v>0.9806878417192537</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3053077067987721</v>
+        <v>0.3100378858658399</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.752203410643894</v>
+        <v>2.755041518084135</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.898358552264106</v>
+        <v>-3.768146103663916</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.811610943059367</v>
+        <v>0.863695922499444</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5033258989679266</v>
+        <v>0.5080560780349943</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.673306327659514</v>
+        <v>2.676144435099754</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.949245264950301</v>
+        <v>-3.819032816350111</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8615464903070644</v>
+        <v>0.9136314697471413</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.452439186281732</v>
+        <v>0.4571693653487998</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.713064532369972</v>
+        <v>2.715902639810213</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.862634522300494</v>
+        <v>-3.732422073700303</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9108185234830311</v>
+        <v>0.9629035029231079</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5310649174868902</v>
+        <v>0.535795096553958</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.774867707209111</v>
+        <v>2.777705814649352</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.922843820305778</v>
+        <v>-3.792631371705588</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8852707851055888</v>
+        <v>0.9373557645456658</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.4755857985486734</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.737278109230612</v>
+        <v>2.740116216670852</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.873657171621427</v>
+        <v>-3.743444723021236</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.903437062619258</v>
+        <v>0.9555220420593349</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.4755857985486734</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.735769727270541</v>
+        <v>2.738607834710781</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.829284039982858</v>
+        <v>-3.699071591382668</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9210491827101217</v>
+        <v>0.9731341621501985</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.519958930187242</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.762256473689118</v>
+        <v>2.765094581129358</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.794552718664357</v>
+        <v>-3.664340270064167</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9293355053761125</v>
+        <v>0.9814204848161894</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.519958930187242</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.756650267827708</v>
+        <v>2.759488375267949</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.746896988103302</v>
+        <v>-3.616684539503111</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9547795546283393</v>
+        <v>1.006864534068416</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.56288448168123</v>
+        <v>0.5676146607482977</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.791625463192146</v>
+        <v>2.794463570632387</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.646378829604547</v>
+        <v>-3.516166381004356</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.999879191402566</v>
+        <v>1.051964170842643</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6634026401799845</v>
+        <v>0.6681328192470523</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.856828731666124</v>
+        <v>2.859666839106365</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.630473500172195</v>
+        <v>-3.500261051572004</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9929959956513792</v>
+        <v>1.045080975091456</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5842899794707457</v>
+        <v>0.5890201585378134</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.796115807716453</v>
+        <v>2.798953915156694</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.585635098563797</v>
+        <v>-3.455422649963606</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.015029058905367</v>
+        <v>1.067114038345444</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5888334124156152</v>
+        <v>0.5935635914826829</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.802939570094003</v>
+        <v>2.805777677534244</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.605133554805805</v>
+        <v>-3.474921106205614</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.011390616039642</v>
+        <v>1.063475595479719</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5407487711357108</v>
+        <v>0.5454789502027786</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.778249724957139</v>
+        <v>2.781087832397379</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.560930717719904</v>
+        <v>-3.430718269119713</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.034951353401839</v>
+        <v>1.087036332841916</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5849516082216113</v>
+        <v>0.589681787288679</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.810651029736516</v>
+        <v>2.813489137176757</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.568490383556951</v>
+        <v>-3.43827793495676</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.030337487536268</v>
+        <v>1.082422466976345</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.6444851912984983</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.841943072611655</v>
+        <v>2.844781180051896</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.410198966017679</v>
+        <v>-3.279986517417488</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.144901819735016</v>
+        <v>1.196986799175094</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.6444851912984983</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.893190837794695</v>
+        <v>2.896028945234935</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.202556962383203</v>
+        <v>-3.072344513783012</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.22639932578306</v>
+        <v>1.278484305223137</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8473970158659068</v>
+        <v>0.8521271949329745</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.016216744569634</v>
+        <v>3.019054852009874</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.151524869660675</v>
+        <v>-3.021312421060484</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.241760391110341</v>
+        <v>1.293845370550418</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8984291085884347</v>
+        <v>0.9031592876555025</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.04178422844142</v>
+        <v>3.044622335881661</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.086300688533469</v>
+        <v>-2.956088239933278</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.285037467653928</v>
+        <v>1.337122447094006</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9636532897156403</v>
+        <v>0.9683834687827081</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.098106141210449</v>
+        <v>3.100944248650689</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.048873668462335</v>
+        <v>-2.918661219862144</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.295969247981662</v>
+        <v>1.34805422742174</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.968904827744822</v>
+        <v>0.9736350068118897</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.097218036327238</v>
+        <v>3.100056143767479</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.04751568348879</v>
+        <v>-2.917303234888599</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.297769234302321</v>
+        <v>1.349854213742398</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.043242953282641</v>
+        <v>1.047973132349708</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.143077703981169</v>
+        <v>3.14591581142141</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.019102420388906</v>
+        <v>-2.888889971788715</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.469692310563485</v>
+        <v>1.521777290003562</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9842673905362118</v>
+        <v>0.9889975696032796</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.268250137354523</v>
+        <v>3.271088244794763</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.944320159363893</v>
+        <v>-2.814107710763702</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.619718124191307</v>
+        <v>1.671803103631385</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.059049651561224</v>
+        <v>1.063779830628292</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.433232403187348</v>
+        <v>3.436070510627588</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.918236075100086</v>
+        <v>-2.788023626499895</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.621859733910689</v>
+        <v>1.673944713350767</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.059049651561224</v>
+        <v>1.063779830628292</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.424940379201207</v>
+        <v>3.427778486641447</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.830358161990965</v>
+        <v>-2.700145713390774</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.655204094738117</v>
+        <v>1.707289074178194</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.174975293984576</v>
+        <v>1.179705473051643</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.492688960238997</v>
+        <v>3.495527067679237</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.821465700597682</v>
+        <v>-2.691253251997491</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.676315485022222</v>
+        <v>1.728400464462299</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.174975293984576</v>
+        <v>1.179705473051643</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.510243365965788</v>
+        <v>3.513081473406029</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.98994181756756</v>
+        <v>-2.859729368967369</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.600780085638855</v>
+        <v>1.652865065078932</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.147027458267995</v>
+        <v>1.151757637335063</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.485329711940424</v>
+        <v>3.488167819380664</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.54368562493812</v>
+        <v>-2.413473176337929</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.760552259878492</v>
+        <v>1.812637239318569</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.052308788598362</v>
+        <v>1.05703896766543</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.409768207326506</v>
+        <v>3.412606314766747</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.520964521254967</v>
+        <v>-2.390752072654776</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.760304723848658</v>
+        <v>1.812389703288735</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.052308788598362</v>
+        <v>1.05703896766543</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.40043222982341</v>
+        <v>3.403270337263651</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.65016633454901</v>
+        <v>-2.519953885948819</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.86753012438221</v>
+        <v>1.919615103822287</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.92310697530432</v>
+        <v>0.9278371543713877</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.481817267698154</v>
+        <v>3.484655375138395</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.676040733023036</v>
+        <v>-2.545828284422845</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.894258187486246</v>
+        <v>1.946343166926323</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9680185840160611</v>
+        <v>0.9727487630831289</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.545842055418845</v>
+        <v>3.548680162859086</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.668986042807862</v>
+        <v>-2.538773594207671</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.893755419561861</v>
+        <v>1.945840399001938</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9750732742312349</v>
+        <v>0.9798034532983027</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.546750225537495</v>
+        <v>3.549588332977736</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.642034818481374</v>
+        <v>-2.511822369881183</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.914542062937198</v>
+        <v>1.966627042377275</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.9946837993260218</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.565684586798868</v>
+        <v>3.568522694239109</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.663579046312161</v>
+        <v>-2.53336659771197</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.090027503949843</v>
+        <v>2.14211248338992</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.9946837993260218</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.749787718943828</v>
+        <v>3.752625826384068</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.685987164117033</v>
+        <v>-2.555774715516842</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.073180951730887</v>
+        <v>2.125265931170964</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.9946837993260218</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.741904413846821</v>
+        <v>3.744742521287062</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.714211399694634</v>
+        <v>-2.583998951094443</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.063945257049484</v>
+        <v>2.116030236489562</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007930372710263</v>
+        <v>1.01266055177733</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.754744464867243</v>
+        <v>3.757582572307484</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.723652325583164</v>
+        <v>-2.641003629543946</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.116422604415919</v>
+        <v>2.149482082831607</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.130357490253654</v>
+        <v>1.021597706772628</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.884454453115125</v>
+        <v>3.81919858302651</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.929891263371597</v>
+        <v>-2.84724256733238</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.036818123845847</v>
+        <v>2.069877602261534</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.8153587689841941</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.763602184987366</v>
+        <v>3.698346314898751</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.006221240972503</v>
+        <v>-2.923572544933286</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.004397945699259</v>
+        <v>2.037457424114947</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9241185524652205</v>
+        <v>0.8153587689841941</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.761713997881141</v>
+        <v>3.696458127792526</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.161178026372632</v>
+        <v>-3.078529330333415</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.93723546114207</v>
+        <v>1.970294939557758</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7691617670650912</v>
+        <v>0.6604019835840649</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.663560156243926</v>
+        <v>3.59830428615531</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.322746451899887</v>
+        <v>-3.24009775586067</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.871042101141321</v>
+        <v>1.904101579557008</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.5336190597861855</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.585924412175351</v>
+        <v>3.520668542086735</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.431047113770007</v>
+        <v>-3.34839841773079</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.840795243259191</v>
+        <v>1.873854721674879</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.5336190597861855</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.598997819041269</v>
+        <v>3.533741948952653</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.590598186533524</v>
+        <v>-3.507949490494306</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.768980010936724</v>
+        <v>1.802039489352412</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4901011764054604</v>
+        <v>0.381341392924434</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.499636415707158</v>
+        <v>3.434380545618543</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.618498973642997</v>
+        <v>-3.535850277603779</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.756343737219937</v>
+        <v>1.789403215635625</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4555042522625256</v>
+        <v>0.3467444687814992</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.477402302348399</v>
+        <v>3.412146432259784</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.741025076345891</v>
+        <v>-3.658376380306673</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.704097740115978</v>
+        <v>1.737157218531666</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3329781495596317</v>
+        <v>0.2242183660786053</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.400651084703862</v>
+        <v>3.335395214615246</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.971539572531479</v>
+        <v>-3.888890876492262</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.678597901232247</v>
+        <v>1.711657379647934</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.102463653374043</v>
+        <v>-0.006296130106983377</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.329048346583012</v>
+        <v>3.263792476494397</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.320284657755923</v>
+        <v>-4.237635961716705</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.679411586144316</v>
+        <v>1.712471064560004</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.1150440840258812</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.404111293233521</v>
+        <v>3.338855423144905</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.474271075532063</v>
+        <v>-4.391622379492846</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.6867972881795</v>
+        <v>1.719856766595188</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.1150440840258812</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.473091562379161</v>
+        <v>3.407835692290545</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.678870510395072</v>
+        <v>-4.596221814355855</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.591008716354418</v>
+        <v>1.624068194770105</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.1150440840258812</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.459142764499282</v>
+        <v>3.393886894410666</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.931345664402796</v>
+        <v>-4.848696968363579</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.501889143806742</v>
+        <v>1.534948622222429</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.1150440840258812</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.471013253554696</v>
+        <v>3.40575738346608</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.224241420882208</v>
+        <v>-5.141592724842991</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.385941375733921</v>
+        <v>1.419000854149608</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.006284300544854848</v>
+        <v>-0.1150440840258812</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.472223788073639</v>
+        <v>3.406967917985023</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.410905549017016</v>
+        <v>-5.328256852977799</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.315397466707319</v>
+        <v>1.348456945123006</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.03302327136941474</v>
+        <v>-0.1417830548504411</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.460302147806225</v>
+        <v>3.395046277717609</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.556926235930979</v>
+        <v>-5.474277539891761</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.252067044677923</v>
+        <v>1.285126523093611</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.04210636316327171</v>
+        <v>-0.150866146644298</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.4499301454661</v>
+        <v>3.384674275377484</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.648640245040564</v>
+        <v>-5.565991549001346</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.377585497733133</v>
+        <v>1.410644976148821</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.04210636316327171</v>
+        <v>-0.150866146644298</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.612134202165144</v>
+        <v>3.546878332076528</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.680291904100534</v>
+        <v>-5.597643208061315</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.35977147207296</v>
+        <v>1.392830950488647</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04727482040771191</v>
+        <v>-0.1560346038887382</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.603879765782294</v>
+        <v>3.538623895693678</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.74935795867347</v>
+        <v>-5.666709262634252</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.342374467812276</v>
+        <v>1.375433946227964</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1096456979013219</v>
+        <v>-0.2184054813823483</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.576686656854619</v>
+        <v>3.511430786766003</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.851334080921878</v>
+        <v>-5.76868538488266</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.310509657368816</v>
+        <v>1.343569135784504</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2116218201497295</v>
+        <v>-0.3203816036307559</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.524426621961477</v>
+        <v>3.459170751872861</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.741327797444656</v>
+        <v>-5.658679101405438</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.34666505800388</v>
+        <v>1.379724536419567</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1884172482324543</v>
+        <v>-0.2971770317134806</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.530502252356018</v>
+        <v>3.465246382267402</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.753857502556535</v>
+        <v>-5.671208806517317</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.345903186681102</v>
+        <v>1.37896266509679</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2022437476989773</v>
+        <v>-0.3110035311800037</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.526456363398078</v>
+        <v>3.461200493309462</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.500797177916668</v>
+        <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.452410777084697</v>
+        <v>-5.369762081045479</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.31947644276904</v>
+        <v>1.506802238168061</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.09920297777285991</v>
+        <v>-0.009556805708166416</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.560318964580384</v>
+        <v>3.6493294114751</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.501768355669378</v>
+        <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.477001021319881</v>
+        <v>-5.394352325280663</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.310611522827678</v>
+        <v>1.497937318226698</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.09920297777285991</v>
+        <v>-0.009556805708166416</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.561290142333094</v>
+        <v>3.650300589227811</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.502611260049134</v>
+        <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.425962645313361</v>
+        <v>-5.343313949274143</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.331869777610041</v>
+        <v>1.519195573009062</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.09920297777285991</v>
+        <v>-0.009556805708166416</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.56213304671285</v>
+        <v>3.651143493607567</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.521649358923279</v>
+        <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.397113968489901</v>
+        <v>-5.314465272450683</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.362447347213571</v>
+        <v>1.549773142612592</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1280516545963202</v>
+        <v>0.01929187111529385</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.598480351681071</v>
+        <v>3.687490798575789</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.337833355047214</v>
+        <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.300479056471261</v>
+        <v>-5.217830360432043</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.217285308144961</v>
+        <v>1.404611103543982</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2246865666149601</v>
+        <v>0.1159267831339338</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.47264529501619</v>
+        <v>3.561655741910907</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.341335399121178</v>
+        <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.231441045522793</v>
+        <v>-5.148792349483575</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.248402556598313</v>
+        <v>1.435728351997333</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2937245775634282</v>
+        <v>0.1849647940824019</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.517570145659235</v>
+        <v>3.606580592553952</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.32576221819726</v>
+        <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.212653945153854</v>
+        <v>-5.130005249114636</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.240344215821971</v>
+        <v>1.427670011220991</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.2037518944513403</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.513269224956681</v>
+        <v>3.602279671851397</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.32494992863369</v>
+        <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.135555343611982</v>
+        <v>-5.052906647572764</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.270371366875149</v>
+        <v>1.45769716227417</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.2037518944513403</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.51245693539311</v>
+        <v>3.601467382287827</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.334818707758763</v>
+        <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.145940538501871</v>
+        <v>-5.063291842462653</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.276086068044266</v>
+        <v>1.463411863443287</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3021264830424774</v>
+        <v>0.193366699561451</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.516094597584249</v>
+        <v>3.605105044478966</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.405655713535188</v>
+        <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.164528697224096</v>
+        <v>-5.081880001184878</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.339487810331801</v>
+        <v>1.526813605730822</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.283538324320252</v>
+        <v>0.1747785408392257</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.575778708127339</v>
+        <v>3.664789155022056</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.402524724353486</v>
+        <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.164827243920132</v>
+        <v>-5.082178547880914</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.336237402471685</v>
+        <v>1.523563197870706</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2832397776242161</v>
+        <v>0.1744799941431898</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.572468590928016</v>
+        <v>3.661479037822733</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.407055619292878</v>
+        <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.064004110229704</v>
+        <v>-4.981355414190486</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.381097550887248</v>
+        <v>1.568423346286269</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2957039931085699</v>
+        <v>0.1869442096275436</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.58447801515802</v>
+        <v>3.673488462052737</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.407184872771421</v>
+        <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.873222749477296</v>
+        <v>-4.790574053438078</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.457539348666754</v>
+        <v>1.644865144065775</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4864853538609773</v>
+        <v>0.377725570379951</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.699076085088008</v>
+        <v>3.788086531982724</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.387021718509017</v>
+        <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.766259391627875</v>
+        <v>-4.683610695588657</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.480161537544119</v>
+        <v>1.66748733294314</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5449499618207787</v>
+        <v>0.4361901783397524</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.713991695601485</v>
+        <v>3.803002142496202</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.421988655121076</v>
+        <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.710928803726112</v>
+        <v>-4.628280107686894</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.537260709316883</v>
+        <v>1.724586504715904</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6002805497225409</v>
+        <v>0.4915207662415146</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.782156984954601</v>
+        <v>3.871167431849317</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.415675223022514</v>
+        <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.69887467681315</v>
+        <v>-4.616225980773931</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.535768927983506</v>
+        <v>1.723094723382526</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6123346766355037</v>
+        <v>0.5035748931544775</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.783076029003816</v>
+        <v>3.872086475898533</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.417555853206649</v>
+        <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.776230166941119</v>
+        <v>-4.693581470901901</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.506707362116454</v>
+        <v>1.694033157515475</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5349791865075343</v>
+        <v>0.4262194030265081</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.73854336511117</v>
+        <v>3.827553812005887</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.430406879084532</v>
+        <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.708181604249589</v>
+        <v>-4.625532908210371</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.546777813070948</v>
+        <v>1.734103608469969</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.4942679657180379</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.792223528603971</v>
+        <v>3.881233975498688</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.645256780013422</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.450609549258126</v>
+        <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.93978199741909</v>
+        <v>-4.857133301379871</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.474340325976742</v>
+        <v>1.661666121375763</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.4942679657180379</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.812426198777565</v>
+        <v>3.901436645672282</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.434215785325008</v>
+        <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.989833542948309</v>
+        <v>-4.907184846909091</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.437925943831937</v>
+        <v>1.625251739230957</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.4942679657180379</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.796032434844447</v>
+        <v>3.885042881739164</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.394467698918475</v>
+        <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.164940375524754</v>
+        <v>-5.082291679485536</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.328135124394825</v>
+        <v>1.515460919793846</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.4942679657180379</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.756284348437914</v>
+        <v>3.84529479533263</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.401490317915415</v>
+        <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.968840222094231</v>
+        <v>-4.886191526055013</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.413597804763974</v>
+        <v>1.600923600162995</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.799127902629587</v>
+        <v>0.6903681191485608</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.880967059493167</v>
+        <v>3.969977506387885</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.500661317488319</v>
+        <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.815814829980947</v>
+        <v>-4.733166133941729</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.573978961182193</v>
+        <v>1.761304756581213</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.8433935112618449</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.071953294334042</v>
+        <v>4.160963741228759</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.688127542396612</v>
+        <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.844122143854217</v>
+        <v>-4.761473447814999</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.750122260541177</v>
+        <v>1.937448055940198</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.8433935112618449</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.259419519242335</v>
+        <v>4.348429966137052</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.657530493750695</v>
+        <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.010715368967739</v>
+        <v>-4.928066672928521</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.652887921849851</v>
+        <v>1.840213717248872</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.6768002861483224</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.128866535528304</v>
+        <v>4.217876982423021</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.661206896412412</v>
+        <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.987679575606173</v>
+        <v>-4.905030879566955</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.665778641856195</v>
+        <v>1.853104437255216</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.6768002861483224</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.132542938190022</v>
+        <v>4.221553385084738</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.658824951535907</v>
+        <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.958433595150477</v>
+        <v>-4.875784899111259</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.675095089161969</v>
+        <v>1.86242088456099</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.6768002861483224</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.130160993313517</v>
+        <v>4.219171440208234</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.656118190693542</v>
+        <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.065359143028328</v>
+        <v>-4.98271044698911</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.629618109168463</v>
+        <v>1.816943904567484</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6786345217514974</v>
+        <v>0.5698747382704711</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.063298903744442</v>
+        <v>4.152309350639158</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.657546992836777</v>
+        <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.210377701535577</v>
+        <v>-5.127729005496358</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.573039487908798</v>
+        <v>1.760365283307819</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5336159632442489</v>
+        <v>0.4248561797632225</v>
       </c>
       <c r="G2057" t="n">
-        <v>3.977716570783326</v>
+        <v>4.066727017678043</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.75747823209453</v>
+        <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.328719467320294</v>
+        <v>-5.246070771281076</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.625634020852664</v>
+        <v>1.812959816251685</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4355422183261126</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.084059433178814</v>
+        <v>4.17306988007353</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.755263929220469</v>
+        <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.380129889641002</v>
+        <v>-5.297481193601784</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.60285554905032</v>
+        <v>1.790181344449341</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4355422183261126</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.081845130304752</v>
+        <v>4.170855577199469</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.755167057294758</v>
+        <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.459549340848754</v>
+        <v>-5.376900644809536</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.570990896641509</v>
+        <v>1.758316692040529</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4355422183261126</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.081748258379042</v>
+        <v>4.170758705273759</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.755160950852801</v>
+        <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.555012338765971</v>
+        <v>-5.472363642726753</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.532799591032664</v>
+        <v>1.720125386431685</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.4355422183261126</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.081742151937084</v>
+        <v>4.170752598831801</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.753257347415412</v>
+        <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.490636427915256</v>
+        <v>-5.407987731876038</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.556646351935561</v>
+        <v>1.743972147334582</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.4999181291768278</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.118464095010125</v>
+        <v>4.207474541904841</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.758991165163138</v>
+        <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.54600559004745</v>
+        <v>-5.463356894008232</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.54023250483041</v>
+        <v>1.727558300229431</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.4999181291768278</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.124197912757851</v>
+        <v>4.213208359652568</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.758529528506071</v>
+        <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.564224057045059</v>
+        <v>-5.481575361005841</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.532483481374299</v>
+        <v>1.71980927677332</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4748116919209856</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.108672413747279</v>
+        <v>4.197682860641995</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.778403921356389</v>
+        <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.525540621701128</v>
+        <v>-5.44289192566191</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.56783124836219</v>
+        <v>1.755157043761211</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4748116919209856</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.128546806597597</v>
+        <v>4.217557253492314</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.762104621881117</v>
+        <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.419505626495819</v>
+        <v>-5.336856930456601</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.593945946969042</v>
+        <v>1.781271742368062</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4748116919209856</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.112247507122325</v>
+        <v>4.201257954017041</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.764535571345163</v>
+        <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.313227829267422</v>
+        <v>-5.153645267323506</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.638888015324446</v>
+        <v>1.856987357085346</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.4748116919209856</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.11467845658637</v>
+        <v>4.203688903481087</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.74747997742454</v>
+        <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.241506382253571</v>
+        <v>-5.081923820309655</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.650521000209364</v>
+        <v>1.868620341970263</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6552929224158626</v>
+        <v>0.5465331389348362</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.140655730874058</v>
+        <v>4.229666177768775</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.694395723345712</v>
+        <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.219133356645865</v>
+        <v>-5.059550794701948</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.606385956373618</v>
+        <v>1.824485298134518</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6665486735287641</v>
+        <v>0.5577888900477378</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.094324927462971</v>
+        <v>4.183335374357687</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.879593928231067</v>
+        <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.25214965255661</v>
+        <v>-5.092567090612693</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.778377642894675</v>
+        <v>1.996476984655575</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5971112968620125</v>
+        <v>0.4883515133809862</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.237860706348274</v>
+        <v>4.326871153242991</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.871515154059316</v>
+        <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.240622016907001</v>
+        <v>-5.081039454963085</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.774909922982768</v>
+        <v>1.993009264743668</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6561119550633749</v>
+        <v>0.5473521715823486</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.265182327097341</v>
+        <v>4.354192773992058</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.875183266581105</v>
+        <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.33796351824937</v>
+        <v>-5.178380956305453</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.739641434967609</v>
+        <v>1.957740776728509</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6116917728978866</v>
+        <v>0.5029319894168602</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.242198330319837</v>
+        <v>4.331208777214553</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.876434348773943</v>
+        <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.423819547589336</v>
+        <v>-5.26423698564542</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.706550105424461</v>
+        <v>1.92464944718536</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5693157036717515</v>
+        <v>0.4605559201907252</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.218023770976995</v>
+        <v>4.307034217871711</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.858853550594445</v>
+        <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.432656345005456</v>
+        <v>-5.273073783061539</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.685434588278515</v>
+        <v>1.903533930039414</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5618735310304008</v>
+        <v>0.4531137475493744</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.195977669212686</v>
+        <v>4.284988116107402</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.869018061639495</v>
+        <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.524038907570914</v>
+        <v>-5.364456345626998</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.659046074297381</v>
+        <v>1.87714541605828</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253086463110561</v>
+        <v>0.4165488628300298</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.184203249426129</v>
+        <v>4.273213696320845</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
-        <v>3.971146319463763</v>
+        <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.512332189583908</v>
+        <v>-5.352749627639992</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.765857019316452</v>
+        <v>1.983956361077351</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.4282555808170362</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.293355538042601</v>
+        <v>4.382365984937317</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
-        <v>3.974178658195168</v>
+        <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.583244263326186</v>
+        <v>-5.423661701382269</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.740524528550945</v>
+        <v>1.958623870311845</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.4282555808170362</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.296387876774006</v>
+        <v>4.385398323668722</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.187083491473226</v>
+        <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.593560361492538</v>
+        <v>-5.433977799548621</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.949302922562463</v>
+        <v>2.167402264323362</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.4282555808170362</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.509292710052064</v>
+        <v>4.59830315694678</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.186262158385316</v>
+        <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.593466393475166</v>
+        <v>-5.433883831531248</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.948519176681502</v>
+        <v>2.166618518442401</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4286254421643542</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.508693293772544</v>
+        <v>4.59770374066726</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.800870306884075</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.180494144329669</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.737067557498551</v>
+        <v>-5.577484995554634</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.885310697016501</v>
+        <v>2.103410038777401</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4286254421643542</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.502925279716898</v>
+        <v>4.591935726611614</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.671015692129646</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.180494144329669</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.736119134380512</v>
+        <v>-5.576536572436595</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.885690066263717</v>
+        <v>2.103789408024616</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4286254421643542</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.502925279716898</v>
+        <v>4.591935726611614</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.904173816052349</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.193221752310762</v>
+        <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.836388952339533</v>
+        <v>-5.676806390395615</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.8583097470612</v>
+        <v>2.0764090888221</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4286254421643542</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.51565288769799</v>
+        <v>4.604663334592706</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.740179607813493</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.195167750735149</v>
+        <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.830396705550721</v>
+        <v>-5.670814143606804</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.862652644201113</v>
+        <v>2.080751985962012</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4286254421643542</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.517598886122378</v>
+        <v>4.606609333017094</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.765050796537942</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.188821886752918</v>
+        <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.741838744419954</v>
+        <v>-5.582256182476036</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.891729964671188</v>
+        <v>2.109829306432088</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4286254421643542</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.511253022140147</v>
+        <v>4.600263469034862</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.758409170771814</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.188130564191914</v>
+        <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.72407966691688</v>
+        <v>-5.564497104972962</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.898142273111414</v>
+        <v>2.116241614872314</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4286254421643542</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.510561699579142</v>
+        <v>4.599572146473858</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.80134059710972</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.200912750100501</v>
+        <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.624449515867812</v>
+        <v>-5.464866953923894</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.950776519439628</v>
+        <v>2.168875861200527</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.5282555932134216</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.58312197611717</v>
+        <v>4.672132423011885</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.798465546843994</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.390067015599227</v>
+        <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.673849024556823</v>
+        <v>-5.514266462612905</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.12017098146275</v>
+        <v>2.338270323223649</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.5385144266451664</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.778431541674943</v>
+        <v>4.867441988569658</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.772186508351855</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.377255688702089</v>
+        <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.467164550914447</v>
+        <v>-5.307581988970529</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.190033444022562</v>
+        <v>2.408132785783462</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.745198900287542</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.88963089896323</v>
+        <v>4.978641345857946</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.763392838551265</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.379257202356194</v>
+        <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.501321445911973</v>
+        <v>-5.341738883968056</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.178372199677657</v>
+        <v>2.396471541438556</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.6616151307467295</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.841482150892848</v>
+        <v>4.930492597787564</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.805590565041106</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.732754316345861</v>
+        <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.408731966850516</v>
+        <v>-5.249149404906599</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.568905105291907</v>
+        <v>2.787004447052806</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.6616151307467295</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.194979264882515</v>
+        <v>5.283989711777231</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.832164354497396</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.737317427912965</v>
+        <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.481892570623661</v>
+        <v>-5.322310008679744</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.544203975349752</v>
+        <v>2.762303317110652</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.6335939307124865</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.182729656429073</v>
+        <v>5.271740103323789</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.858310890492286</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.787147369236492</v>
+        <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.429676260827319</v>
+        <v>-5.270093698883402</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.614920440591816</v>
+        <v>2.833019782352716</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.6335939307124865</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.2325595977526</v>
+        <v>5.321570044647316</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.844935596436468</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.795961339446503</v>
+        <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.397778743742074</v>
+        <v>-5.238196181798156</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.636493417635926</v>
+        <v>2.854592759396825</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.6654914477977323</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.260512078213758</v>
+        <v>5.349522525108474</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.848376866039477</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.7915989234857</v>
+        <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.412534067942214</v>
+        <v>-5.252951505998297</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.626228871995066</v>
+        <v>2.844328213755966</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.6654914477977323</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.256149662252955</v>
+        <v>5.345160109147671</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.868153115524471</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.78252342690198</v>
+        <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.363069444572303</v>
+        <v>-5.203486882628385</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.636939224759311</v>
+        <v>2.85503856652021</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8237158546486703</v>
+        <v>0.7149560711676439</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.276752939691182</v>
+        <v>5.365763386585899</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.849040239867945</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.778931094616914</v>
+        <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.199961452418687</v>
+        <v>-5.04037889047477</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.698590089335692</v>
+        <v>2.916689431096591</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.8780640633212592</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.371025402698286</v>
+        <v>5.460035849593002</v>
       </c>
     </row>
     <row r="2097">
@@ -49779,19 +49779,19 @@
         <v>3.870204928232969</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.787978131308043</v>
+        <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.17931836161746</v>
+        <v>-5.019735799673542</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.71589436234731</v>
+        <v>2.93399370410821</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.8780640633212592</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.380072439389414</v>
+        <v>5.46908288628413</v>
       </c>
     </row>
     <row r="2098">
@@ -49802,19 +49802,19 @@
         <v>3.855534437179672</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.788835596294164</v>
+        <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.115549496405909</v>
+        <v>-5.0824437161481</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.742259373418052</v>
+        <v>2.909768002504508</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.050592712013837</v>
+        <v>0.8153561468467014</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.419191223502466</v>
+        <v>5.432315601385517</v>
       </c>
     </row>
     <row r="2099">
@@ -49825,19 +49825,19 @@
         <v>3.884687848967719</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.751745013084516</v>
+        <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.067541372562216</v>
+        <v>-5.034435592304408</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.724372039745882</v>
+        <v>2.891880668832338</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.050592712013837</v>
+        <v>0.8153561468467014</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.382100640292818</v>
+        <v>5.39522501817587</v>
       </c>
     </row>
     <row r="2100">
@@ -49848,19 +49848,19 @@
         <v>3.895362357018607</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.755677266642467</v>
+        <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.988715715378626</v>
+        <v>-4.955609935120817</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.759834556177268</v>
+        <v>2.927343185263724</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.129418369197427</v>
+        <v>0.8941818040302919</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.433328288160923</v>
+        <v>5.446452666043974</v>
       </c>
     </row>
     <row r="2101">
@@ -49871,19 +49871,19 @@
         <v>3.89161098107513</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.750576359249504</v>
+        <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.796780914124752</v>
+        <v>-4.763675133866943</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.831507569285855</v>
+        <v>2.999016198372311</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.129418369197427</v>
+        <v>0.8941818040302919</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.42822738076796</v>
+        <v>5.441351758651011</v>
       </c>
     </row>
     <row r="2102">
@@ -49894,19 +49894,19 @@
         <v>3.872432493435436</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.745930268638599</v>
+        <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.678607536106824</v>
+        <v>-4.645501755849017</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.874130829882121</v>
+        <v>3.041639458968577</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.247591747215354</v>
+        <v>1.012355182048219</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.494485316967812</v>
+        <v>5.507609694850863</v>
       </c>
     </row>
     <row r="2103">
@@ -49917,19 +49917,19 @@
         <v>3.859571723917725</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.775018861501626</v>
+        <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.565192853324093</v>
+        <v>-4.532087073066285</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.948585295858241</v>
+        <v>3.116093924944696</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.361006429998086</v>
+        <v>1.12576986483095</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.591622719500478</v>
+        <v>5.604747097383528</v>
       </c>
     </row>
     <row r="2104">
@@ -49940,19 +49940,19 @@
         <v>3.828006274013631</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.768579084512803</v>
+        <v>4.922845401496135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.538143815630839</v>
+        <v>-4.505038035373031</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.952965133946719</v>
+        <v>3.120473763033175</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.388055467691339</v>
+        <v>1.152818902524204</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.601412365127607</v>
+        <v>5.614536743010658</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263775</v>
+        <v>3.823987445263773</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.768579084512803</v>
+        <v>4.922845401496135</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.544177095817609</v>
+        <v>-4.511071315559802</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.950551821872011</v>
+        <v>3.118060450958467</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.388055467691339</v>
+        <v>1.152818902524204</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.601412365127607</v>
+        <v>5.614536743010658</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.857438083035479</v>
+        <v>3.868826538066061</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.962374898471428</v>
+        <v>5.048877733623272</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.544177095817609</v>
+        <v>-4.511071315559802</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.950551821872011</v>
+        <v>3.118060450958467</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.388055467691339</v>
+        <v>1.152818902524204</v>
       </c>
       <c r="G2106" t="n">
-        <v>4.955438695457796</v>
+        <v>5.041941530609639</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241003.xlsx
+++ b/tame_output/ON/bt/strategyON_20241003.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>193.3%</t>
+          <t>174.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-595.3%</t>
+          <t>-607.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.6%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>426.1%</t>
+          <t>417.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-612.7%</t>
+          <t>-636.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-238.5%</t>
+          <t>-243.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>129.8%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-64.4%</t>
+          <t>-74.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-262.2%</t>
+          <t>-300.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-108.7%</t>
+          <t>-100.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
     </row>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5330713720359961</v>
+        <v>-0.6545912063460799</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.90774378919858</v>
+        <v>2.859135855474547</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.5216821353811947</v>
+        <v>-0.6432019696912785</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.910124279979741</v>
+        <v>2.861516346255708</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7741600298006006</v>
+        <v>-0.8956798641106845</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.807060013717042</v>
+        <v>2.758452079993008</v>
       </c>
       <c r="F1847" t="n">
         <v>1.291969947040633</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.064291696406032</v>
+        <v>-1.185811530716116</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.690873563673791</v>
+        <v>2.642265629949757</v>
       </c>
       <c r="F1848" t="n">
         <v>1.316051741780813</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.272295754759109</v>
+        <v>-1.393815589069193</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.612564084886485</v>
+        <v>2.563956151162452</v>
       </c>
       <c r="F1849" t="n">
         <v>1.316051741780813</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.334474165920079</v>
+        <v>-1.455994000230163</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.582774176760085</v>
+        <v>2.534166243036052</v>
       </c>
       <c r="F1850" t="n">
         <v>1.253873330619843</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.700542893064732</v>
+        <v>-1.822062727374816</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.429430985208673</v>
+        <v>2.38082305148464</v>
       </c>
       <c r="F1851" t="n">
         <v>0.88780460347519</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.909033674516417</v>
+        <v>-2.0305535088265</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.366372962366768</v>
+        <v>2.317765028642734</v>
       </c>
       <c r="F1852" t="n">
         <v>0.6793138220235055</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.156234859281638</v>
+        <v>-2.277754693591722</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.275591238869248</v>
+        <v>2.226983305145214</v>
       </c>
       <c r="F1853" t="n">
         <v>0.699467175522318</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.648619887305735</v>
+        <v>-2.770139721615819</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.079743619703342</v>
+        <v>2.031135685979308</v>
       </c>
       <c r="F1854" t="n">
         <v>0.2070821474982212</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.906923654989406</v>
+        <v>-3.02844348929949</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.974964651442736</v>
+        <v>1.926356717718702</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.156794335003987</v>
+        <v>-3.278314169314071</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.87678550289152</v>
+        <v>1.828177569167486</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.363306111891009</v>
+        <v>-3.484825946201093</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.790286850792969</v>
+        <v>1.741678917068935</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.68265018697151</v>
+        <v>-3.804170021281594</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.664322147461028</v>
+        <v>1.615714213736994</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.068860018247285</v>
+        <v>-4.190379852557369</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.496171102418122</v>
+        <v>1.447563168694089</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.337411808945159</v>
+        <v>-4.458931643255243</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.377035161141064</v>
+        <v>1.32842722741703</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.1179447876207835</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.673074456175612</v>
+        <v>-4.794594290485695</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.241350693904848</v>
+        <v>1.192742760180814</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.1858757731096883</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.749518786378483</v>
+        <v>-4.871038620688567</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.217260522057941</v>
+        <v>1.168652588333907</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.1054302640160264</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.11464616901723</v>
+        <v>-5.236166003327313</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.070464084008274</v>
+        <v>1.02185615028424</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.4017410483150389</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.523234946197908</v>
+        <v>-5.644754780507992</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.9057901171507612</v>
+        <v>0.857182183426727</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.8103298254957174</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.636995358220773</v>
+        <v>-5.758515192530857</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8554713848130757</v>
+        <v>0.806863451089042</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.8103298254957174</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.05338723250777</v>
+        <v>-6.174907066817855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.686908685707154</v>
+        <v>0.6383007519831203</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.8103298254957174</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.414560862324758</v>
+        <v>-6.536080696634842</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.552697924449038</v>
+        <v>0.5040899907250038</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.8103298254957174</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.757819381967777</v>
+        <v>-6.879339216277861</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4114940817375259</v>
+        <v>0.3628861480134917</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.806022199210121</v>
+        <v>-6.927542033520205</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3906178748955891</v>
+        <v>0.3420099411715549</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.972830859184483</v>
+        <v>-7.094350693494567</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3276733868350523</v>
+        <v>0.2790654531110186</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.852613149208854</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.159550567493786</v>
+        <v>-7.28107040180387</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2489591989769284</v>
+        <v>0.2003512652528943</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.852613149208854</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.542551956236417</v>
+        <v>-7.664071790546501</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09565654215829156</v>
+        <v>0.04704860843425784</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.852613149208854</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.547038401437805</v>
+        <v>-7.66855823574789</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09643348004916641</v>
+        <v>0.04782554632513225</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8570995944102426</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.906568723941807</v>
+        <v>-8.028088558251891</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04202834565438396</v>
+        <v>-0.09063627937841856</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8570995944102426</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.956917787396029</v>
+        <v>-8.078437621706113</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05425195107889547</v>
+        <v>-0.1028598848029296</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.9074486578644647</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.054537064817426</v>
+        <v>-8.176056899127509</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.0902579114256854</v>
+        <v>-0.1388658451497196</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.005067935285861</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.108608564325785</v>
+        <v>-8.230128398635868</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1089929549074564</v>
+        <v>-0.1576008886314906</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.059139434794221</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.112184350417532</v>
+        <v>-8.233704184727616</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1049100722255134</v>
+        <v>-0.1535180059495476</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.084668356710713</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.145837188926006</v>
+        <v>-8.267357023236089</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1138886531444667</v>
+        <v>-0.1624965868685009</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.185081724627751</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.284923303544863</v>
+        <v>-8.406443137854946</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1541513974985884</v>
+        <v>-0.2027593312226226</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.324167839246607</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.460047720931406</v>
+        <v>-8.58156755524149</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2096459437056888</v>
+        <v>-0.2582538774297229</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.499292256633151</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.694499814945896</v>
+        <v>-8.816019649255979</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3106459462130808</v>
+        <v>-0.359253879937115</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.499292256633151</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.798874545972343</v>
+        <v>-8.920394380282426</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3590680293976356</v>
+        <v>-0.4076759631216698</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.603666987659597</v>
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.883341588548403</v>
+        <v>-9.08290784598101</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.3917390565895031</v>
+        <v>-0.471565559562547</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.696570239011216</v>
+        <v>-1.701300418078284</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.144011859736876</v>
+        <v>2.141173752296635</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.009378381916692</v>
+        <v>-9.2089446393493</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4394600453077042</v>
+        <v>-0.5192865482807481</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.671318616201474</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.161856562051836</v>
+        <v>2.159018454611595</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.952306610020761</v>
+        <v>-9.151872867453369</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4126410008629313</v>
+        <v>-0.4924675038359752</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.671318616201474</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.165846897738237</v>
+        <v>2.163008790297996</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.093978451744881</v>
+        <v>-9.293544709177489</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4707849644513211</v>
+        <v>-0.550611467424365</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.671318616201474</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.164371670839495</v>
+        <v>2.161533563399254</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.044387607320047</v>
+        <v>-9.243953864752655</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4358952165165149</v>
+        <v>-0.5157217194895587</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.62172777177664</v>
+        <v>-1.626457950843708</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.209179587659268</v>
+        <v>2.206341480219027</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.895469272848191</v>
+        <v>-9.095035530280798</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.3893790163744555</v>
+        <v>-0.4692055193474993</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.590478181041467</v>
+        <v>-1.595208360108535</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.214878208453689</v>
+        <v>2.212040101013448</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.66962412012878</v>
+        <v>-8.869190377561386</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.2894618822504826</v>
+        <v>-0.3692883852235256</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.548551505454303</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.249613286842195</v>
+        <v>2.246775179401955</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.545045463791189</v>
+        <v>-8.744611721223794</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2384912751593871</v>
+        <v>-0.31831777813243</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.548551505454303</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.250752431398254</v>
+        <v>2.247914323958013</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.520008782222678</v>
+        <v>-8.719575039655284</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2258428283698755</v>
+        <v>-0.3056693313429184</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.523222417903567</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.268583658090803</v>
+        <v>2.265745550650562</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.447875606934797</v>
+        <v>-8.647441864367403</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.1912558540160862</v>
+        <v>-0.2710823569891296</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.523222417903567</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.27431736232944</v>
+        <v>2.271479254889199</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.444671946508992</v>
+        <v>-8.644238203941597</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.1997116522396292</v>
+        <v>-0.2795381552126726</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.520018757477761</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.266502296191058</v>
+        <v>2.263664188750818</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.351212912523767</v>
+        <v>-8.550779169956373</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.1722115199584473</v>
+        <v>-0.2520380229314902</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.520018757477761</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.256618814878151</v>
+        <v>2.25378070743791</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.340559730970336</v>
+        <v>-8.540125988402941</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1697848078364483</v>
+        <v>-0.2496113108094913</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.520018757477761</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.254784254378777</v>
+        <v>2.251946146938536</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.242652692293845</v>
+        <v>-8.442218949726451</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1309223073393126</v>
+        <v>-0.210748810312356</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.452033007617205</v>
+        <v>-1.456763186684273</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.29527538932165</v>
+        <v>2.292437281881409</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.218699151317887</v>
+        <v>-8.418265408750493</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1206723848034361</v>
+        <v>-0.2004988877764791</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.428079466641247</v>
+        <v>-1.432809645708315</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.310316020052718</v>
+        <v>2.307477912612478</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.954639212995091</v>
+        <v>-8.154205470427696</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.0283087256360699</v>
+        <v>-0.1081352286091124</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.164019528318451</v>
+        <v>-1.168749707385519</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.455491666884644</v>
+        <v>2.452653559444403</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.247559589490253</v>
+        <v>-7.447125846922858</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2517360901055645</v>
+        <v>0.171909587132522</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.164019528318451</v>
+        <v>-1.168749707385519</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.452704633224343</v>
+        <v>2.449866525784102</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.207375291124062</v>
+        <v>-7.406941548556667</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2681534333398821</v>
+        <v>0.1883269303668396</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.12383522995226</v>
+        <v>-1.128565409019328</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.477158836131899</v>
+        <v>2.474320728691658</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.0439754201847</v>
+        <v>-7.243541677617305</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.332880202936384</v>
+        <v>0.2530536999633415</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9604353590128976</v>
+        <v>-0.9651655380799653</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.574565579916273</v>
+        <v>2.571727472476033</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.885858040805925</v>
+        <v>-7.08542429823853</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4040515835257468</v>
+        <v>0.3242250805527038</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8023179796341221</v>
+        <v>-0.8070481587011898</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.677360436381391</v>
+        <v>2.67452232894115</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.73619164979841</v>
+        <v>-6.935757907231014</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4610259296157935</v>
+        <v>0.381199426642751</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7094144883915862</v>
+        <v>-0.7141446674586539</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.730210320813953</v>
+        <v>2.727372213373712</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.603916176167523</v>
+        <v>-6.803482433600128</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4151969050753026</v>
+        <v>0.3353704021022601</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5771390147606995</v>
+        <v>-0.5818691938277673</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.71083639099964</v>
+        <v>2.707998283559399</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.43205496060262</v>
+        <v>-6.631621218035225</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4867564519889003</v>
+        <v>0.4069299490158578</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4052777991957967</v>
+        <v>-0.4100079782628644</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.816768181026218</v>
+        <v>2.813930073585978</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.3470902938733</v>
+        <v>-6.546656551305906</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5336486599042871</v>
+        <v>0.4538221569312442</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3203131324664771</v>
+        <v>-0.3250433115335448</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.880653322287469</v>
+        <v>2.877815214847228</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.452680283646405</v>
+        <v>-6.652246541079011</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3634367343958269</v>
+        <v>0.2836102314227835</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4259031222395814</v>
+        <v>-0.4306333013066492</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.689323398824388</v>
+        <v>2.686485291384147</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.384445699020977</v>
+        <v>-6.584011956453583</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4392749101230842</v>
+        <v>0.3594484071500412</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4074877993670454</v>
+        <v>-0.4122179784341132</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.748916934424996</v>
+        <v>2.746078826984755</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.236505657613378</v>
+        <v>-6.436071915045984</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3818301180477168</v>
+        <v>0.3020036150746739</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3871668834584879</v>
+        <v>-0.3918970625255556</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.644488675331723</v>
+        <v>2.641650567891482</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.18353613535939</v>
+        <v>-6.383102392791995</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.394303940695834</v>
+        <v>0.314477437722791</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.334197361204499</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.667556402430638</v>
+        <v>2.664718294990398</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.017747939399099</v>
+        <v>-6.217314196831705</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4536586069848569</v>
+        <v>0.373832104011814</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.334197361204499</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.660595790335545</v>
+        <v>2.657757682895304</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.98438473292033</v>
+        <v>-6.183950990352936</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4814662439575077</v>
+        <v>0.4016397409844648</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.334197361204499</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.675058144716688</v>
+        <v>2.672220037276448</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.876125595797808</v>
+        <v>-6.075691853230414</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5193020192657114</v>
+        <v>0.4394755162926685</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.334197361204499</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.669590265175883</v>
+        <v>2.666752157735643</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.752834460980678</v>
+        <v>-5.952400718413283</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5661165672031405</v>
+        <v>0.4862900642300976</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2109062263873685</v>
+        <v>-0.2156364054544362</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.741063040076738</v>
+        <v>2.738224932636498</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.700137593849386</v>
+        <v>-5.899703851281992</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5948962922929826</v>
+        <v>0.5150697893199392</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1582093592560773</v>
+        <v>-0.1629395383231451</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.780382138592838</v>
+        <v>2.777544031152598</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.456372151865942</v>
+        <v>-5.655938409298548</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6881831774334106</v>
+        <v>0.6083566744603677</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1582093592560773</v>
+        <v>-0.1629395383231451</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.776162846939889</v>
+        <v>2.773324739499648</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.36659647948947</v>
+        <v>-5.566162736922076</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7262177603040159</v>
+        <v>0.6463912573309725</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.0966099143417673</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.815246827808491</v>
+        <v>2.81240872036825</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.116746085540395</v>
+        <v>-5.42632435466748</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8188999928673475</v>
+        <v>0.6950686852165129</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.0966099143417673</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.807988902792193</v>
+        <v>2.805150795351952</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.940853993072963</v>
+        <v>-5.250432262200048</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8928559533749691</v>
+        <v>0.7690246457241345</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.0966099143417673</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.811588026312842</v>
+        <v>2.808749918872601</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.7694075300505</v>
+        <v>-5.078985799177585</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9747620446385084</v>
+        <v>0.8509307369876735</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.07483654868069584</v>
+        <v>0.07010636961362809</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.927783410180873</v>
+        <v>2.924945302740633</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.689385242941379</v>
+        <v>-4.998963512068464</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.005791437098454</v>
+        <v>0.8819601294476189</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1548588357898168</v>
+        <v>0.1501286567227491</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.974817260062643</v>
+        <v>2.971979152622402</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.625749500707444</v>
+        <v>-4.935327769834529</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.035940535046345</v>
+        <v>0.91210922739551</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2184945780237513</v>
+        <v>0.2137643989566836</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.017693506457321</v>
+        <v>3.01485539901708</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.532052182491049</v>
+        <v>-4.841630451618134</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.054613721116698</v>
+        <v>0.9307824134658635</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2184945780237513</v>
+        <v>0.2137643989566836</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.998887765241117</v>
+        <v>2.996049657800876</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.542554805556338</v>
+        <v>-4.852133074683423</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.05215574851546</v>
+        <v>0.9283244408646254</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2079919549584625</v>
+        <v>0.2032617758913947</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.99432926802682</v>
+        <v>2.99149116058658</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.430068544887463</v>
+        <v>-4.739646814014549</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.10107956661783</v>
+        <v>0.9772482589669955</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2079919549584625</v>
+        <v>0.2032617758913947</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.998258581861641</v>
+        <v>2.9954204744214</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.412354858009598</v>
+        <v>-4.721933127136683</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.108843625286316</v>
+        <v>0.9850123176354817</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2111732838553793</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.000845963117131</v>
+        <v>2.99800785567689</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.28888058669658</v>
+        <v>-4.598458855823665</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.155231405031517</v>
+        <v>1.031400097380682</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2111732838553793</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.997844034337124</v>
+        <v>2.995005926896884</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.230944754698364</v>
+        <v>-4.540523023825449</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.179984774841418</v>
+        <v>1.056153467190583</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2367351585381285</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.014760196157388</v>
+        <v>3.011922088717147</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.098077065635087</v>
+        <v>-4.407655334762172</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.249026033268552</v>
+        <v>1.125194725617717</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2367351585381285</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.030654378959211</v>
+        <v>3.02781627151897</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.977903982270588</v>
+        <v>-4.287482251397673</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.298241111054653</v>
+        <v>1.174409803403818</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3569082419026275</v>
+        <v>0.3521780628355597</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.103904073418212</v>
+        <v>3.101065965977972</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.842650620940611</v>
+        <v>-4.152228890067696</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.362430558148084</v>
+        <v>1.238599250497249</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4921616032326046</v>
+        <v>0.4874314241655369</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.195144192777639</v>
+        <v>3.192306085337398</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.902525448298303</v>
+        <v>-4.212103717425388</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.324518118606433</v>
+        <v>1.200686810955598</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4322867758749125</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.145256787764449</v>
+        <v>3.142418680324209</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.782705217387466</v>
+        <v>-4.092283486514551</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.387735380204976</v>
+        <v>1.263904072554142</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4322867758749125</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.160545956998658</v>
+        <v>3.157707849558417</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.785174923849272</v>
+        <v>-4.094753192976357</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.294391696942696</v>
+        <v>1.170560389291861</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4298170694131063</v>
+        <v>0.4250868903460386</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.066708332444016</v>
+        <v>3.063870225003775</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.853545110173282</v>
+        <v>-4.163123379300368</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.186305483898393</v>
+        <v>1.062474176247558</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4390927684493213</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.991535613351046</v>
+        <v>2.988697505910805</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.965417389799432</v>
+        <v>-4.274995658926518</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.131993280679824</v>
+        <v>1.008161973028989</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4390927684493213</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.981972321982937</v>
+        <v>2.979134214542697</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.949442724313164</v>
+        <v>-4.259020993440251</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.104957671798358</v>
+        <v>0.9811263641475234</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4390927684493213</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.948546846906964</v>
+        <v>2.945708739466724</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.773968464520695</v>
+        <v>-4.083546733647781</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.179714607707134</v>
+        <v>1.055883300056299</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4390927684493213</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.953114078898752</v>
+        <v>2.950275971458512</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.766044089935781</v>
+        <v>-4.075622359062867</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.158626386302307</v>
+        <v>1.034795078651472</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4390927684493213</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.928856107659959</v>
+        <v>2.926018000219719</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.759765887365932</v>
+        <v>-4.069344156493018</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.089675980731696</v>
+        <v>0.9658446730808612</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4453709710191703</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.861161342603319</v>
+        <v>2.858323235163078</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.699913268162209</v>
+        <v>-4.009491537289295</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.123789414845318</v>
+        <v>0.9999581071944827</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4453709710191703</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.871333729035451</v>
+        <v>2.86849562159521</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.613669805135832</v>
+        <v>-3.923248074262917</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.153233070629729</v>
+        <v>1.029401762978894</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4453709710191703</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.866279999609311</v>
+        <v>2.863441892169071</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.658976624534811</v>
+        <v>-3.968554893661897</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.126886118314663</v>
+        <v>1.003054810663828</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4045608080099395</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.833569677248299</v>
+        <v>2.830731569808058</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.688009729237113</v>
+        <v>-3.997587998364198</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.115824749466844</v>
+        <v>0.9919934418160088</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4045608080099395</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.8341215502814</v>
+        <v>2.831283442841159</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.595199247786254</v>
+        <v>-3.904777516913339</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.082221633938553</v>
+        <v>0.958390326287718</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4973712894607989</v>
+        <v>0.4926411103937312</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.819080531043281</v>
+        <v>2.816242423603041</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.639588717115681</v>
+        <v>-3.949166986242767</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.066339322131383</v>
+        <v>0.942508014480548</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4529818201313712</v>
+        <v>0.4482516410643035</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.794320325370225</v>
+        <v>2.791482217929985</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.619085023230184</v>
+        <v>-3.928663292357269</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.069616508197305</v>
+        <v>0.9457852005464698</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4734855140168686</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.801698250213247</v>
+        <v>2.798860142773006</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.702757119942516</v>
+        <v>-4.012335389069602</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.041638965343039</v>
+        <v>0.9178076576922041</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4734855140168686</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.807189546043914</v>
+        <v>2.804351438603673</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.730537517843869</v>
+        <v>-4.040115786970954</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.042024007951037</v>
+        <v>0.9181927003002022</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4457051161155155</v>
+        <v>0.4409749370484478</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.802018509071641</v>
+        <v>2.799180401631401</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.848918190574008</v>
+        <v>-4.158496459701093</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8330274588596347</v>
+        <v>0.7091961512088001</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3784872639645393</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.600043517781709</v>
+        <v>2.597205410341468</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.957532269017339</v>
+        <v>-4.267110538144424</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.909731488201508</v>
+        <v>0.7859001805506731</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3784872639645393</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.720193178500915</v>
+        <v>2.717355071060674</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.922123230769196</v>
+        <v>-4.231701499896281</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9384081296030882</v>
+        <v>0.8145768219522533</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3784872639645393</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.734706204603238</v>
+        <v>2.731868097162997</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.930584399424657</v>
+        <v>-4.240162668551742</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9324431034832723</v>
+        <v>0.8086117958324377</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3700260953090783</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.72704894475233</v>
+        <v>2.724210837312089</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.753468069389491</v>
+        <v>-4.063046338516576</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.000018664342641</v>
+        <v>0.8761873566918066</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3700260953090783</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.723777973597632</v>
+        <v>2.720939866157391</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.798560314223036</v>
+        <v>-4.108138583350121</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9826651581711361</v>
+        <v>0.8588338505203013</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3081300521396885</v>
+        <v>0.3033998730726207</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.687323739457911</v>
+        <v>2.684485632017671</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.619184892984268</v>
+        <v>-3.928763162111354</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.048202301973058</v>
+        <v>0.9243709943222227</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4649068103104071</v>
+        <v>0.4601766312433394</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.775176769666757</v>
+        <v>2.772338662226516</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.664199106504875</v>
+        <v>-3.97377737563196</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.011004071896405</v>
+        <v>0.88717276424557</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4345579149958025</v>
+        <v>0.4298277359287348</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.737774887809584</v>
+        <v>2.734936780369343</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.752210293063572</v>
+        <v>-4.061788562190657</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9814911596118716</v>
+        <v>0.857659851961037</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3690814071366296</v>
+        <v>0.3643512280695618</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.704180545433026</v>
+        <v>2.701342437992785</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.853408074500745</v>
+        <v>-4.162986343627829</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9402159689335039</v>
+        <v>0.8163846612826693</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3006725935913104</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.662339179202335</v>
+        <v>2.659501071762095</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.846897107886432</v>
+        <v>-4.156475377013517</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9404203171335457</v>
+        <v>0.8165890094827111</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3006725935913104</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.659939140756652</v>
+        <v>2.657101033316412</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.827858980179135</v>
+        <v>-4.137437249306219</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9445602874247097</v>
+        <v>0.820728979773875</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2424889822601158</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.62155369316618</v>
+        <v>2.61871558572594</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131247</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.880374782453955</v>
+        <v>-4.18995305158104</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.042848368148972</v>
+        <v>0.9190170604981371</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2424889822601158</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.740848094800371</v>
+        <v>2.73800998736013</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.883783093888534</v>
+        <v>-4.209919126130583</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.042318372561274</v>
+        <v>0.9118639596644535</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2750055512694932</v>
+        <v>0.2424521980219776</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.761191365192131</v>
+        <v>2.741659353243621</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.864426957994687</v>
+        <v>-4.190562990236735</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.056069357315738</v>
+        <v>0.9256149444189186</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2750055512694932</v>
+        <v>0.2424521980219776</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.767199895589057</v>
+        <v>2.747667883640547</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.93775648673278</v>
+        <v>-4.263892518974828</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9246877670977007</v>
+        <v>0.794233354200881</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2754002136891152</v>
+        <v>0.2428468604415995</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.66538691431803</v>
+        <v>2.64585490236952</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.021577708007478</v>
+        <v>-4.347713740249526</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8939529001193025</v>
+        <v>0.7634984872224826</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2754002136891152</v>
+        <v>0.2428468604415995</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.668180535849511</v>
+        <v>2.648648523901001</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.015425001954694</v>
+        <v>-4.341561034196742</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8970763309320746</v>
+        <v>0.7666219180352547</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2815529197418994</v>
+        <v>0.2489995664943838</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.67253450787284</v>
+        <v>2.65300249592433</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.032234300105196</v>
+        <v>-4.358370332347244</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8894330884119841</v>
+        <v>0.7589786755151642</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2647436215913978</v>
+        <v>0.2321902683438822</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.661529405722649</v>
+        <v>2.641997393774139</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.969936301329074</v>
+        <v>-4.296072333571122</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9806878417192537</v>
+        <v>0.850233428822434</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3100378858658399</v>
+        <v>0.2774845326183242</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.755041518084135</v>
+        <v>2.735509506135625</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.768146103663916</v>
+        <v>-4.094282135905964</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.863695922499444</v>
+        <v>0.7332415096026241</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5080560780349943</v>
+        <v>0.4755027247874786</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.676144435099754</v>
+        <v>2.656612423151245</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.819032816350111</v>
+        <v>-4.145168848592158</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9136314697471413</v>
+        <v>0.7831770568503216</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4571693653487998</v>
+        <v>0.4246160121012841</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.715902639810213</v>
+        <v>2.696370627861703</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.732422073700303</v>
+        <v>-4.058558105942351</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9629035029231079</v>
+        <v>0.832449090026288</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.535795096553958</v>
+        <v>0.5032417433064423</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.777705814649352</v>
+        <v>2.758173802700842</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.792631371705588</v>
+        <v>-4.118767403947636</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9373557645456658</v>
+        <v>0.8069013516488457</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4755857985486734</v>
+        <v>0.4430324453011578</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.740116216670852</v>
+        <v>2.720584204722343</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.743444723021236</v>
+        <v>-4.069580755263285</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9555220420593349</v>
+        <v>0.8250676291625147</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4755857985486734</v>
+        <v>0.4430324453011578</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.738607834710781</v>
+        <v>2.719075822762272</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.699071591382668</v>
+        <v>-4.025207623624716</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9731341621501985</v>
+        <v>0.8426797492533784</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.519958930187242</v>
+        <v>0.4874055769397264</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.765094581129358</v>
+        <v>2.745562569180849</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.664340270064167</v>
+        <v>-3.990476302306215</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9814204848161894</v>
+        <v>0.8509660719193692</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.519958930187242</v>
+        <v>0.4874055769397264</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.759488375267949</v>
+        <v>2.73995636331944</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.616684539503111</v>
+        <v>-3.94282057174516</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.006864534068416</v>
+        <v>0.8764101211715962</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5676146607482977</v>
+        <v>0.5350613075007821</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.794463570632387</v>
+        <v>2.774931558683877</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.516166381004356</v>
+        <v>-3.842302413246405</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.051964170842643</v>
+        <v>0.9215097579458229</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6681328192470523</v>
+        <v>0.6355794659995366</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.859666839106365</v>
+        <v>2.840134827157855</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.500261051572004</v>
+        <v>-3.826397083814053</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.045080975091456</v>
+        <v>0.9146265621946361</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5890201585378134</v>
+        <v>0.5564668052902977</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.798953915156694</v>
+        <v>2.779421903208184</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.455422649963606</v>
+        <v>-3.781558682205655</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.067114038345444</v>
+        <v>0.9366596254486239</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5935635914826829</v>
+        <v>0.5610102382351672</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.805777677534244</v>
+        <v>2.786245665585734</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.474921106205614</v>
+        <v>-3.801057138447663</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.063475595479719</v>
+        <v>0.9330211825828987</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5454789502027786</v>
+        <v>0.5129255969552629</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.781087832397379</v>
+        <v>2.76155582044887</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.430718269119713</v>
+        <v>-3.756854301361762</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.087036332841916</v>
+        <v>0.956581919945096</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.589681787288679</v>
+        <v>0.5571284340411633</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.813489137176757</v>
+        <v>2.793957125228247</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.43827793495676</v>
+        <v>-3.764413967198809</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.082422466976345</v>
+        <v>0.9519680540795248</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6444851912984983</v>
+        <v>0.6119318380509826</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.844781180051896</v>
+        <v>2.825249168103386</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.279986517417488</v>
+        <v>-3.606122549659537</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.196986799175094</v>
+        <v>1.066532386278273</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6444851912984983</v>
+        <v>0.6119318380509826</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.896028945234935</v>
+        <v>2.876496933286426</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.072344513783012</v>
+        <v>-3.398480546025061</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.278484305223137</v>
+        <v>1.148029892326317</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8521271949329745</v>
+        <v>0.8195738416854588</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.019054852009874</v>
+        <v>2.999522840061365</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.021312421060484</v>
+        <v>-3.347448453302533</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.293845370550418</v>
+        <v>1.163390957653598</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9031592876555025</v>
+        <v>0.8706059344079867</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.044622335881661</v>
+        <v>3.025090323933151</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.956088239933278</v>
+        <v>-3.282224272175327</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.337122447094006</v>
+        <v>1.206668034197185</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9683834687827081</v>
+        <v>0.9358301155351924</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.100944248650689</v>
+        <v>3.08141223670218</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.918661219862144</v>
+        <v>-3.244797252104193</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.34805422742174</v>
+        <v>1.217599814524919</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9736350068118897</v>
+        <v>0.941081653564374</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.100056143767479</v>
+        <v>3.080524131818969</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.917303234888599</v>
+        <v>-3.243439267130648</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.349854213742398</v>
+        <v>1.219399800845578</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.047973132349708</v>
+        <v>1.015419779102193</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.14591581142141</v>
+        <v>3.1263837994729</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.888889971788715</v>
+        <v>-3.215026004030764</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.521777290003562</v>
+        <v>1.391322877106742</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9889975696032796</v>
+        <v>0.9564442163557638</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.271088244794763</v>
+        <v>3.251556232846254</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.814107710763702</v>
+        <v>-3.140243743005751</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.671803103631385</v>
+        <v>1.541348690734564</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.063779830628292</v>
+        <v>1.031226477380776</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.436070510627588</v>
+        <v>3.416538498679079</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.788023626499895</v>
+        <v>-3.114159658741944</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.673944713350767</v>
+        <v>1.543490300453946</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.063779830628292</v>
+        <v>1.031226477380776</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.427778486641447</v>
+        <v>3.408246474692938</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.700145713390774</v>
+        <v>-3.026281745632823</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.707289074178194</v>
+        <v>1.576834661281374</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.179705473051643</v>
+        <v>1.147152119804128</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.495527067679237</v>
+        <v>3.475995055730728</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.691253251997491</v>
+        <v>-3.01738928423954</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.728400464462299</v>
+        <v>1.597946051565479</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.179705473051643</v>
+        <v>1.147152119804128</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.513081473406029</v>
+        <v>3.49354946145752</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.859729368967369</v>
+        <v>-3.185865401209418</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.652865065078932</v>
+        <v>1.522410652182111</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.151757637335063</v>
+        <v>1.119204284087547</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.488167819380664</v>
+        <v>3.468635807432155</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.413473176337929</v>
+        <v>-2.739609208579978</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.812637239318569</v>
+        <v>1.682182826421749</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.05703896766543</v>
+        <v>1.024485614417914</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.412606314766747</v>
+        <v>3.393074302818237</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.390752072654776</v>
+        <v>-2.716888104896825</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.812389703288735</v>
+        <v>1.681935290391915</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.05703896766543</v>
+        <v>1.024485614417914</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.403270337263651</v>
+        <v>3.383738325315142</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.519953885948819</v>
+        <v>-2.846089918190868</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.919615103822287</v>
+        <v>1.789160690925467</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9278371543713877</v>
+        <v>0.895283801123872</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.484655375138395</v>
+        <v>3.465123363189885</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.545828284422845</v>
+        <v>-2.871964316664894</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.946343166926323</v>
+        <v>1.815888754029503</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9727487630831289</v>
+        <v>0.9401954098356131</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.548680162859086</v>
+        <v>3.529148150910577</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.538773594207671</v>
+        <v>-2.86490962644972</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.945840399001938</v>
+        <v>1.815385986105118</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9798034532983027</v>
+        <v>0.9472501000507869</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.549588332977736</v>
+        <v>3.530056321029226</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.511822369881183</v>
+        <v>-2.837958402123232</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.966627042377275</v>
+        <v>1.836172629480455</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9946837993260218</v>
+        <v>0.9621304460785061</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.568522694239109</v>
+        <v>3.548990682290599</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.53336659771197</v>
+        <v>-2.859502629954019</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.14211248338992</v>
+        <v>2.011658070493099</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9946837993260218</v>
+        <v>0.9621304460785061</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.752625826384068</v>
+        <v>3.733093814435559</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.555774715516842</v>
+        <v>-2.881910747758891</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.125265931170964</v>
+        <v>1.994811518274144</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9946837993260218</v>
+        <v>0.9621304460785061</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.744742521287062</v>
+        <v>3.725210509338552</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.583998951094443</v>
+        <v>-2.910134983336492</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.116030236489562</v>
+        <v>1.985575823592741</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.01266055177733</v>
+        <v>0.9801071985298146</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.757582572307484</v>
+        <v>3.738050560358975</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.641003629543946</v>
+        <v>-2.919575909225022</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.149482082831607</v>
+        <v>2.038053170959176</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.021597706772628</v>
+        <v>1.102534316073206</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.81919858302651</v>
+        <v>3.867760548606856</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.84724256733238</v>
+        <v>-3.125814847013455</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.069877602261534</v>
+        <v>1.958448690389104</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8153587689841941</v>
+        <v>0.8962953782847725</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.698346314898751</v>
+        <v>3.746908280479097</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.923572544933286</v>
+        <v>-3.202144824614361</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.037457424114947</v>
+        <v>1.926028512242516</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8153587689841941</v>
+        <v>0.8962953782847725</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.696458127792526</v>
+        <v>3.745020093372872</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.078529330333415</v>
+        <v>-3.35710161001449</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.970294939557758</v>
+        <v>1.858866027685327</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6604019835840649</v>
+        <v>0.7413385928846432</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.59830428615531</v>
+        <v>3.646866251735657</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.24009775586067</v>
+        <v>-3.518670035541745</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.904101579557008</v>
+        <v>1.792672667684577</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5336190597861855</v>
+        <v>0.6145556690867638</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.520668542086735</v>
+        <v>3.569230507667082</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.34839841773079</v>
+        <v>-3.626970697411865</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.873854721674879</v>
+        <v>1.762425809802448</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5336190597861855</v>
+        <v>0.6145556690867638</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.533741948952653</v>
+        <v>3.582303914533</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.507949490494306</v>
+        <v>-3.786521770175382</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.802039489352412</v>
+        <v>1.690610577479981</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.381341392924434</v>
+        <v>0.4622780022250124</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.434380545618543</v>
+        <v>3.48294251119889</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.535850277603779</v>
+        <v>-3.814422557284855</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.789403215635625</v>
+        <v>1.677974303763194</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3467444687814992</v>
+        <v>0.4276810780820776</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.412146432259784</v>
+        <v>3.460708397840131</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.658376380306673</v>
+        <v>-3.936948659987749</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.737157218531666</v>
+        <v>1.625728306659235</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2242183660786053</v>
+        <v>0.3051549753791837</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.335395214615246</v>
+        <v>3.383957180195593</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.888890876492262</v>
+        <v>-4.167463156173337</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.711657379647934</v>
+        <v>1.600228467775504</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.006296130106983377</v>
+        <v>0.07464047919359496</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.263792476494397</v>
+        <v>3.312354442074743</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.237635961716705</v>
+        <v>-4.516208241397781</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.712471064560004</v>
+        <v>1.601042152687573</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1150440840258812</v>
+        <v>-0.03410747472530284</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.338855423144905</v>
+        <v>3.387417388725252</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.391622379492846</v>
+        <v>-4.670194659173921</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.719856766595188</v>
+        <v>1.608427854722757</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1150440840258812</v>
+        <v>-0.03410747472530284</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.407835692290545</v>
+        <v>3.456397657870892</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.596221814355855</v>
+        <v>-4.87479409403693</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.624068194770105</v>
+        <v>1.512639282897674</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1150440840258812</v>
+        <v>-0.03410747472530284</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.393886894410666</v>
+        <v>3.442448859991013</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.848696968363579</v>
+        <v>-5.127269248044654</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.534948622222429</v>
+        <v>1.423519710349999</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1150440840258812</v>
+        <v>-0.03410747472530284</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.40575738346608</v>
+        <v>3.454319349046427</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.141592724842991</v>
+        <v>-5.420165004524066</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.419000854149608</v>
+        <v>1.307571942277177</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1150440840258812</v>
+        <v>-0.03410747472530284</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.406967917985023</v>
+        <v>3.45552988356537</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.328256852977799</v>
+        <v>-5.606829132658874</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.348456945123006</v>
+        <v>1.237028033250576</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1417830548504411</v>
+        <v>-0.06084644554986274</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.395046277717609</v>
+        <v>3.443608243297956</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.474277539891761</v>
+        <v>-5.752849819572837</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.285126523093611</v>
+        <v>1.17369761122118</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.150866146644298</v>
+        <v>-0.06992953734371971</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.384674275377484</v>
+        <v>3.433236240957831</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.565991549001346</v>
+        <v>-5.844563828682421</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.410644976148821</v>
+        <v>1.29921606427639</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.150866146644298</v>
+        <v>-0.06992953734371971</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.546878332076528</v>
+        <v>3.595440297656875</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.597643208061315</v>
+        <v>-5.876215487742391</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.392830950488647</v>
+        <v>1.281402038616217</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1560346038887382</v>
+        <v>-0.07509799458815991</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.538623895693678</v>
+        <v>3.587185861274025</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.666709262634252</v>
+        <v>-5.945281542315327</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.375433946227964</v>
+        <v>1.264005034355533</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.2184054813823483</v>
+        <v>-0.1374688720817699</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.511430786766003</v>
+        <v>3.55999275234635</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.76868538488266</v>
+        <v>-6.047257664563735</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.343569135784504</v>
+        <v>1.232140223912073</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.3203816036307559</v>
+        <v>-0.2394449943301775</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.459170751872861</v>
+        <v>3.507732717453208</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.658679101405438</v>
+        <v>-5.937251381086513</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.379724536419567</v>
+        <v>1.268295624547137</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2971770317134806</v>
+        <v>-0.2162404224129023</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.465246382267402</v>
+        <v>3.513808347847749</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.671208806517317</v>
+        <v>-5.949781086198392</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.37896266509679</v>
+        <v>1.26753375322436</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3110035311800037</v>
+        <v>-0.2300669218794253</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.461200493309462</v>
+        <v>3.509762458889809</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.369762081045479</v>
+        <v>-5.648334360726555</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.506802238168061</v>
+        <v>1.39537332629563</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.009556805708166416</v>
+        <v>0.07137980359241192</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.6493294114751</v>
+        <v>3.697891377055448</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.394352325280663</v>
+        <v>-5.672924604961739</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.497937318226698</v>
+        <v>1.386508406354268</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.009556805708166416</v>
+        <v>0.07137980359241192</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.650300589227811</v>
+        <v>3.698862554808158</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.343313949274143</v>
+        <v>-5.621886228955218</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.519195573009062</v>
+        <v>1.407766661136631</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.009556805708166416</v>
+        <v>0.07137980359241192</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.651143493607567</v>
+        <v>3.699705459187914</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.314465272450683</v>
+        <v>-5.593037552131758</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.549773142612592</v>
+        <v>1.438344230740161</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.01929187111529385</v>
+        <v>0.1002284804158722</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.687490798575789</v>
+        <v>3.736052764156136</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.217830360432043</v>
+        <v>-5.496402640113118</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.404611103543982</v>
+        <v>1.293182191671551</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1159267831339338</v>
+        <v>0.1968633924345121</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.561655741910907</v>
+        <v>3.610217707491254</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.148792349483575</v>
+        <v>-5.42736462916465</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.435728351997333</v>
+        <v>1.324299440124903</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1849647940824019</v>
+        <v>0.2659014033829802</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.606580592553952</v>
+        <v>3.655142558134299</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.130005249114636</v>
+        <v>-5.408577528795711</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.427670011220991</v>
+        <v>1.316241099348561</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2037518944513403</v>
+        <v>0.2846885037519187</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.602279671851397</v>
+        <v>3.650841637431745</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.052906647572764</v>
+        <v>-5.331478927253839</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.45769716227417</v>
+        <v>1.346268250401739</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2037518944513403</v>
+        <v>0.2846885037519187</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.601467382287827</v>
+        <v>3.650029347868174</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.063291842462653</v>
+        <v>-5.341864122143728</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.463411863443287</v>
+        <v>1.351982951570856</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.193366699561451</v>
+        <v>0.2743033088620294</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.605105044478966</v>
+        <v>3.653667010059313</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.081880001184878</v>
+        <v>-5.360452280865953</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.526813605730822</v>
+        <v>1.415384693858391</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1747785408392257</v>
+        <v>0.255715150139804</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.664789155022056</v>
+        <v>3.713351120602403</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.082178547880914</v>
+        <v>-5.360750827561989</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.523563197870706</v>
+        <v>1.412134285998275</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1744799941431898</v>
+        <v>0.2554166034437681</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.661479037822733</v>
+        <v>3.71004100340308</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.981355414190486</v>
+        <v>-5.259927693871561</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.568423346286269</v>
+        <v>1.456994434413838</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.1869442096275436</v>
+        <v>0.2678808189281219</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.673488462052737</v>
+        <v>3.722050427633084</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.790574053438078</v>
+        <v>-5.069146333119154</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.644865144065775</v>
+        <v>1.533436232193344</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.377725570379951</v>
+        <v>0.4586621796805293</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.788086531982724</v>
+        <v>3.836648497563071</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.683610695588657</v>
+        <v>-4.962182975269732</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.66748733294314</v>
+        <v>1.556058421070709</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4361901783397524</v>
+        <v>0.5171267876403307</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.803002142496202</v>
+        <v>3.851564108076549</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.628280107686894</v>
+        <v>-4.906852387367969</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.724586504715904</v>
+        <v>1.613157592843473</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4915207662415146</v>
+        <v>0.5724573755420929</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.871167431849317</v>
+        <v>3.919729397429665</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.616225980773931</v>
+        <v>-4.894798260455007</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.723094723382526</v>
+        <v>1.611665811510096</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5035748931544775</v>
+        <v>0.5845115024550557</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.872086475898533</v>
+        <v>3.92064844147888</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.693581470901901</v>
+        <v>-4.972153750582976</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.694033157515475</v>
+        <v>1.582604245643044</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4262194030265081</v>
+        <v>0.5071560123270863</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.827553812005887</v>
+        <v>3.876115777586234</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.625532908210371</v>
+        <v>-4.904105187891446</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.734103608469969</v>
+        <v>1.622674696597538</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4942679657180379</v>
+        <v>0.5752045750186161</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.881233975498688</v>
+        <v>3.929795941079035</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.857133301379871</v>
+        <v>-5.135705581060947</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.661666121375763</v>
+        <v>1.550237209503332</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4942679657180379</v>
+        <v>0.5752045750186161</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.901436645672282</v>
+        <v>3.949998611252629</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.907184846909091</v>
+        <v>-5.185757126590167</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.625251739230957</v>
+        <v>1.513822827358526</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4942679657180379</v>
+        <v>0.5752045750186161</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.885042881739164</v>
+        <v>3.93360484731951</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.082291679485536</v>
+        <v>-5.360863959166611</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.515460919793846</v>
+        <v>1.404032007921415</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4942679657180379</v>
+        <v>0.5752045750186161</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.84529479533263</v>
+        <v>3.893856760912977</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.886191526055013</v>
+        <v>-5.164763805736088</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.600923600162995</v>
+        <v>1.489494688290564</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6903681191485608</v>
+        <v>0.771304728449139</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.969977506387885</v>
+        <v>4.018539471968231</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.733166133941729</v>
+        <v>-5.011738413622804</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.761304756581213</v>
+        <v>1.649875844708782</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8433935112618449</v>
+        <v>0.9243301205624231</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.160963741228759</v>
+        <v>4.209525706809107</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.761473447814999</v>
+        <v>-5.040045727496074</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.937448055940198</v>
+        <v>1.826019144067767</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8433935112618449</v>
+        <v>0.9243301205624231</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.348429966137052</v>
+        <v>4.396991931717398</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.928066672928521</v>
+        <v>-5.206638952609596</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.840213717248872</v>
+        <v>1.728784805376441</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6768002861483224</v>
+        <v>0.7577368954489008</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.217876982423021</v>
+        <v>4.266438948003368</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.905030879566955</v>
+        <v>-5.183603159248031</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.853104437255216</v>
+        <v>1.741675525382785</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6768002861483224</v>
+        <v>0.7577368954489008</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.221553385084738</v>
+        <v>4.270115350665086</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.875784899111259</v>
+        <v>-5.154357178792334</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.86242088456099</v>
+        <v>1.750991972688559</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6768002861483224</v>
+        <v>0.7577368954489008</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.219171440208234</v>
+        <v>4.267733405788581</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.98271044698911</v>
+        <v>-5.261282726670185</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.816943904567484</v>
+        <v>1.705514992695053</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.5698747382704711</v>
+        <v>0.6508113475710494</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.152309350639158</v>
+        <v>4.200871316219505</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.127729005496358</v>
+        <v>-5.406301285177434</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.760365283307819</v>
+        <v>1.648936371435388</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4248561797632225</v>
+        <v>0.5057927890638009</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.066727017678043</v>
+        <v>4.11528898325839</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.246070771281076</v>
+        <v>-5.524643050962151</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.812959816251685</v>
+        <v>1.701530904379254</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.4355422183261126</v>
+        <v>0.516478827626691</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.17306988007353</v>
+        <v>4.221631845653877</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.297481193601784</v>
+        <v>-5.576053473282859</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.790181344449341</v>
+        <v>1.67875243257691</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.4355422183261126</v>
+        <v>0.516478827626691</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.170855577199469</v>
+        <v>4.219417542779817</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.376900644809536</v>
+        <v>-5.655472924490611</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.758316692040529</v>
+        <v>1.646887780168099</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.4355422183261126</v>
+        <v>0.516478827626691</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.170758705273759</v>
+        <v>4.219320670854105</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.472363642726753</v>
+        <v>-5.750935922407828</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.720125386431685</v>
+        <v>1.608696474559254</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.4355422183261126</v>
+        <v>0.516478827626691</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.170752598831801</v>
+        <v>4.219314564412149</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.407987731876038</v>
+        <v>-5.686560011557114</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.743972147334582</v>
+        <v>1.632543235462151</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.4999181291768278</v>
+        <v>0.5808547384774061</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.207474541904841</v>
+        <v>4.256036507485188</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.463356894008232</v>
+        <v>-5.741929173689307</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.727558300229431</v>
+        <v>1.616129388357</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.4999181291768278</v>
+        <v>0.5808547384774061</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.213208359652568</v>
+        <v>4.261770325232915</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.481575361005841</v>
+        <v>-5.760147640686916</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.71980927677332</v>
+        <v>1.608380364900889</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4748116919209856</v>
+        <v>0.5557483012215639</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.197682860641995</v>
+        <v>4.246244826222342</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.44289192566191</v>
+        <v>-5.721464205342985</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.755157043761211</v>
+        <v>1.64372813188878</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4748116919209856</v>
+        <v>0.5557483012215639</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.217557253492314</v>
+        <v>4.26611921907266</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.336856930456601</v>
+        <v>-5.615429210137676</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.781271742368062</v>
+        <v>1.669842830495631</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4748116919209856</v>
+        <v>0.5557483012215639</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.201257954017041</v>
+        <v>4.249819919597389</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.153645267323506</v>
+        <v>-5.432217547004581</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.856987357085346</v>
+        <v>1.745558445212915</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4748116919209856</v>
+        <v>0.5557483012215639</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.203688903481087</v>
+        <v>4.252250869061434</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.081923820309655</v>
+        <v>-5.36049609999073</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.868620341970263</v>
+        <v>1.757191430097833</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5465331389348362</v>
+        <v>0.6274697482354146</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.229666177768775</v>
+        <v>4.278228143349121</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.059550794701948</v>
+        <v>-5.338123074383024</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.824485298134518</v>
+        <v>1.713056386262087</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5577888900477378</v>
+        <v>0.6387254993483161</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.183335374357687</v>
+        <v>4.231897339938034</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.092567090612693</v>
+        <v>-5.371139370293768</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.996476984655575</v>
+        <v>1.885048072783144</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.4883515133809862</v>
+        <v>0.5692881226815645</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.326871153242991</v>
+        <v>4.375433118823339</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.081039454963085</v>
+        <v>-5.35961173464416</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.993009264743668</v>
+        <v>1.881580352871237</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.5473521715823486</v>
+        <v>0.6282887808829269</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.354192773992058</v>
+        <v>4.402754739572405</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.178380956305453</v>
+        <v>-5.456953235986528</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.957740776728509</v>
+        <v>1.846311864856078</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5029319894168602</v>
+        <v>0.5838685987174386</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.331208777214553</v>
+        <v>4.379770742794901</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.26423698564542</v>
+        <v>-5.542809265326495</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.92464944718536</v>
+        <v>1.813220535312929</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.4605559201907252</v>
+        <v>0.5414925294913036</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.307034217871711</v>
+        <v>4.355596183452058</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.273073783061539</v>
+        <v>-5.551646062742615</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.903533930039414</v>
+        <v>1.792105018166983</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.4531137475493744</v>
+        <v>0.5340503568499528</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.284988116107402</v>
+        <v>4.333550081687749</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.364456345626998</v>
+        <v>-5.643028625308073</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.87714541605828</v>
+        <v>1.765716504185849</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.4165488628300298</v>
+        <v>0.4974854721306081</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.273213696320845</v>
+        <v>4.321775661901192</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.352749627639992</v>
+        <v>-5.631321907321067</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.983956361077351</v>
+        <v>1.87252744920492</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.4282555808170362</v>
+        <v>0.5091921901176145</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.382365984937317</v>
+        <v>4.430927950517664</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.423661701382269</v>
+        <v>-5.702233981063344</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.958623870311845</v>
+        <v>1.847194958439414</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.4282555808170362</v>
+        <v>0.5091921901176145</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.385398323668722</v>
+        <v>4.433960289249069</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.433977799548621</v>
+        <v>-5.712550079229696</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.167402264323362</v>
+        <v>2.055973352450931</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.4282555808170362</v>
+        <v>0.5091921901176145</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.59830315694678</v>
+        <v>4.646865122527127</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.433883831531248</v>
+        <v>-5.712456111212323</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.166618518442401</v>
+        <v>2.05518960656997</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.4286254421643542</v>
+        <v>0.5095620514649325</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.59770374066726</v>
+        <v>4.646265706247608</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.577484995554634</v>
+        <v>-5.856057275235709</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.103410038777401</v>
+        <v>1.99198112690497</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.4286254421643542</v>
+        <v>0.5095620514649325</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.591935726611614</v>
+        <v>4.640497692191961</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.576536572436595</v>
+        <v>-5.85510885211767</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.103789408024616</v>
+        <v>1.992360496152185</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.4286254421643542</v>
+        <v>0.5095620514649325</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.591935726611614</v>
+        <v>4.640497692191961</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.676806390395615</v>
+        <v>-5.955378670076691</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.0764090888221</v>
+        <v>1.964980176949669</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.4286254421643542</v>
+        <v>0.5095620514649325</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.604663334592706</v>
+        <v>4.653225300173053</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.670814143606804</v>
+        <v>-5.949386423287879</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.080751985962012</v>
+        <v>1.969323074089581</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.4286254421643542</v>
+        <v>0.5095620514649325</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.606609333017094</v>
+        <v>4.655171298597441</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.582256182476036</v>
+        <v>-5.860828462157111</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.109829306432088</v>
+        <v>1.998400394559658</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.4286254421643542</v>
+        <v>0.5095620514649325</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.600263469034862</v>
+        <v>4.64882543461521</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.564497104972962</v>
+        <v>-5.843069384654037</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.116241614872314</v>
+        <v>2.004812702999883</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.4286254421643542</v>
+        <v>0.5095620514649325</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.599572146473858</v>
+        <v>4.648134112054206</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.464866953923894</v>
+        <v>-5.74343923360497</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.168875861200527</v>
+        <v>2.057446949328097</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.5282555932134216</v>
+        <v>0.609192202514</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.672132423011885</v>
+        <v>4.720694388592233</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.514266462612905</v>
+        <v>-5.792838742293981</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.338270323223649</v>
+        <v>2.226841411351219</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.5385144266451664</v>
+        <v>0.6194510359457447</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.867441988569658</v>
+        <v>4.916003954150006</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.307581988970529</v>
+        <v>-5.586154268651605</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.408132785783462</v>
+        <v>2.296703873911031</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.745198900287542</v>
+        <v>0.8261355095881203</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.978641345857946</v>
+        <v>5.027203311438293</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.341738883968056</v>
+        <v>-5.620311163649131</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.396471541438556</v>
+        <v>2.285042629566126</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.6616151307467295</v>
+        <v>0.7425517400473078</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.930492597787564</v>
+        <v>4.979054563367911</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.249149404906599</v>
+        <v>-5.527721684587674</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.787004447052806</v>
+        <v>2.675575535180375</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.6616151307467295</v>
+        <v>0.7425517400473078</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.283989711777231</v>
+        <v>5.332551677357579</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.322310008679744</v>
+        <v>-5.600882288360819</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.762303317110652</v>
+        <v>2.650874405238221</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.6335939307124865</v>
+        <v>0.7145305400130648</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.271740103323789</v>
+        <v>5.320302068904136</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.270093698883402</v>
+        <v>-5.548665978564477</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.833019782352716</v>
+        <v>2.721590870480285</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.6335939307124865</v>
+        <v>0.7145305400130648</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.321570044647316</v>
+        <v>5.370132010227663</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.238196181798156</v>
+        <v>-5.516768461479232</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.854592759396825</v>
+        <v>2.743163847524394</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.6654914477977323</v>
+        <v>0.7464280570983106</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.349522525108474</v>
+        <v>5.398084490688822</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.252951505998297</v>
+        <v>-5.531523785679372</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.844328213755966</v>
+        <v>2.732899301883535</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.6654914477977323</v>
+        <v>0.7464280570983106</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.345160109147671</v>
+        <v>5.393722074728018</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.203486882628385</v>
+        <v>-5.482059162309461</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.85503856652021</v>
+        <v>2.743609654647779</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.7149560711676439</v>
+        <v>0.7958926804682223</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.365763386585899</v>
+        <v>5.414325352166245</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.04037889047477</v>
+        <v>-5.318951170155845</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.916689431096591</v>
+        <v>2.80526051922416</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.8780640633212592</v>
+        <v>0.9590006726218375</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.460035849593002</v>
+        <v>5.508597815173349</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.019735799673542</v>
+        <v>-5.298308079354618</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.93399370410821</v>
+        <v>2.822564792235779</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.8780640633212592</v>
+        <v>0.9590006726218375</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.46908288628413</v>
+        <v>5.517644851864477</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.0824437161481</v>
+        <v>-5.361015995829176</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.909768002504508</v>
+        <v>2.798339090632078</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.8153561468467014</v>
+        <v>0.8962927561472798</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.432315601385517</v>
+        <v>5.480877566965864</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.034435592304408</v>
+        <v>-5.27532836933506</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.891880668832338</v>
+        <v>2.795523558020076</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.8153561468467014</v>
+        <v>0.8962927561472798</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.39522501817587</v>
+        <v>5.443786983756216</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.955609935120817</v>
+        <v>-5.19650271215147</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.927343185263724</v>
+        <v>2.830986074451463</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.8941818040302919</v>
+        <v>0.9751184133308702</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.446452666043974</v>
+        <v>5.495014631624321</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.763675133866943</v>
+        <v>-5.004567910897596</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.999016198372311</v>
+        <v>2.902659087560049</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.8941818040302919</v>
+        <v>0.9751184133308702</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.441351758651011</v>
+        <v>5.489913724231358</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.645501755849017</v>
+        <v>-4.886394532879669</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.041639458968577</v>
+        <v>2.945282348156315</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.012355182048219</v>
+        <v>1.093291791348797</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.507609694850863</v>
+        <v>5.556171660431209</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.532087073066285</v>
+        <v>-4.772979850096937</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.116093924944696</v>
+        <v>3.019736814132435</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.12576986483095</v>
+        <v>1.206706474131529</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.604747097383528</v>
+        <v>5.653309062963875</v>
       </c>
     </row>
     <row r="2104">
@@ -49943,16 +49943,16 @@
         <v>4.922845401496135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.505038035373031</v>
+        <v>-4.745930812403683</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.120473763033175</v>
+        <v>3.024116652220913</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.152818902524204</v>
+        <v>1.233755511824782</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.614536743010658</v>
+        <v>5.663098708591004</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263773</v>
+        <v>3.823987445263771</v>
       </c>
       <c r="C2105" t="n">
         <v>4.922845401496135</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.511071315559802</v>
+        <v>-4.751964092590454</v>
       </c>
       <c r="E2105" t="n">
-        <v>3.118060450958467</v>
+        <v>3.021703340146205</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.152818902524204</v>
+        <v>1.233755511824782</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.614536743010658</v>
+        <v>5.663098708591004</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.868826538066061</v>
+        <v>3.502369099565479</v>
       </c>
       <c r="C2106" t="n">
-        <v>5.048877733623272</v>
+        <v>4.85641790664968</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.511071315559802</v>
+        <v>-4.751964092590454</v>
       </c>
       <c r="E2106" t="n">
-        <v>3.118060450958467</v>
+        <v>3.021703340146205</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.152818902524204</v>
+        <v>1.233755511824782</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.041941530609639</v>
+        <v>4.849481703636048</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241003.xlsx
+++ b/tame_output/ON/bt/strategyON_20241003.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>58.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>111.1%</t>
+          <t>113.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>174.0%</t>
+          <t>181.0%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>417.6%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-636.8%</t>
+          <t>-614.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-64.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-300.2%</t>
+          <t>-287.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-100.6%</t>
+          <t>-74.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>130.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,57 +1456,57 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>118.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>136.1%</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-9.057688270276868</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.4446875423097185</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.570948920052083</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.236174838083527</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.933109613939276</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.3937169352186229</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.570948920052083</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.237313982639586</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.908072932370766</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.3810684884291113</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.545619832501347</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.255145209332135</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.835939757082885</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.3464815140753221</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.545619832501347</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.260878913570772</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.644238203941597</v>
+        <v>-8.832736096657079</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2795381552126726</v>
+        <v>-0.354937312298865</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.542416172075541</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.263664188750818</v>
+        <v>2.253063847432391</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.550779169956373</v>
+        <v>-8.739277062671855</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2520380229314902</v>
+        <v>-0.3274371800176827</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.542416172075541</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.25378070743791</v>
+        <v>2.243180366119483</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.540125988402941</v>
+        <v>-8.728623881118423</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2496113108094913</v>
+        <v>-0.3250104678956842</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.542416172075541</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.251946146938536</v>
+        <v>2.241345805620109</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.442218949726451</v>
+        <v>-8.630716842441933</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.210748810312356</v>
+        <v>-0.2861479673985485</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.456763186684273</v>
+        <v>-1.474430422214985</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.292437281881409</v>
+        <v>2.281836940562982</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.418265408750493</v>
+        <v>-8.606763301465975</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2004988877764791</v>
+        <v>-0.275898044862672</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.432809645708315</v>
+        <v>-1.450476881239027</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.307477912612478</v>
+        <v>2.29687757129405</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.154205470427696</v>
+        <v>-8.342703363143178</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1081352286091124</v>
+        <v>-0.1835343856953053</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.186416942916231</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.452653559444403</v>
+        <v>2.442053218125976</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.447125846922858</v>
+        <v>-7.63562373963834</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.171909587132522</v>
+        <v>0.09651043004632909</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.186416942916231</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.449866525784102</v>
+        <v>2.439266184465675</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.406941548556667</v>
+        <v>-7.595439441272149</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1883269303668396</v>
+        <v>0.1129277732806466</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.128565409019328</v>
+        <v>-1.14623264455004</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.474320728691658</v>
+        <v>2.463720387373231</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.243541677617305</v>
+        <v>-7.432039570332787</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2530536999633415</v>
+        <v>0.1776545428771485</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9651655380799653</v>
+        <v>-0.9828327736106774</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.571727472476033</v>
+        <v>2.561127131157605</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.08542429823853</v>
+        <v>-7.273922190954011</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3242250805527038</v>
+        <v>0.2488259234665113</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8070481587011898</v>
+        <v>-0.824715394231902</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.67452232894115</v>
+        <v>2.663921987622723</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.935757907231014</v>
+        <v>-7.124255799946496</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.381199426642751</v>
+        <v>0.305800269556558</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7141446674586539</v>
+        <v>-0.731811902989366</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.727372213373712</v>
+        <v>2.716771872055285</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.803482433600128</v>
+        <v>-6.99198032631561</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3353704021022601</v>
+        <v>0.2599712450160672</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5818691938277673</v>
+        <v>-0.5995364293584794</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.707998283559399</v>
+        <v>2.697397942240972</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.631621218035225</v>
+        <v>-6.820119110750707</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4069299490158578</v>
+        <v>0.3315307919296648</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4100079782628644</v>
+        <v>-0.4276752137935765</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.813930073585978</v>
+        <v>2.80332973226755</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.546656551305906</v>
+        <v>-6.735154444021388</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4538221569312442</v>
+        <v>0.3784229998450512</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3250433115335448</v>
+        <v>-0.342710547064257</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.877815214847228</v>
+        <v>2.867214873528801</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.652246541079011</v>
+        <v>-6.840744433794493</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2836102314227835</v>
+        <v>0.208211074336591</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4306333013066492</v>
+        <v>-0.4483005368373613</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.686485291384147</v>
+        <v>2.675884950065719</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.584011956453583</v>
+        <v>-6.772509849169065</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3594484071500412</v>
+        <v>0.2840492500638483</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4122179784341132</v>
+        <v>-0.4298852139648253</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.746078826984755</v>
+        <v>2.735478485666328</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.436071915045984</v>
+        <v>-6.624569807761466</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3020036150746739</v>
+        <v>0.2266044579884809</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3918970625255556</v>
+        <v>-0.4095642980562678</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.641650567891482</v>
+        <v>2.631050226573055</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.383102392791995</v>
+        <v>-6.571600285507477</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.314477437722791</v>
+        <v>0.2390782806365981</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3565947758022789</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.664718294990398</v>
+        <v>2.65411795367197</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.217314196831705</v>
+        <v>-6.405812089547187</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.373832104011814</v>
+        <v>0.2984329469256215</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3565947758022789</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.657757682895304</v>
+        <v>2.647157341576877</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.183950990352936</v>
+        <v>-6.372448883068418</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4016397409844648</v>
+        <v>0.3262405838982718</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3565947758022789</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.672220037276448</v>
+        <v>2.66161969595802</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.075691853230414</v>
+        <v>-6.264189745945896</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4394755162926685</v>
+        <v>0.3640763592064755</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3565947758022789</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.666752157735643</v>
+        <v>2.656151816417215</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.952400718413283</v>
+        <v>-6.140898611128765</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4862900642300976</v>
+        <v>0.4108909071439046</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2156364054544362</v>
+        <v>-0.2333036409851484</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.738224932636498</v>
+        <v>2.72762459131807</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.899703851281992</v>
+        <v>-6.088201743997474</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5150697893199392</v>
+        <v>0.4396706322337467</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.1806067738538572</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.777544031152598</v>
+        <v>2.76694368983417</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.655938409298548</v>
+        <v>-5.84443630201403</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6083566744603677</v>
+        <v>0.5329575173741752</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.1806067738538572</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.773324739499648</v>
+        <v>2.762724398181221</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.566162736922076</v>
+        <v>-5.754660629637558</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6463912573309725</v>
+        <v>0.57099210024478</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.1190073289395472</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.81240872036825</v>
+        <v>2.801808379049823</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.42632435466748</v>
+        <v>-5.504810235688483</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6950686852165129</v>
+        <v>0.6636743328081121</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.1190073289395472</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.805150795351952</v>
+        <v>2.794550454033525</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.250432262200048</v>
+        <v>-5.328918143221051</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7690246457241345</v>
+        <v>0.7376302933157333</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.1190073289395472</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.808749918872601</v>
+        <v>2.798149577554174</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.078985799177585</v>
+        <v>-5.157471680198587</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8509307369876735</v>
+        <v>0.8195363845792727</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.07010636961362809</v>
+        <v>0.05243913408291595</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.924945302740633</v>
+        <v>2.914344961422205</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.998963512068464</v>
+        <v>-5.077449393089466</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8819601294476189</v>
+        <v>0.8505657770392179</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1501286567227491</v>
+        <v>0.1324614211920369</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.971979152622402</v>
+        <v>2.961378811303975</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.935327769834529</v>
+        <v>-5.013813650855532</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.91210922739551</v>
+        <v>0.8807148749871088</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.1960971634259714</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.01485539901708</v>
+        <v>3.004255057698653</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.841630451618134</v>
+        <v>-4.920116332639137</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9307824134658635</v>
+        <v>0.8993880610574627</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.1960971634259714</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.996049657800876</v>
+        <v>2.985449316482448</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.852133074683423</v>
+        <v>-4.930618955704426</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9283244408646254</v>
+        <v>0.8969300884562244</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.1855945403606826</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.99149116058658</v>
+        <v>2.980890819268152</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.739646814014549</v>
+        <v>-4.818132695035551</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9772482589669955</v>
+        <v>0.9458539065585945</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.1855945403606826</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.9954204744214</v>
+        <v>2.984820133102973</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.721933127136683</v>
+        <v>-4.800419008157686</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9850123176354817</v>
+        <v>0.9536179652270806</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.1887758692575994</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.99800785567689</v>
+        <v>2.987407514358463</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.598458855823665</v>
+        <v>-4.676944736844668</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.031400097380682</v>
+        <v>1.000005744972281</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.1887758692575994</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.995005926896884</v>
+        <v>2.984405585578456</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.540523023825449</v>
+        <v>-4.619008904846452</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.056153467190583</v>
+        <v>1.024759114782182</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2143377439403487</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.011922088717147</v>
+        <v>3.00132174739872</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.407655334762172</v>
+        <v>-4.486141215783174</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.125194725617717</v>
+        <v>1.093800373209316</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.2143377439403487</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.02781627151897</v>
+        <v>3.017215930200543</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.287482251397673</v>
+        <v>-4.365968132418676</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.174409803403818</v>
+        <v>1.143015450995418</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3521780628355597</v>
+        <v>0.3345108273048476</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.101065965977972</v>
+        <v>3.090465624659545</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.152228890067696</v>
+        <v>-4.230714771088699</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.238599250497249</v>
+        <v>1.207204898088848</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4874314241655369</v>
+        <v>0.4697641886348247</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.192306085337398</v>
+        <v>3.181705744018971</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.212103717425388</v>
+        <v>-4.290589598446391</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.200686810955598</v>
+        <v>1.169292458547197</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4098893612771326</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.142418680324209</v>
+        <v>3.131818339005781</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.092283486514551</v>
+        <v>-4.170769367535554</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.263904072554142</v>
+        <v>1.23250972014574</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.4098893612771326</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.157707849558417</v>
+        <v>3.14710750823999</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.094753192976357</v>
+        <v>-4.17323907399736</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.170560389291861</v>
+        <v>1.13916603688346</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4250868903460386</v>
+        <v>0.4074196548153264</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.063870225003775</v>
+        <v>3.053269883685348</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.163123379300368</v>
+        <v>-4.24160926032137</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.062474176247558</v>
+        <v>1.031079823839157</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4166953538515414</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.988697505910805</v>
+        <v>2.978097164592378</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.274995658926518</v>
+        <v>-4.353481539947521</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.008161973028989</v>
+        <v>0.976767620620588</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4166953538515414</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.979134214542697</v>
+        <v>2.968533873224269</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.259020993440251</v>
+        <v>-4.337506874461253</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9811263641475234</v>
+        <v>0.9497320117391224</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4166953538515414</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.945708739466724</v>
+        <v>2.935108398148297</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.083546733647781</v>
+        <v>-4.162032614668783</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.055883300056299</v>
+        <v>1.024488947647898</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4166953538515414</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.950275971458512</v>
+        <v>2.939675630140084</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.075622359062867</v>
+        <v>-4.154108240083869</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.034795078651472</v>
+        <v>1.003400726243071</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.4166953538515414</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.926018000219719</v>
+        <v>2.915417658901291</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.069344156493018</v>
+        <v>-4.14783003751402</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9658446730808612</v>
+        <v>0.9344503206724601</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4229735564213905</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.858323235163078</v>
+        <v>2.847722893844651</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.009491537289295</v>
+        <v>-4.087977418310297</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9999581071944827</v>
+        <v>0.9685637547860817</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4229735564213905</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.86849562159521</v>
+        <v>2.857895280276783</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.923248074262917</v>
+        <v>-4.001733955283919</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.029401762978894</v>
+        <v>0.9980074105704932</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.4229735564213905</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.863441892169071</v>
+        <v>2.852841550850644</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.968554893661897</v>
+        <v>-4.047040774682899</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.003054810663828</v>
+        <v>0.9716604582554269</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.3821633934121597</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.830731569808058</v>
+        <v>2.820131228489631</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.997587998364198</v>
+        <v>-4.0760738793852</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9919934418160088</v>
+        <v>0.960599089407608</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.3821633934121597</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.831283442841159</v>
+        <v>2.820683101522732</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.904777516913339</v>
+        <v>-3.983263397934341</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.958390326287718</v>
+        <v>0.9269959738793172</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4926411103937312</v>
+        <v>0.474973874863019</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.816242423603041</v>
+        <v>2.805642082284614</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.949166986242767</v>
+        <v>-4.027652867263769</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.942508014480548</v>
+        <v>0.9111136620721469</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4482516410643035</v>
+        <v>0.4305844055335913</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.791482217929985</v>
+        <v>2.780881876611558</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.928663292357269</v>
+        <v>-4.007149173378272</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9457852005464698</v>
+        <v>0.9143908481380687</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.4510880994190887</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.798860142773006</v>
+        <v>2.788259801454579</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.012335389069602</v>
+        <v>-4.090821270090604</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9178076576922041</v>
+        <v>0.886413305283803</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.4510880994190887</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.804351438603673</v>
+        <v>2.793751097285246</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.040115786970954</v>
+        <v>-4.118601667991957</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9181927003002022</v>
+        <v>0.8867983478918011</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4409749370484478</v>
+        <v>0.4233077015177356</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.799180401631401</v>
+        <v>2.788580060312973</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.158496459701093</v>
+        <v>-4.236982340722095</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7091961512088001</v>
+        <v>0.677801798800399</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.3560898493667594</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.597205410341468</v>
+        <v>2.586605069023041</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.267110538144424</v>
+        <v>-4.345596419165426</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7859001805506731</v>
+        <v>0.7545058281422721</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.3560898493667594</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.717355071060674</v>
+        <v>2.706754729742247</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.231701499896281</v>
+        <v>-4.310187380917283</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8145768219522533</v>
+        <v>0.7831824695438523</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.3560898493667594</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.731868097162997</v>
+        <v>2.72126775584457</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.240162668551742</v>
+        <v>-4.318648549572744</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8086117958324377</v>
+        <v>0.7772174434240366</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.3476286807112984</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.724210837312089</v>
+        <v>2.713610495993662</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.063046338516576</v>
+        <v>-4.141532219537578</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8761873566918066</v>
+        <v>0.8447930042834055</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.3476286807112984</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.720939866157391</v>
+        <v>2.710339524838964</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.108138583350121</v>
+        <v>-4.186624464371124</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8588338505203013</v>
+        <v>0.8274394981119002</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3033998730726207</v>
+        <v>0.2857326375419086</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.684485632017671</v>
+        <v>2.673885290699243</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.928763162111354</v>
+        <v>-4.007249043132356</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9243709943222227</v>
+        <v>0.8929766419138216</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4601766312433394</v>
+        <v>0.4425093957126273</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.772338662226516</v>
+        <v>2.761738320908089</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.97377737563196</v>
+        <v>-4.052263256652962</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.88717276424557</v>
+        <v>0.8557784118371692</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4298277359287348</v>
+        <v>0.4121605003980227</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.734936780369343</v>
+        <v>2.724336439050916</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.061788562190657</v>
+        <v>-4.140274443211659</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.857659851961037</v>
+        <v>0.826265499552636</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3643512280695618</v>
+        <v>0.3466839925388497</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.701342437992785</v>
+        <v>2.690742096674358</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.162986343627829</v>
+        <v>-4.241472224648832</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8163846612826693</v>
+        <v>0.7849903088742685</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.2782751789935305</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.659501071762095</v>
+        <v>2.648900730443668</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.156475377013517</v>
+        <v>-4.234961258034519</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8165890094827111</v>
+        <v>0.7851946570743102</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.2782751789935305</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.657101033316412</v>
+        <v>2.646500691997984</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.137437249306219</v>
+        <v>-4.215923130327222</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.820728979773875</v>
+        <v>0.789334627365474</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.220091567662336</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.61871558572594</v>
+        <v>2.608115244407513</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.18995305158104</v>
+        <v>-4.268438932602042</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9190170604981371</v>
+        <v>0.8876227080897361</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.220091567662336</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.73800998736013</v>
+        <v>2.727409646041703</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.209919126130583</v>
+        <v>-4.271847244036622</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9118639596644535</v>
+        <v>0.8870927125020378</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2424521980219776</v>
+        <v>0.2526081366717133</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.741659353243621</v>
+        <v>2.747752916433463</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.190562990236735</v>
+        <v>-4.252491108142775</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9256149444189186</v>
+        <v>0.9008436972565028</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2424521980219776</v>
+        <v>0.2526081366717133</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.747667883640547</v>
+        <v>2.753761446830389</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.263892518974828</v>
+        <v>-4.325820636880867</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.794233354200881</v>
+        <v>0.7694621070384651</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2428468604415995</v>
+        <v>0.2530027990913353</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.64585490236952</v>
+        <v>2.651948465559362</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.347713740249526</v>
+        <v>-4.409641858155566</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7634984872224826</v>
+        <v>0.7387272400600668</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2428468604415995</v>
+        <v>0.2530027990913353</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.648648523901001</v>
+        <v>2.654742087090843</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.341561034196742</v>
+        <v>-4.403489152102781</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7666219180352547</v>
+        <v>0.741850670872839</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2489995664943838</v>
+        <v>0.2591555051441196</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.65300249592433</v>
+        <v>2.659096059114171</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.358370332347244</v>
+        <v>-4.420298450253283</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7589786755151642</v>
+        <v>0.7342074283527484</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2321902683438822</v>
+        <v>0.2423462069936179</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.641997393774139</v>
+        <v>2.648090956963981</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.296072333571122</v>
+        <v>-4.358000451477161</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.850233428822434</v>
+        <v>0.8254621816600181</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2774845326183242</v>
+        <v>0.28764047126806</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.735509506135625</v>
+        <v>2.741603069325467</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.094282135905964</v>
+        <v>-4.156210253812003</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7332415096026241</v>
+        <v>0.7084702624402084</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4755027247874786</v>
+        <v>0.4856586634372144</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.656612423151245</v>
+        <v>2.662705986341086</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.145168848592158</v>
+        <v>-4.207096966498198</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7831770568503216</v>
+        <v>0.7584058096879058</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4246160121012841</v>
+        <v>0.4347719507510198</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.696370627861703</v>
+        <v>2.702464191051545</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.058558105942351</v>
+        <v>-4.120486223848391</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.832449090026288</v>
+        <v>0.807677842863872</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5032417433064423</v>
+        <v>0.5133976819561781</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.758173802700842</v>
+        <v>2.764267365890684</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.118767403947636</v>
+        <v>-4.180695521853676</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8069013516488457</v>
+        <v>0.7821301044864297</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4430324453011578</v>
+        <v>0.4531883839508936</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.720584204722343</v>
+        <v>2.726677767912185</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.069580755263285</v>
+        <v>-4.131508873169325</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8250676291625147</v>
+        <v>0.800296382000099</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4430324453011578</v>
+        <v>0.4531883839508936</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.719075822762272</v>
+        <v>2.725169385952113</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.025207623624716</v>
+        <v>-4.087135741530756</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8426797492533784</v>
+        <v>0.8179085020909627</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4874055769397264</v>
+        <v>0.4975615155894622</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.745562569180849</v>
+        <v>2.751656132370691</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.990476302306215</v>
+        <v>-4.052404420212255</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8509660719193692</v>
+        <v>0.8261948247569533</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4874055769397264</v>
+        <v>0.4975615155894622</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.73995636331944</v>
+        <v>2.746049926509281</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.94282057174516</v>
+        <v>-4.004748689651199</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8764101211715962</v>
+        <v>0.8516388740091803</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5350613075007821</v>
+        <v>0.5452172461505178</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.774931558683877</v>
+        <v>2.781025121873719</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.842302413246405</v>
+        <v>-3.904230531152445</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9215097579458229</v>
+        <v>0.8967385107834069</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6355794659995366</v>
+        <v>0.6457354046492724</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.840134827157855</v>
+        <v>2.846228390347696</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.826397083814053</v>
+        <v>-3.888325201720092</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9146265621946361</v>
+        <v>0.8898553150322202</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5564668052902977</v>
+        <v>0.5666227439400335</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.779421903208184</v>
+        <v>2.785515466398025</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.781558682205655</v>
+        <v>-3.843486800111694</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9366596254486239</v>
+        <v>0.9118883782862079</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5610102382351672</v>
+        <v>0.571166176884903</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.786245665585734</v>
+        <v>2.792339228775576</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.801057138447663</v>
+        <v>-3.862985256353702</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9330211825828987</v>
+        <v>0.9082499354204827</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5129255969552629</v>
+        <v>0.5230815356049987</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.76155582044887</v>
+        <v>2.767649383638711</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.756854301361762</v>
+        <v>-3.818782419267802</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.956581919945096</v>
+        <v>0.93181067278268</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5571284340411633</v>
+        <v>0.5672843726908992</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.793957125228247</v>
+        <v>2.800050688418088</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.764413967198809</v>
+        <v>-3.780493000780229</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9519680540795248</v>
+        <v>0.9455364406469569</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6119318380509826</v>
+        <v>0.6240678056499535</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.825249168103386</v>
+        <v>2.832530748662769</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.606122549659537</v>
+        <v>-3.622201583240956</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.066532386278273</v>
+        <v>1.060100772845705</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6119318380509826</v>
+        <v>0.6240678056499535</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.876496933286426</v>
+        <v>2.883778513845809</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.398480546025061</v>
+        <v>-3.41455957960648</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.148029892326317</v>
+        <v>1.141598278893749</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8195738416854588</v>
+        <v>0.8317098092844296</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.999522840061365</v>
+        <v>3.006804420620747</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.347448453302533</v>
+        <v>-3.363527486883952</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.163390957653598</v>
+        <v>1.15695934422103</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8706059344079867</v>
+        <v>0.8827419020069576</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.025090323933151</v>
+        <v>3.032371904492534</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.282224272175327</v>
+        <v>-3.298303305756747</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.206668034197185</v>
+        <v>1.200236420764617</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9358301155351924</v>
+        <v>0.9479660831341632</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.08141223670218</v>
+        <v>3.088693817261562</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.244797252104193</v>
+        <v>-3.260876285685613</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.217599814524919</v>
+        <v>1.211168201092351</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.941081653564374</v>
+        <v>0.9532176211633449</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.080524131818969</v>
+        <v>3.087805712378352</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.243439267130648</v>
+        <v>-3.259518300712068</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.219399800845578</v>
+        <v>1.21296818741301</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.015419779102193</v>
+        <v>1.027555746701164</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.1263837994729</v>
+        <v>3.133665380032283</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636289</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.215026004030764</v>
+        <v>-3.231105037612184</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.391322877106742</v>
+        <v>1.384891263674174</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9564442163557638</v>
+        <v>0.9685801839547348</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.251556232846254</v>
+        <v>3.258837813405637</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.140243743005751</v>
+        <v>-3.156322776587171</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.541348690734564</v>
+        <v>1.534917077301996</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.031226477380776</v>
+        <v>1.043362444979747</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.416538498679079</v>
+        <v>3.423820079238461</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.114159658741944</v>
+        <v>-3.130238692323363</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.543490300453946</v>
+        <v>1.537058687021378</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.031226477380776</v>
+        <v>1.043362444979747</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.408246474692938</v>
+        <v>3.41552805525232</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.026281745632823</v>
+        <v>-3.042360779214243</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.576834661281374</v>
+        <v>1.570403047848806</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.147152119804128</v>
+        <v>1.159288087403099</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.475995055730728</v>
+        <v>3.48327663629011</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.01738928423954</v>
+        <v>-3.03346831782096</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.597946051565479</v>
+        <v>1.591514438132911</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.147152119804128</v>
+        <v>1.159288087403099</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.49354946145752</v>
+        <v>3.500831042016902</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.185865401209418</v>
+        <v>-3.201944434790838</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.522410652182111</v>
+        <v>1.515979038749544</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.119204284087547</v>
+        <v>1.131340251686518</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.468635807432155</v>
+        <v>3.475917387991537</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.739609208579978</v>
+        <v>-2.755688242161398</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.682182826421749</v>
+        <v>1.675751212989181</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.024485614417914</v>
+        <v>1.036621582016885</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.393074302818237</v>
+        <v>3.40035588337762</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.716888104896825</v>
+        <v>-2.732967138478245</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.681935290391915</v>
+        <v>1.675503676959347</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.024485614417914</v>
+        <v>1.036621582016885</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.383738325315142</v>
+        <v>3.391019905874524</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.846089918190868</v>
+        <v>-2.862168951772288</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.789160690925467</v>
+        <v>1.782729077492899</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.895283801123872</v>
+        <v>0.9074197687228429</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.465123363189885</v>
+        <v>3.472404943749268</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.871964316664894</v>
+        <v>-2.888043350246313</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.815888754029503</v>
+        <v>1.809457140596935</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9401954098356131</v>
+        <v>0.9523313774345841</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.529148150910577</v>
+        <v>3.536429731469959</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.86490962644972</v>
+        <v>-2.88098866003114</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.815385986105118</v>
+        <v>1.80895437267255</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9472501000507869</v>
+        <v>0.9593860676497579</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.530056321029226</v>
+        <v>3.537337901588609</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.837958402123232</v>
+        <v>-2.854037435704652</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.836172629480455</v>
+        <v>1.829741016047887</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9621304460785061</v>
+        <v>0.974266413677477</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.548990682290599</v>
+        <v>3.556272262849982</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.859502629954019</v>
+        <v>-2.875581663535439</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.011658070493099</v>
+        <v>2.005226457060531</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9621304460785061</v>
+        <v>0.974266413677477</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.733093814435559</v>
+        <v>3.740375394994941</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.881910747758891</v>
+        <v>-2.897989781340311</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.994811518274144</v>
+        <v>1.988379904841576</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9621304460785061</v>
+        <v>0.974266413677477</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.725210509338552</v>
+        <v>3.732492089897935</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.910134983336492</v>
+        <v>-2.926214016917911</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.985575823592741</v>
+        <v>1.979144210160173</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9801071985298146</v>
+        <v>0.9922431661287856</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.738050560358975</v>
+        <v>3.745332140918357</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.919575909225022</v>
+        <v>-2.935654942806441</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.038053170959176</v>
+        <v>2.031621557526608</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.102534316073206</v>
+        <v>1.114670283672177</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.867760548606856</v>
+        <v>3.875042129166239</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.125814847013455</v>
+        <v>-3.141893880594875</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.958448690389104</v>
+        <v>1.952017076956536</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8962953782847725</v>
+        <v>0.9084313458837434</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.746908280479097</v>
+        <v>3.75418986103848</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347709</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.202144824614361</v>
+        <v>-3.218223858195781</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.926028512242516</v>
+        <v>1.919596898809949</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8962953782847725</v>
+        <v>0.9084313458837434</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.745020093372872</v>
+        <v>3.752301673932255</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.35710161001449</v>
+        <v>-3.37318064359591</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.858866027685327</v>
+        <v>1.852434414252759</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7413385928846432</v>
+        <v>0.7534745604836142</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.646866251735657</v>
+        <v>3.65414783229504</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343072</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.518670035541745</v>
+        <v>-3.534749069123165</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.792672667684577</v>
+        <v>1.786241054252009</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6145556690867638</v>
+        <v>0.6266916366857348</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.569230507667082</v>
+        <v>3.576512088226464</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389355</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.626970697411865</v>
+        <v>-3.643049730993285</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.762425809802448</v>
+        <v>1.75599419636988</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6145556690867638</v>
+        <v>0.6266916366857348</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.582303914533</v>
+        <v>3.589585495092383</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.786521770175382</v>
+        <v>-3.802600803756802</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.690610577479981</v>
+        <v>1.684178964047413</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4622780022250124</v>
+        <v>0.4744139698239833</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.48294251119889</v>
+        <v>3.490224091758272</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.814422557284855</v>
+        <v>-3.830501590866275</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.677974303763194</v>
+        <v>1.671542690330626</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4276810780820776</v>
+        <v>0.4398170456810485</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.460708397840131</v>
+        <v>3.467989978399513</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.936948659987749</v>
+        <v>-3.953027693569168</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.625728306659235</v>
+        <v>1.619296693226667</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3051549753791837</v>
+        <v>0.3172909429781546</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.383957180195593</v>
+        <v>3.391238760754976</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.167463156173337</v>
+        <v>-4.183542189754757</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.600228467775504</v>
+        <v>1.593796854342936</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.07464047919359496</v>
+        <v>0.08677644679256591</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.312354442074743</v>
+        <v>3.319636022634126</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.516208241397781</v>
+        <v>-4.5322872749792</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.601042152687573</v>
+        <v>1.594610539255005</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.03410747472530284</v>
+        <v>-0.02197150712633189</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.387417388725252</v>
+        <v>3.394698969284635</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.670194659173921</v>
+        <v>-4.686273692755341</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.608427854722757</v>
+        <v>1.601996241290189</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.03410747472530284</v>
+        <v>-0.02197150712633189</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.456397657870892</v>
+        <v>3.463679238430275</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.87479409403693</v>
+        <v>-4.89087312761835</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.512639282897674</v>
+        <v>1.506207669465106</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.03410747472530284</v>
+        <v>-0.02197150712633189</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.442448859991013</v>
+        <v>3.449730440550395</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.127269248044654</v>
+        <v>-5.143348281626074</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.423519710349999</v>
+        <v>1.417088096917431</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.03410747472530284</v>
+        <v>-0.02197150712633189</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.454319349046427</v>
+        <v>3.461600929605809</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.420165004524066</v>
+        <v>-5.436244038105486</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.307571942277177</v>
+        <v>1.30114032884461</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.03410747472530284</v>
+        <v>-0.02197150712633189</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.45552988356537</v>
+        <v>3.462811464124753</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.606829132658874</v>
+        <v>-5.622908166240294</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.237028033250576</v>
+        <v>1.230596419818008</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.06084644554986274</v>
+        <v>-0.04871047795089178</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.443608243297956</v>
+        <v>3.450889823857338</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.752849819572837</v>
+        <v>-5.768928853154256</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.17369761122118</v>
+        <v>1.167265997788612</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.06992953734371971</v>
+        <v>-0.05779356974474875</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.433236240957831</v>
+        <v>3.440517821517214</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830331</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.844563828682421</v>
+        <v>-5.860642862263841</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.29921606427639</v>
+        <v>1.292784450843822</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.06992953734371971</v>
+        <v>-0.05779356974474875</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.595440297656875</v>
+        <v>3.602721878216258</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.876215487742391</v>
+        <v>-5.89229452132381</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.281402038616217</v>
+        <v>1.274970425183649</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.07509799458815991</v>
+        <v>-0.06296202698918896</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.587185861274025</v>
+        <v>3.594467441833408</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.75004401586815</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.945281542315327</v>
+        <v>-5.961360575896747</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.264005034355533</v>
+        <v>1.257573420922965</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1374688720817699</v>
+        <v>-0.125332904482799</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.55999275234635</v>
+        <v>3.567274332905733</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332697</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.047257664563735</v>
+        <v>-6.063336698145155</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.232140223912073</v>
+        <v>1.225708610479505</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2394449943301775</v>
+        <v>-0.2273090267312066</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.507732717453208</v>
+        <v>3.515014298012591</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231813</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.937251381086513</v>
+        <v>-5.953330414667933</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.268295624547137</v>
+        <v>1.261864011114569</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2162404224129023</v>
+        <v>-0.2041044548139314</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.513808347847749</v>
+        <v>3.521089928407132</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.949781086198392</v>
+        <v>-5.965860119779812</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.26753375322436</v>
+        <v>1.261102139791792</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2300669218794253</v>
+        <v>-0.2179309542804544</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.509762458889809</v>
+        <v>3.517044039449192</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.648334360726555</v>
+        <v>-5.664413394307974</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.39537332629563</v>
+        <v>1.388941712863062</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.07137980359241192</v>
+        <v>0.08351577119138287</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.697891377055448</v>
+        <v>3.70517295761483</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.672924604961739</v>
+        <v>-5.689003638543158</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.386508406354268</v>
+        <v>1.3800767929217</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.07137980359241192</v>
+        <v>0.08351577119138287</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.698862554808158</v>
+        <v>3.706144135367541</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.621886228955218</v>
+        <v>-5.637965262536638</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.407766661136631</v>
+        <v>1.401335047704063</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.07137980359241192</v>
+        <v>0.08351577119138287</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.699705459187914</v>
+        <v>3.706987039747296</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.593037552131758</v>
+        <v>-5.609116585713178</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.438344230740161</v>
+        <v>1.431912617307593</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1002284804158722</v>
+        <v>0.1123644480148431</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.736052764156136</v>
+        <v>3.743334344715518</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700481</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.496402640113118</v>
+        <v>-5.512481673694538</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.293182191671551</v>
+        <v>1.286750578238983</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1968633924345121</v>
+        <v>0.2089993600334831</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.610217707491254</v>
+        <v>3.617499288050637</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.42736462916465</v>
+        <v>-5.44344366274607</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.324299440124903</v>
+        <v>1.317867826692335</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2659014033829802</v>
+        <v>0.2780373709819511</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.655142558134299</v>
+        <v>3.662424138693682</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833463</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.408577528795711</v>
+        <v>-5.424656562377131</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.316241099348561</v>
+        <v>1.309809485915993</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2846885037519187</v>
+        <v>0.2968244713508896</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.650841637431745</v>
+        <v>3.658123217991127</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.331478927253839</v>
+        <v>-5.347557960835259</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.346268250401739</v>
+        <v>1.339836636969171</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2846885037519187</v>
+        <v>0.2968244713508896</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.650029347868174</v>
+        <v>3.657310928427557</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.341864122143728</v>
+        <v>-5.357943155725148</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.351982951570856</v>
+        <v>1.345551338138288</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2743033088620294</v>
+        <v>0.2864392764610003</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.653667010059313</v>
+        <v>3.660948590618696</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.360452280865953</v>
+        <v>-5.376531314447373</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.415384693858391</v>
+        <v>1.408953080425823</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.255715150139804</v>
+        <v>0.267851117738775</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.713351120602403</v>
+        <v>3.720632701161786</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.360750827561989</v>
+        <v>-5.376829861143409</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.412134285998275</v>
+        <v>1.405702672565707</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2554166034437681</v>
+        <v>0.2675525710427391</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.71004100340308</v>
+        <v>3.717322583962463</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.259927693871561</v>
+        <v>-5.276006727452981</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.456994434413838</v>
+        <v>1.45056282098127</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2678808189281219</v>
+        <v>0.2800167865270929</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.722050427633084</v>
+        <v>3.729332008192466</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.80735616812147</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.069146333119154</v>
+        <v>-5.085225366700573</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.533436232193344</v>
+        <v>1.527004618760776</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4586621796805293</v>
+        <v>0.4707981472795003</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.836648497563071</v>
+        <v>3.843930078122454</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906083</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.962182975269732</v>
+        <v>-4.978262008851152</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.556058421070709</v>
+        <v>1.549626807638141</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5171267876403307</v>
+        <v>0.5292627552393017</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.851564108076549</v>
+        <v>3.858845688635931</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912988</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.906852387367969</v>
+        <v>-4.922931420949389</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.613157592843473</v>
+        <v>1.606725979410905</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5724573755420929</v>
+        <v>0.5845933431410638</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.919729397429665</v>
+        <v>3.927010977989047</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539897</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.894798260455007</v>
+        <v>-4.910877294036426</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.611665811510096</v>
+        <v>1.605234198077528</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5845115024550557</v>
+        <v>0.5966474700540266</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.92064844147888</v>
+        <v>3.927930022038263</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.972153750582976</v>
+        <v>-4.988232784164396</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.582604245643044</v>
+        <v>1.576172632210476</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5071560123270863</v>
+        <v>0.5192919799260572</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.876115777586234</v>
+        <v>3.883397358145617</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382923</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.904105187891446</v>
+        <v>-4.920184221472866</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.622674696597538</v>
+        <v>1.61624308316497</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5752045750186161</v>
+        <v>0.5873405426175871</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.929795941079035</v>
+        <v>3.937077521638417</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013422</v>
+        <v>3.645256780013431</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.135705581060947</v>
+        <v>-5.151784614642366</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.550237209503332</v>
+        <v>1.543805596070764</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5752045750186161</v>
+        <v>0.5873405426175871</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.949998611252629</v>
+        <v>3.957280191812012</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.185757126590167</v>
+        <v>-5.201836160171586</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.513822827358526</v>
+        <v>1.507391213925958</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5752045750186161</v>
+        <v>0.5873405426175871</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.93360484731951</v>
+        <v>3.940886427878893</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.360863959166611</v>
+        <v>-5.376942992748031</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.404032007921415</v>
+        <v>1.397600394488847</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5752045750186161</v>
+        <v>0.5873405426175871</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.893856760912977</v>
+        <v>3.90113834147236</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.164763805736088</v>
+        <v>-5.180842839317508</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.489494688290564</v>
+        <v>1.483063074857996</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.771304728449139</v>
+        <v>0.78344069604811</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.018539471968231</v>
+        <v>4.025821052527614</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.011738413622804</v>
+        <v>-5.027817447204224</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.649875844708782</v>
+        <v>1.643444231276214</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9243301205624231</v>
+        <v>0.9364660881613941</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.209525706809107</v>
+        <v>4.216807287368488</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.040045727496074</v>
+        <v>-5.056124761077494</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.826019144067767</v>
+        <v>1.819587530635199</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9243301205624231</v>
+        <v>0.9364660881613941</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.396991931717398</v>
+        <v>4.404273512276781</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.206638952609596</v>
+        <v>-5.222717986191016</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.728784805376441</v>
+        <v>1.722353191943873</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7577368954489008</v>
+        <v>0.7698728630478717</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.266438948003368</v>
+        <v>4.273720528562751</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.183603159248031</v>
+        <v>-5.19968219282945</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.741675525382785</v>
+        <v>1.735243911950217</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7577368954489008</v>
+        <v>0.7698728630478717</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.270115350665086</v>
+        <v>4.277396931224469</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.154357178792334</v>
+        <v>-5.170436212373754</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.750991972688559</v>
+        <v>1.744560359255991</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7577368954489008</v>
+        <v>0.7698728630478717</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.267733405788581</v>
+        <v>4.275014986347964</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.261282726670185</v>
+        <v>-5.277361760251605</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.705514992695053</v>
+        <v>1.699083379262485</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6508113475710494</v>
+        <v>0.6629473151700204</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.200871316219505</v>
+        <v>4.208152896778888</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.406301285177434</v>
+        <v>-5.422380318758854</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.648936371435388</v>
+        <v>1.64250475800282</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5057927890638009</v>
+        <v>0.5179287566627718</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.11528898325839</v>
+        <v>4.122570563817773</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.524643050962151</v>
+        <v>-5.540722084543571</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.701530904379254</v>
+        <v>1.695099290946686</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.516478827626691</v>
+        <v>0.5286147952256619</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.221631845653877</v>
+        <v>4.22891342621326</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790806</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.576053473282859</v>
+        <v>-5.592132506864279</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.67875243257691</v>
+        <v>1.672320819144342</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.516478827626691</v>
+        <v>0.5286147952256619</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.219417542779817</v>
+        <v>4.226699123339199</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437335</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.655472924490611</v>
+        <v>-5.671551958072031</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.646887780168099</v>
+        <v>1.640456166735531</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.516478827626691</v>
+        <v>0.5286147952256619</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.219320670854105</v>
+        <v>4.226602251413488</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298403</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.750935922407828</v>
+        <v>-5.767014955989248</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.608696474559254</v>
+        <v>1.602264861126686</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.516478827626691</v>
+        <v>0.5286147952256619</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.219314564412149</v>
+        <v>4.226596144971531</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960218004</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.686560011557114</v>
+        <v>-5.702639045138533</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.632543235462151</v>
+        <v>1.626111622029583</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5808547384774061</v>
+        <v>0.592990706076377</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.256036507485188</v>
+        <v>4.263318088044571</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.73608941335354</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.741929173689307</v>
+        <v>-5.758008207270727</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.616129388357</v>
+        <v>1.609697774924432</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5808547384774061</v>
+        <v>0.592990706076377</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.261770325232915</v>
+        <v>4.269051905792297</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113283</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.760147640686916</v>
+        <v>-5.776226674268336</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.608380364900889</v>
+        <v>1.601948751468321</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5557483012215639</v>
+        <v>0.5678842688205349</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.246244826222342</v>
+        <v>4.253526406781725</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113692</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.721464205342985</v>
+        <v>-5.737543238924405</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.64372813188878</v>
+        <v>1.637296518456212</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5557483012215639</v>
+        <v>0.5678842688205349</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.26611921907266</v>
+        <v>4.273400799632043</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.615429210137676</v>
+        <v>-5.631508243719096</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.669842830495631</v>
+        <v>1.663411217063063</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5557483012215639</v>
+        <v>0.5678842688205349</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.249819919597389</v>
+        <v>4.257101500156771</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.432217547004581</v>
+        <v>-5.448296580586001</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.745558445212915</v>
+        <v>1.739126831780347</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5557483012215639</v>
+        <v>0.5678842688205349</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.252250869061434</v>
+        <v>4.259532449620816</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.36049609999073</v>
+        <v>-5.37657513357215</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.757191430097833</v>
+        <v>1.750759816665265</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6274697482354146</v>
+        <v>0.6396057158343855</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.278228143349121</v>
+        <v>4.285509723908504</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.338123074383024</v>
+        <v>-5.354202107964444</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.713056386262087</v>
+        <v>1.706624772829519</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6387254993483161</v>
+        <v>0.6508614669472871</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.231897339938034</v>
+        <v>4.239178920497417</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456726</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.371139370293768</v>
+        <v>-5.387218403875188</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.885048072783144</v>
+        <v>1.878616459350576</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5692881226815645</v>
+        <v>0.5814240902805354</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.375433118823339</v>
+        <v>4.382714699382722</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.71376253688368</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.35961173464416</v>
+        <v>-5.37569076822558</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.881580352871237</v>
+        <v>1.875148739438669</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6282887808829269</v>
+        <v>0.6404247484818979</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.402754739572405</v>
+        <v>4.410036320131788</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.7171506992363</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.456953235986528</v>
+        <v>-5.473032269567948</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.846311864856078</v>
+        <v>1.83988025142351</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5838685987174386</v>
+        <v>0.5960045663164095</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.379770742794901</v>
+        <v>4.387052323354284</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942768</v>
+        <v>3.705201079427686</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.542809265326495</v>
+        <v>-5.558888298907915</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.813220535312929</v>
+        <v>1.806788921880361</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5414925294913036</v>
+        <v>0.5536284970902745</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.355596183452058</v>
+        <v>4.36287776401144</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610376</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.551646062742615</v>
+        <v>-5.567725096324034</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.792105018166983</v>
+        <v>1.785673404734415</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5340503568499528</v>
+        <v>0.5461863244489238</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.333550081687749</v>
+        <v>4.340831662247131</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667457</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.643028625308073</v>
+        <v>-5.546292348645173</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.765716504185849</v>
+        <v>1.80441101485101</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.4974854721306081</v>
+        <v>0.5297525438449536</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.321775661901192</v>
+        <v>4.341135904929799</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889187</v>
+        <v>3.673978374889193</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.631321907321067</v>
+        <v>-5.534585630658166</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.87252744920492</v>
+        <v>1.91122195987008</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5091921901176145</v>
+        <v>0.54145926183196</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.430927950517664</v>
+        <v>4.450288193546271</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.68247609940957</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.702233981063344</v>
+        <v>-5.605497704400443</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.847194958439414</v>
+        <v>1.885889469104574</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5091921901176145</v>
+        <v>0.54145926183196</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.433960289249069</v>
+        <v>4.453320532277676</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.712550079229696</v>
+        <v>-5.615813802566795</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.055973352450931</v>
+        <v>2.094667863116092</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5091921901176145</v>
+        <v>0.54145926183196</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.646865122527127</v>
+        <v>4.666225365555734</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762289</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.712456111212323</v>
+        <v>-5.615719834549423</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.05518960656997</v>
+        <v>2.093884117235131</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5095620514649325</v>
+        <v>0.541829123179278</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.646265706247608</v>
+        <v>4.665625949276214</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884075</v>
+        <v>3.800870306884081</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.856057275235709</v>
+        <v>-5.759320998572808</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.99198112690497</v>
+        <v>2.03067563757013</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5095620514649325</v>
+        <v>0.541829123179278</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.640497692191961</v>
+        <v>4.659857935220568</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129646</v>
+        <v>3.671015692129644</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.85510885211767</v>
+        <v>-5.75837257545477</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.992360496152185</v>
+        <v>2.031055006817346</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5095620514649325</v>
+        <v>0.541829123179278</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.640497692191961</v>
+        <v>4.659857935220568</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052349</v>
+        <v>3.904173816052348</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.955378670076691</v>
+        <v>-5.85864239341379</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.964980176949669</v>
+        <v>2.003674687614829</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5095620514649325</v>
+        <v>0.541829123179278</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.653225300173053</v>
+        <v>4.67258554320166</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813493</v>
+        <v>3.740179607813491</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.949386423287879</v>
+        <v>-5.852650146624979</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.969323074089581</v>
+        <v>2.008017584754742</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5095620514649325</v>
+        <v>0.541829123179278</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.655171298597441</v>
+        <v>4.674531541626048</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537942</v>
+        <v>3.76505079653794</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.860828462157111</v>
+        <v>-5.764092185494211</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.998400394559658</v>
+        <v>2.037094905224818</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5095620514649325</v>
+        <v>0.541829123179278</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.64882543461521</v>
+        <v>4.668185677643817</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771814</v>
+        <v>3.758409170771812</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.843069384654037</v>
+        <v>-5.746333107991137</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.004812702999883</v>
+        <v>2.043507213665043</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5095620514649325</v>
+        <v>0.541829123179278</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.648134112054206</v>
+        <v>4.667494355082813</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.74343923360497</v>
+        <v>-5.495608021949182</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.057446949328097</v>
+        <v>2.156579433990412</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.609192202514</v>
+        <v>0.7925542092212328</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.720694388592233</v>
+        <v>4.830711592616573</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.792838742293981</v>
+        <v>-5.545007530638193</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.226841411351219</v>
+        <v>2.325973896013533</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6194510359457447</v>
+        <v>0.8028130426529775</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.916003954150006</v>
+        <v>5.026021158174346</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351855</v>
+        <v>3.772186508351859</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.586154268651605</v>
+        <v>-5.338323056995817</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.296703873911031</v>
+        <v>2.395836358573346</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8261355095881203</v>
+        <v>1.009497516295353</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.027203311438293</v>
+        <v>5.137220515462633</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551265</v>
+        <v>3.763392838551272</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.620311163649131</v>
+        <v>-5.372479951993343</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.285042629566126</v>
+        <v>2.38417511422844</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7425517400473078</v>
+        <v>0.9259137467545407</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.979054563367911</v>
+        <v>5.089071767392251</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041106</v>
+        <v>3.80559056504111</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.527721684587674</v>
+        <v>-5.279890472931887</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.675575535180375</v>
+        <v>2.774708019842691</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7425517400473078</v>
+        <v>0.9259137467545407</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.332551677357579</v>
+        <v>5.442568881381918</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497396</v>
+        <v>3.832164354497402</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.600882288360819</v>
+        <v>-5.353051076705031</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.650874405238221</v>
+        <v>2.750006889900536</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7145305400130648</v>
+        <v>0.8978925467202976</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.320302068904136</v>
+        <v>5.430319272928475</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492286</v>
+        <v>3.858310890492294</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.548665978564477</v>
+        <v>-5.300834766908689</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.721590870480285</v>
+        <v>2.8207233551426</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7145305400130648</v>
+        <v>0.8978925467202976</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.370132010227663</v>
+        <v>5.480149214252003</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436468</v>
+        <v>3.844935596436475</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.516768461479232</v>
+        <v>-5.268937249823444</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.743163847524394</v>
+        <v>2.842296332186709</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7464280570983106</v>
+        <v>0.9297900638055434</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.398084490688822</v>
+        <v>5.508101694713162</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039477</v>
+        <v>3.848376866039484</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.531523785679372</v>
+        <v>-5.283692574023584</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.732899301883535</v>
+        <v>2.83203178654585</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7464280570983106</v>
+        <v>0.9297900638055434</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.393722074728018</v>
+        <v>5.503739278752358</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524471</v>
+        <v>3.868153115524478</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.482059162309461</v>
+        <v>-5.234227950653673</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.743609654647779</v>
+        <v>2.842742139310094</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.7958926804682223</v>
+        <v>0.9792546871754551</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.414325352166245</v>
+        <v>5.524342556190585</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867945</v>
+        <v>3.849040239867952</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.318951170155845</v>
+        <v>-5.071119958500057</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.80526051922416</v>
+        <v>2.904393003886475</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9590006726218375</v>
+        <v>1.14236267932907</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.508597815173349</v>
+        <v>5.618615019197689</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232969</v>
+        <v>3.870204928232966</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.298308079354618</v>
+        <v>-5.05047686769883</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.822564792235779</v>
+        <v>2.921697276898094</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9590006726218375</v>
+        <v>1.14236267932907</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.517644851864477</v>
+        <v>5.627662055888817</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179672</v>
+        <v>3.85553443717967</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.361015995829176</v>
+        <v>-5.113184784173388</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.798339090632078</v>
+        <v>2.897471575294392</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.8962927561472798</v>
+        <v>1.079654762854513</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.480877566965864</v>
+        <v>5.590894770990204</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967719</v>
+        <v>3.884687848967718</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.27532836933506</v>
+        <v>-5.065176660329695</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.795523558020076</v>
+        <v>2.879584241622222</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.8962927561472798</v>
+        <v>1.079654762854513</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.443786983756216</v>
+        <v>5.553804187780556</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018607</v>
+        <v>3.89536235701861</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.19650271215147</v>
+        <v>-4.889768314928409</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.830986074451463</v>
+        <v>2.953679833340687</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.9751184133308702</v>
+        <v>1.255063108255799</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.495014631624321</v>
+        <v>5.662981448579278</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.89161098107513</v>
+        <v>3.891610981075132</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.004567910897596</v>
+        <v>-4.697833513674535</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.902659087560049</v>
+        <v>3.025352846449273</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.9751184133308702</v>
+        <v>1.255063108255799</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.489913724231358</v>
+        <v>5.657880541186315</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435436</v>
+        <v>3.872432493435442</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.886394532879669</v>
+        <v>-4.579660135656608</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.945282348156315</v>
+        <v>3.067976107045539</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.093291791348797</v>
+        <v>1.373236486273727</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.556171660431209</v>
+        <v>5.724138477386167</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917725</v>
+        <v>3.859571723917728</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.772979850096937</v>
+        <v>-4.466245452873877</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.019736814132435</v>
+        <v>3.142430573021659</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.206706474131529</v>
+        <v>1.486651169056458</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.653309062963875</v>
+        <v>5.821275879918833</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013631</v>
+        <v>3.828006274013635</v>
       </c>
       <c r="C2104" t="n">
         <v>4.922845401496135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.745930812403683</v>
+        <v>-4.439196415180623</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.024116652220913</v>
+        <v>3.146810411110137</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.233755511824782</v>
+        <v>1.513700206749712</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.663098708591004</v>
+        <v>5.831065525545962</v>
       </c>
     </row>
     <row r="2105">
@@ -49966,16 +49966,16 @@
         <v>4.922845401496135</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.751964092590454</v>
+        <v>-4.445229695367393</v>
       </c>
       <c r="E2105" t="n">
-        <v>3.021703340146205</v>
+        <v>3.144397099035429</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.233755511824782</v>
+        <v>1.513700206749712</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.663098708591004</v>
+        <v>5.831065525545962</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.502369099565479</v>
+        <v>3.86075709904484</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.85641790664968</v>
+        <v>4.926483568638547</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.751964092590454</v>
+        <v>-4.531699836281179</v>
       </c>
       <c r="E2106" t="n">
-        <v>3.021703340146205</v>
+        <v>3.113447209812327</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.233755511824782</v>
+        <v>1.490480208720284</v>
       </c>
       <c r="G2106" t="n">
-        <v>4.849481703636048</v>
+        <v>5.820771693870718</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241003.xlsx
+++ b/tame_output/ON/bt/strategyON_20241003.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>121.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>101.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>181.0%</t>
+          <t>203.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-614.7%</t>
+          <t>-603.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-64.9%</t>
+          <t>-38.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-287.1%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-99.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.6%</t>
+          <t>133.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>118.9%</t>
+          <t>121.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>136.1%</t>
+          <t>143.9%</t>
         </is>
       </c>
     </row>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.057688270276868</v>
+        <v>-8.869190377561386</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4446875423097185</v>
+        <v>-0.3692883852235256</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.570948920052083</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.236174838083527</v>
+        <v>2.246775179401955</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.933109613939276</v>
+        <v>-8.744611721223794</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3937169352186229</v>
+        <v>-0.31831777813243</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.570948920052083</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.237313982639586</v>
+        <v>2.247914323958013</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.908072932370766</v>
+        <v>-8.719575039655284</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3810684884291113</v>
+        <v>-0.3056693313429184</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.545619832501347</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.255145209332135</v>
+        <v>2.265745550650562</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.835939757082885</v>
+        <v>-8.647441864367403</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3464815140753221</v>
+        <v>-0.2710823569891296</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.545619832501347</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.260878913570772</v>
+        <v>2.271479254889199</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.832736096657079</v>
+        <v>-8.644238203941597</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.354937312298865</v>
+        <v>-0.2795381552126726</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.542416172075541</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.253063847432391</v>
+        <v>2.263664188750818</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.739277062671855</v>
+        <v>-8.550779169956373</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3274371800176827</v>
+        <v>-0.2520380229314902</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.542416172075541</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.243180366119483</v>
+        <v>2.25378070743791</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.728623881118423</v>
+        <v>-8.440649547895999</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3250104678956842</v>
+        <v>-0.2098207346067142</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.542416172075541</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.241345805620109</v>
+        <v>2.251946146938536</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.630716842441933</v>
+        <v>-8.342742509219509</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2861479673985485</v>
+        <v>-0.170958234109579</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.474430422214985</v>
+        <v>-1.456763186684273</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.281836940562982</v>
+        <v>2.292437281881409</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.606763301465975</v>
+        <v>-8.318788968243551</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.275898044862672</v>
+        <v>-0.160708311573702</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.450476881239027</v>
+        <v>-1.432809645708315</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.29687757129405</v>
+        <v>2.307477912612478</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.342703363143178</v>
+        <v>-8.054729029920754</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1835343856953053</v>
+        <v>-0.0683446524063358</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.186416942916231</v>
+        <v>-1.168749707385519</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.442053218125976</v>
+        <v>2.452653559444403</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.63562373963834</v>
+        <v>-7.347649406415916</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.09651043004632909</v>
+        <v>0.2117001633352986</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.186416942916231</v>
+        <v>-1.168749707385519</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.439266184465675</v>
+        <v>2.449866525784102</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388731</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.595439441272149</v>
+        <v>-7.307465108049725</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1129277732806466</v>
+        <v>0.2281175065696162</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.14623264455004</v>
+        <v>-1.128565409019328</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.463720387373231</v>
+        <v>2.474320728691658</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626478</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.432039570332787</v>
+        <v>-7.144065237110363</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1776545428771485</v>
+        <v>0.2928442761661181</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9828327736106774</v>
+        <v>-0.9651655380799653</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.561127131157605</v>
+        <v>2.571727472476033</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.273922190954011</v>
+        <v>-6.985947857731587</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2488259234665113</v>
+        <v>0.3640156567554809</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.824715394231902</v>
+        <v>-0.8070481587011898</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.663921987622723</v>
+        <v>2.67452232894115</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.124255799946496</v>
+        <v>-6.836281466724072</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.305800269556558</v>
+        <v>0.4209900028455276</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.731811902989366</v>
+        <v>-0.7141446674586539</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.716771872055285</v>
+        <v>2.727372213373712</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.99198032631561</v>
+        <v>-6.704005993093186</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2599712450160672</v>
+        <v>0.3751609783050367</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5995364293584794</v>
+        <v>-0.5818691938277673</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.697397942240972</v>
+        <v>2.707998283559399</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.820119110750707</v>
+        <v>-6.532144777528283</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3315307919296648</v>
+        <v>0.4467205252186348</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4276752137935765</v>
+        <v>-0.4100079782628644</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.80332973226755</v>
+        <v>2.813930073585978</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.735154444021388</v>
+        <v>-6.447180110798964</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3784229998450512</v>
+        <v>0.4936127331340212</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.342710547064257</v>
+        <v>-0.3250433115335448</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.867214873528801</v>
+        <v>2.877815214847228</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.840744433794493</v>
+        <v>-6.552770100572069</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.208211074336591</v>
+        <v>0.3234008076255606</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4483005368373613</v>
+        <v>-0.4306333013066492</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.675884950065719</v>
+        <v>2.686485291384147</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.772509849169065</v>
+        <v>-6.484535515946641</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2840492500638483</v>
+        <v>0.3992389833528178</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4298852139648253</v>
+        <v>-0.4122179784341132</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.735478485666328</v>
+        <v>2.746078826984755</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.624569807761466</v>
+        <v>-6.336595474539042</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2266044579884809</v>
+        <v>0.3417941912774505</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.4095642980562678</v>
+        <v>-0.3918970625255556</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.631050226573055</v>
+        <v>2.641650567891482</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.571600285507477</v>
+        <v>-6.283625952285053</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2390782806365981</v>
+        <v>0.3542680139255676</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3565947758022789</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.65411795367197</v>
+        <v>2.664718294990398</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.405812089547187</v>
+        <v>-6.117837756324763</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2984329469256215</v>
+        <v>0.413622680214591</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3565947758022789</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.647157341576877</v>
+        <v>2.657757682895304</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.372448883068418</v>
+        <v>-6.084474549845994</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3262405838982718</v>
+        <v>0.4414303171872414</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3565947758022789</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.66161969595802</v>
+        <v>2.672220037276448</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.82855148672282</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.264189745945896</v>
+        <v>-5.976215412723472</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3640763592064755</v>
+        <v>0.4792660924954455</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3565947758022789</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.656151816417215</v>
+        <v>2.666752157735643</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.140898611128765</v>
+        <v>-5.852924277906341</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4108909071439046</v>
+        <v>0.5260806404328746</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2333036409851484</v>
+        <v>-0.2156364054544362</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.72762459131807</v>
+        <v>2.738224932636498</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.088201743997474</v>
+        <v>-5.80022741077505</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4396706322337467</v>
+        <v>0.5548603655227162</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1806067738538572</v>
+        <v>-0.1629395383231451</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.76694368983417</v>
+        <v>2.777544031152598</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.84443630201403</v>
+        <v>-5.556461968791606</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5329575173741752</v>
+        <v>0.6481472506631447</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1806067738538572</v>
+        <v>-0.1629395383231451</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.762724398181221</v>
+        <v>2.773324739499648</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.754660629637558</v>
+        <v>-5.466686296415133</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.57099210024478</v>
+        <v>0.6861818335337495</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1190073289395472</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.801808379049823</v>
+        <v>2.81240872036825</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.504810235688483</v>
+        <v>-5.216835902466059</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6636743328081121</v>
+        <v>0.7788640660970816</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1190073289395472</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.794550454033525</v>
+        <v>2.805150795351952</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.328918143221051</v>
+        <v>-5.040943809998627</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7376302933157333</v>
+        <v>0.8528200266047032</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1190073289395472</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.798149577554174</v>
+        <v>2.808749918872601</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.78093391139299</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.157471680198587</v>
+        <v>-4.869497346976163</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8195363845792727</v>
+        <v>0.9347261178682422</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.05243913408291595</v>
+        <v>0.07010636961362809</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.914344961422205</v>
+        <v>2.924945302740633</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632784</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.077449393089466</v>
+        <v>-4.789475059867042</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8505657770392179</v>
+        <v>0.9657555103281874</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1324614211920369</v>
+        <v>0.1501286567227491</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.961378811303975</v>
+        <v>2.971979152622402</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.013813650855532</v>
+        <v>-4.725839317633108</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8807148749871088</v>
+        <v>0.9959046082760785</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1960971634259714</v>
+        <v>0.2137643989566836</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.004255057698653</v>
+        <v>3.01485539901708</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.920116332639137</v>
+        <v>-4.632141999416713</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8993880610574627</v>
+        <v>1.014577794346432</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1960971634259714</v>
+        <v>0.2137643989566836</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.985449316482448</v>
+        <v>2.996049657800876</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242295</v>
+        <v>3.797694884242297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.930618955704426</v>
+        <v>-4.527181548925486</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8969300884562244</v>
+        <v>1.0583050511678</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1855945403606826</v>
+        <v>0.3187248494479103</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.980890819268152</v>
+        <v>3.060769004720489</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.818132695035551</v>
+        <v>-4.414695288256612</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9458539065585945</v>
+        <v>1.10722886927017</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1855945403606826</v>
+        <v>0.3187248494479103</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.984820133102973</v>
+        <v>3.064698318555309</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.800419008157686</v>
+        <v>-4.396981601378746</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9536179652270806</v>
+        <v>1.114992927938657</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1887758692575994</v>
+        <v>0.3219061783448271</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.987407514358463</v>
+        <v>3.0672856998108</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.676944736844668</v>
+        <v>-4.273507330065728</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.000005744972281</v>
+        <v>1.161380707683857</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1887758692575994</v>
+        <v>0.3219061783448271</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.984405585578456</v>
+        <v>3.064283771030793</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.619008904846452</v>
+        <v>-4.215571498067512</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.024759114782182</v>
+        <v>1.186134077493758</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2143377439403487</v>
+        <v>0.3474680530275764</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.00132174739872</v>
+        <v>3.081199932851057</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.486141215783174</v>
+        <v>-4.082703809004235</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.093800373209316</v>
+        <v>1.255175335920892</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2143377439403487</v>
+        <v>0.3474680530275764</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.017215930200543</v>
+        <v>3.09709411565288</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.365968132418676</v>
+        <v>-3.962530725639736</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.143015450995418</v>
+        <v>1.304390413706993</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3345108273048476</v>
+        <v>0.4676411363920753</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.090465624659545</v>
+        <v>3.170343810111881</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.230714771088699</v>
+        <v>-3.827277364309759</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.207204898088848</v>
+        <v>1.368579860800424</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4697641886348247</v>
+        <v>0.6028944977220525</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.181705744018971</v>
+        <v>3.261583929471307</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.290589598446391</v>
+        <v>-3.887152191667451</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.169292458547197</v>
+        <v>1.330667421258773</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4098893612771326</v>
+        <v>0.5430196703643604</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.131818339005781</v>
+        <v>3.211696524458118</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.170769367535554</v>
+        <v>-3.767331960756614</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.23250972014574</v>
+        <v>1.393884682857316</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4098893612771326</v>
+        <v>0.5430196703643604</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.14710750823999</v>
+        <v>3.226985693692327</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.17323907399736</v>
+        <v>-3.76980166721842</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.13916603688346</v>
+        <v>1.300540999595036</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4074196548153264</v>
+        <v>0.5405499639025542</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.053269883685348</v>
+        <v>3.133148069137684</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.24160926032137</v>
+        <v>-3.83817185354243</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.031079823839157</v>
+        <v>1.192454786550733</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4166953538515414</v>
+        <v>0.5498256629387691</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.978097164592378</v>
+        <v>3.057975350044715</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.353481539947521</v>
+        <v>-3.95004413316858</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.976767620620588</v>
+        <v>1.138142583332164</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4166953538515414</v>
+        <v>0.5498256629387691</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.968533873224269</v>
+        <v>3.048412058676606</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.337506874461253</v>
+        <v>-3.934069467682312</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9497320117391224</v>
+        <v>1.111106974450699</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4166953538515414</v>
+        <v>0.5498256629387691</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.935108398148297</v>
+        <v>3.014986583600633</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.162032614668783</v>
+        <v>-3.758595207889843</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.024488947647898</v>
+        <v>1.185863910359474</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4166953538515414</v>
+        <v>0.5498256629387691</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.939675630140084</v>
+        <v>3.019553815592421</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.154108240083869</v>
+        <v>-3.750670833304929</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.003400726243071</v>
+        <v>1.164775688954647</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4166953538515414</v>
+        <v>0.5498256629387691</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.915417658901291</v>
+        <v>2.995295844353628</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.14783003751402</v>
+        <v>-3.74439263073508</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9344503206724601</v>
+        <v>1.095825283384036</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4229735564213905</v>
+        <v>0.5561038655086181</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.847722893844651</v>
+        <v>2.927601079296987</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.087977418310297</v>
+        <v>-3.684540011531357</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9685637547860817</v>
+        <v>1.129938717497658</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4229735564213905</v>
+        <v>0.5561038655086181</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.857895280276783</v>
+        <v>2.93777346572912</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.001733955283919</v>
+        <v>-3.59829654850498</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9980074105704932</v>
+        <v>1.159382373282069</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4229735564213905</v>
+        <v>0.5561038655086181</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.852841550850644</v>
+        <v>2.93271973630298</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.047040774682899</v>
+        <v>-3.643603367903959</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9716604582554269</v>
+        <v>1.133035420967003</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3821633934121597</v>
+        <v>0.5152937024993873</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.820131228489631</v>
+        <v>2.900009413941967</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.0760738793852</v>
+        <v>-3.672636472606261</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.960599089407608</v>
+        <v>1.121974052119184</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3821633934121597</v>
+        <v>0.5152937024993873</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.820683101522732</v>
+        <v>2.900561286975069</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.983263397934341</v>
+        <v>-3.579825991155402</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9269959738793172</v>
+        <v>1.088370936590893</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.474973874863019</v>
+        <v>0.6081041839502467</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.805642082284614</v>
+        <v>2.88552026773695</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.027652867263769</v>
+        <v>-3.624215460484829</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9111136620721469</v>
+        <v>1.072488624783723</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4305844055335913</v>
+        <v>0.563714714620819</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.780881876611558</v>
+        <v>2.860760062063894</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.007149173378272</v>
+        <v>-3.603711766599332</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9143908481380687</v>
+        <v>1.075765810849645</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4510880994190887</v>
+        <v>0.5842184085063163</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.788259801454579</v>
+        <v>2.868137986906916</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.090821270090604</v>
+        <v>-3.687383863311664</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.886413305283803</v>
+        <v>1.047788267995379</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4510880994190887</v>
+        <v>0.5842184085063163</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.793751097285246</v>
+        <v>2.873629282737583</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.118601667991957</v>
+        <v>-3.715164261213017</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8867983478918011</v>
+        <v>1.048173310603377</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4233077015177356</v>
+        <v>0.5564380106049633</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.788580060312973</v>
+        <v>2.86845824576531</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.236982340722095</v>
+        <v>-3.833544933943156</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.677801798800399</v>
+        <v>0.839176761511975</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3560898493667594</v>
+        <v>0.4892201584539871</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.586605069023041</v>
+        <v>2.666483254475378</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.345596419165426</v>
+        <v>-3.942159012386487</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7545058281422721</v>
+        <v>0.915880790853848</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3560898493667594</v>
+        <v>0.4892201584539871</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.706754729742247</v>
+        <v>2.786632915194583</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.310187380917283</v>
+        <v>-3.906749974138344</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7831824695438523</v>
+        <v>0.9445574322554282</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3560898493667594</v>
+        <v>0.4892201584539871</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.72126775584457</v>
+        <v>2.801145941296906</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.318648549572744</v>
+        <v>-3.915211142793805</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7772174434240366</v>
+        <v>0.9385924061356123</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3476286807112984</v>
+        <v>0.4807589897985261</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.713610495993662</v>
+        <v>2.793488681445998</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.141532219537578</v>
+        <v>-3.738094812758639</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8447930042834055</v>
+        <v>1.006167966994981</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3476286807112984</v>
+        <v>0.4807589897985261</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.710339524838964</v>
+        <v>2.790217710291301</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.186624464371124</v>
+        <v>-3.783187057592184</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8274394981119002</v>
+        <v>0.9888144608234761</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2857326375419086</v>
+        <v>0.4188629466291363</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.673885290699243</v>
+        <v>2.75376347615158</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.007249043132356</v>
+        <v>-3.603811636353417</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8929766419138216</v>
+        <v>1.054351604625398</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4425093957126273</v>
+        <v>0.5756397047998549</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.761738320908089</v>
+        <v>2.841616506360425</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.052263256652962</v>
+        <v>-3.648825849874023</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8557784118371692</v>
+        <v>1.017153374548745</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4121605003980227</v>
+        <v>0.5452908094852503</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.724336439050916</v>
+        <v>2.804214624503252</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.140274443211659</v>
+        <v>-3.73683703643272</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.826265499552636</v>
+        <v>0.9876404622642116</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3466839925388497</v>
+        <v>0.4798143016260774</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.690742096674358</v>
+        <v>2.770620282126695</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.241472224648832</v>
+        <v>-3.838034817869893</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7849903088742685</v>
+        <v>0.9463652715858442</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2782751789935305</v>
+        <v>0.4114054880807582</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.648900730443668</v>
+        <v>2.728778915896004</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.234961258034519</v>
+        <v>-3.83152385125558</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7851946570743102</v>
+        <v>0.9465696197858859</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2782751789935305</v>
+        <v>0.4114054880807582</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.646500691997984</v>
+        <v>2.726378877450321</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.215923130327222</v>
+        <v>-3.812485723548283</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.789334627365474</v>
+        <v>0.9507095900770497</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.220091567662336</v>
+        <v>0.3532218767495636</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.608115244407513</v>
+        <v>2.687993429859849</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.268438932602042</v>
+        <v>-3.865001525823103</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8876227080897361</v>
+        <v>1.048997670801312</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.220091567662336</v>
+        <v>0.3532218767495636</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.727409646041703</v>
+        <v>2.807287831494039</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.271847244036622</v>
+        <v>-3.868409837257683</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8870927125020378</v>
+        <v>1.048467675213614</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2526081366717133</v>
+        <v>0.385738445758941</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.747752916433463</v>
+        <v>2.8276311018858</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.252491108142775</v>
+        <v>-3.849053701363836</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9008436972565028</v>
+        <v>1.062218659968079</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2526081366717133</v>
+        <v>0.385738445758941</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.753761446830389</v>
+        <v>2.833639632282726</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.325820636880867</v>
+        <v>-3.922383230101928</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7694621070384651</v>
+        <v>0.9308370697500408</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2530027990913353</v>
+        <v>0.3861331081785629</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.651948465559362</v>
+        <v>2.731826651011698</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.409641858155566</v>
+        <v>-4.006204451376626</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7387272400600668</v>
+        <v>0.9001022027716425</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2530027990913353</v>
+        <v>0.3861331081785629</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.654742087090843</v>
+        <v>2.734620272543179</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.403489152102781</v>
+        <v>-4.000051745323842</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.741850670872839</v>
+        <v>0.9032256335844147</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2591555051441196</v>
+        <v>0.3922858142313472</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.659096059114171</v>
+        <v>2.738974244566508</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.420298450253283</v>
+        <v>-4.016861043474344</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7342074283527484</v>
+        <v>0.8955823910643241</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2423462069936179</v>
+        <v>0.3754765160808456</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.648090956963981</v>
+        <v>2.727969142416317</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.358000451477161</v>
+        <v>-3.954563044698222</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8254621816600181</v>
+        <v>0.9868371443715938</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.28764047126806</v>
+        <v>0.4207707803552876</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.741603069325467</v>
+        <v>2.821481254777804</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992195</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.156210253812003</v>
+        <v>-3.752772847033064</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7084702624402084</v>
+        <v>0.8698452251517841</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4856586634372144</v>
+        <v>0.618788972524442</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.662705986341086</v>
+        <v>2.742584171793423</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.207096966498198</v>
+        <v>-3.803659559719259</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7584058096879058</v>
+        <v>0.9197807723994815</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4347719507510198</v>
+        <v>0.5679022598382475</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.702464191051545</v>
+        <v>2.782342376503882</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.120486223848391</v>
+        <v>-3.717048817069451</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.807677842863872</v>
+        <v>0.9690528055754479</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5133976819561781</v>
+        <v>0.6465279910434057</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.764267365890684</v>
+        <v>2.84414555134302</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.180695521853676</v>
+        <v>-3.777258115074736</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7821301044864297</v>
+        <v>0.9435050671980059</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4531883839508936</v>
+        <v>0.5863186930381212</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.726677767912185</v>
+        <v>2.806555953364521</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.131508873169325</v>
+        <v>-3.728071466390384</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.800296382000099</v>
+        <v>0.9616713447116749</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4531883839508936</v>
+        <v>0.5863186930381212</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.725169385952113</v>
+        <v>2.80504757140445</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.833513460316254</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.087135741530756</v>
+        <v>-3.683698334751816</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8179085020909627</v>
+        <v>0.9792834648025386</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4975615155894622</v>
+        <v>0.6306918246766898</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.751656132370691</v>
+        <v>2.831534317823027</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.052404420212255</v>
+        <v>-3.648967013433315</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8261948247569533</v>
+        <v>0.9875697874685296</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4975615155894622</v>
+        <v>0.6306918246766898</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.746049926509281</v>
+        <v>2.825928111961618</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190327</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.004748689651199</v>
+        <v>-3.601311282872259</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8516388740091803</v>
+        <v>1.013013836720757</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5452172461505178</v>
+        <v>0.6783475552377455</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.781025121873719</v>
+        <v>2.860903307326056</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569619</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.904230531152445</v>
+        <v>-3.500793124373504</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8967385107834069</v>
+        <v>1.058113473494983</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6457354046492724</v>
+        <v>0.7788657137365</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.846228390347696</v>
+        <v>2.926106575800033</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.888325201720092</v>
+        <v>-3.484887794941152</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8898553150322202</v>
+        <v>1.051230277743797</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5666227439400335</v>
+        <v>0.6997530530272611</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.785515466398025</v>
+        <v>2.865393651850362</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.843486800111694</v>
+        <v>-3.440049393332754</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9118883782862079</v>
+        <v>1.073263340997784</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.571166176884903</v>
+        <v>0.7042964859721306</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.792339228775576</v>
+        <v>2.872217414227912</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.862985256353702</v>
+        <v>-3.459547849574762</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9082499354204827</v>
+        <v>1.069624898132059</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5230815356049987</v>
+        <v>0.6562118446922263</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.767649383638711</v>
+        <v>2.847527569091048</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405963</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.818782419267802</v>
+        <v>-3.415345012488861</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.93181067278268</v>
+        <v>1.093185635494256</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5672843726908992</v>
+        <v>0.7004146817781267</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.800050688418088</v>
+        <v>2.879928873870425</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265647</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.780493000780229</v>
+        <v>-3.422904678325908</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9455364406469569</v>
+        <v>1.088571769628685</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6240678056499535</v>
+        <v>0.755218085787946</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.832530748662769</v>
+        <v>2.911220916745564</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284882</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.622201583240956</v>
+        <v>-3.264613260786636</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.060100772845705</v>
+        <v>1.203136101827434</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6240678056499535</v>
+        <v>0.755218085787946</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.883778513845809</v>
+        <v>2.962468681928604</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321025</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.41455957960648</v>
+        <v>-3.05697125715216</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.141598278893749</v>
+        <v>1.284633607875477</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8317098092844296</v>
+        <v>0.9628600894224222</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.006804420620747</v>
+        <v>3.085494588703543</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475142</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.363527486883952</v>
+        <v>-3.005939164429632</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.15695934422103</v>
+        <v>1.299994673202759</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8827419020069576</v>
+        <v>1.01389218214495</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.032371904492534</v>
+        <v>3.111062072575329</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404856</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.298303305756747</v>
+        <v>-2.940714983302426</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.200236420764617</v>
+        <v>1.343271749746346</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9479660831341632</v>
+        <v>1.079116363272156</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.088693817261562</v>
+        <v>3.167383985344358</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.260876285685613</v>
+        <v>-2.903287963231292</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.211168201092351</v>
+        <v>1.35420353007408</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9532176211633449</v>
+        <v>1.084367901301337</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.087805712378352</v>
+        <v>3.166495880461147</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992663</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.259518300712068</v>
+        <v>-2.901929978257747</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.21296818741301</v>
+        <v>1.356003516394738</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.027555746701164</v>
+        <v>1.158706026839156</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.133665380032283</v>
+        <v>3.212355548115079</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.231105037612184</v>
+        <v>-2.873516715157863</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.384891263674174</v>
+        <v>1.527926592655902</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9685801839547348</v>
+        <v>1.099730464092727</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.258837813405637</v>
+        <v>3.337527981488432</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957629</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.156322776587171</v>
+        <v>-2.79873445413285</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.534917077301996</v>
+        <v>1.677952406283725</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.043362444979747</v>
+        <v>1.17451272511774</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.423820079238461</v>
+        <v>3.502510247321257</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.130238692323363</v>
+        <v>-2.772650369869043</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.537058687021378</v>
+        <v>1.680094016003107</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.043362444979747</v>
+        <v>1.17451272511774</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.41552805525232</v>
+        <v>3.494218223335116</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.042360779214243</v>
+        <v>-2.684772456759922</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.570403047848806</v>
+        <v>1.713438376830535</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.159288087403099</v>
+        <v>1.290438367541091</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.48327663629011</v>
+        <v>3.561966804372906</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.79626414395986</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.03346831782096</v>
+        <v>-2.675879995366639</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.591514438132911</v>
+        <v>1.734549767114639</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.159288087403099</v>
+        <v>1.290438367541091</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.500831042016902</v>
+        <v>3.579521210099697</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945369</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.201944434790838</v>
+        <v>-2.844356112336517</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.515979038749544</v>
+        <v>1.659014367731272</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.131340251686518</v>
+        <v>1.26249053182451</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.475917387991537</v>
+        <v>3.554607556074333</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782711</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.755688242161398</v>
+        <v>-2.398099919707077</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.675751212989181</v>
+        <v>1.81878654197091</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.036621582016885</v>
+        <v>1.167771862154877</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.40035588337762</v>
+        <v>3.479046051460415</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632639</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.732967138478245</v>
+        <v>-2.375378816023924</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.675503676959347</v>
+        <v>1.818539005941075</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.036621582016885</v>
+        <v>1.167771862154877</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.391019905874524</v>
+        <v>3.469710073957319</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777676</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.862168951772288</v>
+        <v>-2.504580629317967</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.782729077492899</v>
+        <v>1.925764406474627</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9074197687228429</v>
+        <v>1.038570048860835</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.472404943749268</v>
+        <v>3.551095111832063</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.888043350246313</v>
+        <v>-2.530455027791993</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.809457140596935</v>
+        <v>1.952492469578663</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9523313774345841</v>
+        <v>1.083481657572576</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.536429731469959</v>
+        <v>3.615119899552754</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.88098866003114</v>
+        <v>-2.523400337576819</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.80895437267255</v>
+        <v>1.951989701654278</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9593860676497579</v>
+        <v>1.09053634778775</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.537337901588609</v>
+        <v>3.616028069671404</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.854037435704652</v>
+        <v>-2.496449113250331</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.829741016047887</v>
+        <v>1.972776345029615</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.974266413677477</v>
+        <v>1.105416693815469</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.556272262849982</v>
+        <v>3.634962430932777</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784111</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.875581663535439</v>
+        <v>-2.517993341081118</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.005226457060531</v>
+        <v>2.148261786042259</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.974266413677477</v>
+        <v>1.105416693815469</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.740375394994941</v>
+        <v>3.819065563077737</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.897989781340311</v>
+        <v>-2.54040145888599</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.988379904841576</v>
+        <v>2.131415233823304</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.974266413677477</v>
+        <v>1.105416693815469</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.732492089897935</v>
+        <v>3.81118225798073</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.926214016917911</v>
+        <v>-2.568625694463591</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.979144210160173</v>
+        <v>2.122179539141901</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9922431661287856</v>
+        <v>1.123393446266778</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.745332140918357</v>
+        <v>3.824022309001152</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.935654942806441</v>
+        <v>-2.578066620352121</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.031621557526608</v>
+        <v>2.174656886508337</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.114670283672177</v>
+        <v>1.245820563810169</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.875042129166239</v>
+        <v>3.953732297249035</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321638</v>
+        <v>3.714941193321639</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.141893880594875</v>
+        <v>-2.784305558140554</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.952017076956536</v>
+        <v>2.095052405938264</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9084313458837434</v>
+        <v>1.039581626021736</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.75418986103848</v>
+        <v>3.832880029121275</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.218223858195781</v>
+        <v>-2.86063553574146</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.919596898809949</v>
+        <v>2.062632227791677</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9084313458837434</v>
+        <v>1.039581626021736</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.752301673932255</v>
+        <v>3.830991842015051</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.37318064359591</v>
+        <v>-3.015592321141589</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.852434414252759</v>
+        <v>1.995469743234487</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7534745604836142</v>
+        <v>0.8846248406216064</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.65414783229504</v>
+        <v>3.732838000377835</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343072</v>
+        <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.534749069123165</v>
+        <v>-3.177160746668844</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.786241054252009</v>
+        <v>1.929276383233738</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6266916366857348</v>
+        <v>0.757841916823727</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.576512088226464</v>
+        <v>3.65520225630926</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389355</v>
+        <v>3.754596135389356</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.643049730993285</v>
+        <v>-3.285461408538964</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.75599419636988</v>
+        <v>1.899029525351609</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6266916366857348</v>
+        <v>0.757841916823727</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.589585495092383</v>
+        <v>3.668275663175178</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.802600803756802</v>
+        <v>-3.445012481302481</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.684178964047413</v>
+        <v>1.827214293029142</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4744139698239833</v>
+        <v>0.6055642499619756</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.490224091758272</v>
+        <v>3.568914259841068</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.830501590866275</v>
+        <v>-3.472913268411954</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.671542690330626</v>
+        <v>1.814578019312354</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4398170456810485</v>
+        <v>0.5709673258190407</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.467989978399513</v>
+        <v>3.546680146482309</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.953027693569168</v>
+        <v>-3.595439371114848</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.619296693226667</v>
+        <v>1.762332022208396</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3172909429781546</v>
+        <v>0.4484412231161469</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.391238760754976</v>
+        <v>3.469928928837771</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.183542189754757</v>
+        <v>-3.825953867300436</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.593796854342936</v>
+        <v>1.736832183324664</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.08677644679256591</v>
+        <v>0.2179267269305581</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.319636022634126</v>
+        <v>3.398326190716922</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.5322872749792</v>
+        <v>-4.17469895252488</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.594610539255005</v>
+        <v>1.737645868236734</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.02197150712633189</v>
+        <v>0.1091787730116603</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.394698969284635</v>
+        <v>3.47338913736743</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.686273692755341</v>
+        <v>-4.32868537030102</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.601996241290189</v>
+        <v>1.745031570271917</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.02197150712633189</v>
+        <v>0.1091787730116603</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.463679238430275</v>
+        <v>3.54236940651307</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.89087312761835</v>
+        <v>-4.533284805164029</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.506207669465106</v>
+        <v>1.649242998446835</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.02197150712633189</v>
+        <v>0.1091787730116603</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.449730440550395</v>
+        <v>3.528420608633191</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.143348281626074</v>
+        <v>-4.785759959171753</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.417088096917431</v>
+        <v>1.560123425899159</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.02197150712633189</v>
+        <v>0.1091787730116603</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.461600929605809</v>
+        <v>3.540291097688605</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.67402853597316</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.436244038105486</v>
+        <v>-4.922939355730181</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.30114032884461</v>
+        <v>1.506462201794732</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.02197150712633189</v>
+        <v>0.1091787730116603</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.462811464124753</v>
+        <v>3.541501632207548</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251947</v>
+        <v>3.663509457251949</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.622908166240294</v>
+        <v>-5.109603483864989</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.230596419818008</v>
+        <v>1.43591829276813</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.04871047795089178</v>
+        <v>0.08243980218710045</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.450889823857338</v>
+        <v>3.529579991940134</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.768928853154256</v>
+        <v>-5.255624170778951</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.167265997788612</v>
+        <v>1.372587870738734</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.05779356974474875</v>
+        <v>0.07335671039324348</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.440517821517214</v>
+        <v>3.519207989600009</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.860642862263841</v>
+        <v>-5.347338179888537</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.292784450843822</v>
+        <v>1.498106323793944</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.05779356974474875</v>
+        <v>0.07335671039324348</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.602721878216258</v>
+        <v>3.681412046299053</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.89229452132381</v>
+        <v>-5.378989838948506</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.274970425183649</v>
+        <v>1.480292298133771</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.06296202698918896</v>
+        <v>0.06818825314880328</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.594467441833408</v>
+        <v>3.673157609916203</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586815</v>
+        <v>3.750044015868152</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.961360575896747</v>
+        <v>-5.448055893521443</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.257573420922965</v>
+        <v>1.462895293873087</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.125332904482799</v>
+        <v>0.005817375655193247</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.567274332905733</v>
+        <v>3.645964500988528</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332697</v>
+        <v>3.783632867332699</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.063336698145155</v>
+        <v>-5.55003201576985</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.225708610479505</v>
+        <v>1.431030483429626</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2273090267312066</v>
+        <v>-0.09615874659321433</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.515014298012591</v>
+        <v>3.593704466095386</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231813</v>
+        <v>3.798296784231816</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.953330414667933</v>
+        <v>-5.440025732292629</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.261864011114569</v>
+        <v>1.467185884064691</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2041044548139314</v>
+        <v>-0.07295417467593912</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.521089928407132</v>
+        <v>3.599780096489927</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.965860119779812</v>
+        <v>-5.452555437404508</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.261102139791792</v>
+        <v>1.466424012741913</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2179309542804544</v>
+        <v>-0.08678067414246216</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.517044039449192</v>
+        <v>3.595734207531987</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.664413394307974</v>
+        <v>-5.15110871193267</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.388941712863062</v>
+        <v>1.594263585813184</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.08351577119138287</v>
+        <v>0.2146660513293751</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.70517295761483</v>
+        <v>3.783863125697625</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679627</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.689003638543158</v>
+        <v>-5.175698956167854</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.3800767929217</v>
+        <v>1.585398665871821</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.08351577119138287</v>
+        <v>0.2146660513293751</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.706144135367541</v>
+        <v>3.784834303450336</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474162</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.637965262536638</v>
+        <v>-5.124660580161334</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.401335047704063</v>
+        <v>1.606656920654185</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.08351577119138287</v>
+        <v>0.2146660513293751</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.706987039747296</v>
+        <v>3.785677207830092</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969547</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.609116585713178</v>
+        <v>-5.095811903337873</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.431912617307593</v>
+        <v>1.637234490257715</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1123644480148431</v>
+        <v>0.2435147281528354</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.743334344715518</v>
+        <v>3.822024512798313</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700481</v>
+        <v>3.825752932700482</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.512481673694538</v>
+        <v>-4.999176991319233</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.286750578238983</v>
+        <v>1.492072451189105</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2089993600334831</v>
+        <v>0.3401496401714753</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.617499288050637</v>
+        <v>3.696189456133432</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077646</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.44344366274607</v>
+        <v>-4.930138980370765</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.317867826692335</v>
+        <v>1.523189699642456</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2780373709819511</v>
+        <v>0.4091876511199434</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.662424138693682</v>
+        <v>3.741114306776477</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833463</v>
+        <v>3.775028860833466</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.424656562377131</v>
+        <v>-4.911351880001827</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.309809485915993</v>
+        <v>1.515131358866114</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2968244713508896</v>
+        <v>0.4279747514888819</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.658123217991127</v>
+        <v>3.736813386073922</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.82103066007763</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.347557960835259</v>
+        <v>-4.834253278459954</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.339836636969171</v>
+        <v>1.545158509919293</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2968244713508896</v>
+        <v>0.4279747514888819</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.657310928427557</v>
+        <v>3.736001096510352</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147912</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.357943155725148</v>
+        <v>-4.844638473349844</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.345551338138288</v>
+        <v>1.55087321108841</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2864392764610003</v>
+        <v>0.4175895565989926</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.660948590618696</v>
+        <v>3.739638758701491</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735288</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.376531314447373</v>
+        <v>-4.863226632072069</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.408953080425823</v>
+        <v>1.614274953375945</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.267851117738775</v>
+        <v>0.3990013978767672</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.720632701161786</v>
+        <v>3.799322869244581</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496557</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.376829861143409</v>
+        <v>-4.863525178768104</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.405702672565707</v>
+        <v>1.611024545515829</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2675525710427391</v>
+        <v>0.3987028511807313</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.717322583962463</v>
+        <v>3.796012752045258</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108863</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.276006727452981</v>
+        <v>-4.762702045077677</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.45056282098127</v>
+        <v>1.655884693931392</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2800167865270929</v>
+        <v>0.4111670666650851</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.729332008192466</v>
+        <v>3.808022176275262</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812147</v>
+        <v>3.807356168121474</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.085225366700573</v>
+        <v>-4.571920684325269</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.527004618760776</v>
+        <v>1.732326491710898</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4707981472795003</v>
+        <v>0.6019484274174924</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.843930078122454</v>
+        <v>3.922620246205249</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906083</v>
+        <v>3.775233033906088</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.978262008851152</v>
+        <v>-4.464957326475847</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.549626807638141</v>
+        <v>1.754948680588263</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5292627552393017</v>
+        <v>0.6604130353772939</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.858845688635931</v>
+        <v>3.937535856718727</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912988</v>
+        <v>3.785761685912992</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.922931420949389</v>
+        <v>-4.409626738574085</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.606725979410905</v>
+        <v>1.812047852361027</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5845933431410638</v>
+        <v>0.7157436232790561</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.927010977989047</v>
+        <v>4.005701146071843</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539897</v>
+        <v>3.743767956539902</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.910877294036426</v>
+        <v>-4.397572611661122</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.605234198077528</v>
+        <v>1.81055607102765</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5966474700540266</v>
+        <v>0.7277977501920189</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.927930022038263</v>
+        <v>4.006620190121058</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811017</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.988232784164396</v>
+        <v>-4.474928101789091</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.576172632210476</v>
+        <v>1.781494505160598</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5192919799260572</v>
+        <v>0.6504422600640495</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.883397358145617</v>
+        <v>3.962087526228412</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382923</v>
+        <v>3.612322444382928</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.920184221472866</v>
+        <v>-4.406879539097561</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.61624308316497</v>
+        <v>1.821564956115092</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5873405426175871</v>
+        <v>0.7184908227555793</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.937077521638417</v>
+        <v>4.015767689721212</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013431</v>
+        <v>3.645256780013435</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.151784614642366</v>
+        <v>-4.638479932267062</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.543805596070764</v>
+        <v>1.749127469020886</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5873405426175871</v>
+        <v>0.7184908227555793</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.957280191812012</v>
+        <v>4.035970359894806</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498972</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.201836160171586</v>
+        <v>-4.688531477796282</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.507391213925958</v>
+        <v>1.71271308687608</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5873405426175871</v>
+        <v>0.7184908227555793</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.940886427878893</v>
+        <v>4.019576595961689</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800101</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.376942992748031</v>
+        <v>-4.863638310372727</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.397600394488847</v>
+        <v>1.602922267438969</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5873405426175871</v>
+        <v>0.7184908227555793</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.90113834147236</v>
+        <v>3.979828509555155</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660854</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.180842839317508</v>
+        <v>-4.667538156942204</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.483063074857996</v>
+        <v>1.688384947808118</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.78344069604811</v>
+        <v>0.9145909761861022</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.025821052527614</v>
+        <v>4.104511220610409</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.027817447204224</v>
+        <v>-4.514512764828919</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.643444231276214</v>
+        <v>1.848766104226336</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9364660881613941</v>
+        <v>1.067616368299386</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.216807287368488</v>
+        <v>4.295497455451284</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791152</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.056124761077494</v>
+        <v>-4.54282007870219</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.819587530635199</v>
+        <v>2.024909403585321</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9364660881613941</v>
+        <v>1.067616368299386</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.404273512276781</v>
+        <v>4.482963680359576</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620438</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.222717986191016</v>
+        <v>-4.709413303815712</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.722353191943873</v>
+        <v>1.927675064893994</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7698728630478717</v>
+        <v>0.9010231431858637</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.273720528562751</v>
+        <v>4.352410696645546</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285651</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.19968219282945</v>
+        <v>-4.686377510454146</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.735243911950217</v>
+        <v>1.940565784900339</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7698728630478717</v>
+        <v>0.9010231431858637</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.277396931224469</v>
+        <v>4.356087099307263</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399473</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.170436212373754</v>
+        <v>-4.657131529998449</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.744560359255991</v>
+        <v>1.949882232206113</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7698728630478717</v>
+        <v>0.9010231431858637</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.275014986347964</v>
+        <v>4.353705154430759</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256376</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.277361760251605</v>
+        <v>-4.7640570778763</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.699083379262485</v>
+        <v>1.904405252212607</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6629473151700204</v>
+        <v>0.7940975953080124</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.208152896778888</v>
+        <v>4.286843064861683</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701003</v>
+        <v>3.689942600701007</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.422380318758854</v>
+        <v>-4.909075636383549</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.64250475800282</v>
+        <v>1.847826630952942</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5179287566627718</v>
+        <v>0.6490790368007638</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.122570563817773</v>
+        <v>4.201260731900568</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687018</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.540722084543571</v>
+        <v>-5.027417402168266</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.695099290946686</v>
+        <v>1.900421163896808</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5286147952256619</v>
+        <v>0.6597650753636539</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.22891342621326</v>
+        <v>4.307603594296055</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.71487905179081</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.592132506864279</v>
+        <v>-5.078827824488974</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.672320819144342</v>
+        <v>1.877642692094464</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5286147952256619</v>
+        <v>0.6597650753636539</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.226699123339199</v>
+        <v>4.305389291421994</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437335</v>
+        <v>3.704757949437338</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.671551958072031</v>
+        <v>-5.158247275696726</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.640456166735531</v>
+        <v>1.845778039685652</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5286147952256619</v>
+        <v>0.6597650753636539</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.226602251413488</v>
+        <v>4.305292419496284</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298403</v>
+        <v>3.736804952298407</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.767014955989248</v>
+        <v>-5.253710273613944</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.602264861126686</v>
+        <v>1.807586734076808</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5286147952256619</v>
+        <v>0.6597650753636539</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.226596144971531</v>
+        <v>4.305286313054326</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218004</v>
+        <v>3.715372960218009</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.702639045138533</v>
+        <v>-5.189334362763229</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.626111622029583</v>
+        <v>1.831433494979705</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.592990706076377</v>
+        <v>0.7241409862143691</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.263318088044571</v>
+        <v>4.342008256127366</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73608941335354</v>
+        <v>3.736089413353544</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.758008207270727</v>
+        <v>-5.244703524895423</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.609697774924432</v>
+        <v>1.815019647874554</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.592990706076377</v>
+        <v>0.7241409862143691</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.269051905792297</v>
+        <v>4.347742073875093</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113283</v>
+        <v>3.736822870113287</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.776226674268336</v>
+        <v>-5.262921991893031</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.601948751468321</v>
+        <v>1.807270624418443</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5678842688205349</v>
+        <v>0.6990345489585269</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.253526406781725</v>
+        <v>4.332216574864519</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113692</v>
+        <v>3.790272500113695</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.737543238924405</v>
+        <v>-5.224238556549101</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.637296518456212</v>
+        <v>1.842618391406334</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5678842688205349</v>
+        <v>0.6990345489585269</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.273400799632043</v>
+        <v>4.352090967714838</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016436</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.631508243719096</v>
+        <v>-5.118203561343791</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.663411217063063</v>
+        <v>1.868733090013186</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5678842688205349</v>
+        <v>0.6990345489585269</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.257101500156771</v>
+        <v>4.335791668239566</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.448296580586001</v>
+        <v>-4.934991898210696</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.739126831780347</v>
+        <v>1.944448704730469</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5678842688205349</v>
+        <v>0.6990345489585269</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.259532449620816</v>
+        <v>4.338222617703612</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.37657513357215</v>
+        <v>-4.863270451196845</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.750759816665265</v>
+        <v>1.956081689615386</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6396057158343855</v>
+        <v>0.7707559959723775</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.285509723908504</v>
+        <v>4.3641998919913</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394116</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.354202107964444</v>
+        <v>-4.840897425589139</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.706624772829519</v>
+        <v>1.911946645779641</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6508614669472871</v>
+        <v>0.7820117470852791</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.239178920497417</v>
+        <v>4.317869088580212</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456733</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.387218403875188</v>
+        <v>-4.873913721499884</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.878616459350576</v>
+        <v>2.083938332300698</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5814240902805354</v>
+        <v>0.7125743704185274</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.382714699382722</v>
+        <v>4.461404867465516</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71376253688368</v>
+        <v>3.713762536883684</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.37569076822558</v>
+        <v>-4.862386085850275</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.875148739438669</v>
+        <v>2.08047061238879</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6404247484818979</v>
+        <v>0.7715750286198899</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.410036320131788</v>
+        <v>4.488726488214583</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.7171506992363</v>
+        <v>3.717150699236305</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.473032269567948</v>
+        <v>-4.959727587192644</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.83988025142351</v>
+        <v>2.045202124373632</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5960045663164095</v>
+        <v>0.7271548464544015</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.387052323354284</v>
+        <v>4.465742491437078</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427686</v>
+        <v>3.705201079427692</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.558888298907915</v>
+        <v>-5.04558361653261</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.806788921880361</v>
+        <v>2.012110794830483</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5536284970902745</v>
+        <v>0.6847787772282665</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.36287776401144</v>
+        <v>4.441567932094236</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610376</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.567725096324034</v>
+        <v>-5.05442041394873</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.785673404734415</v>
+        <v>1.990995277684537</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5461863244489238</v>
+        <v>0.6773366045869158</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.340831662247131</v>
+        <v>4.419521830329927</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667457</v>
+        <v>3.715544411667461</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.546292348645173</v>
+        <v>-5.145802976514188</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.80441101485101</v>
+        <v>1.964606763703403</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5297525438449536</v>
+        <v>0.6407717198675711</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.341135904929799</v>
+        <v>4.40774741054337</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889193</v>
+        <v>3.673978374889198</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.534585630658166</v>
+        <v>-5.134096258527182</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.91122195987008</v>
+        <v>2.071417708722474</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.54145926183196</v>
+        <v>0.6524784378545775</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.450288193546271</v>
+        <v>4.516899699159842</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940957</v>
+        <v>3.682476099409575</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.605497704400443</v>
+        <v>-5.205008332269459</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.885889469104574</v>
+        <v>2.046085217956968</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.54145926183196</v>
+        <v>0.6524784378545775</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.453320532277676</v>
+        <v>4.519932037891246</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452574</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.615813802566795</v>
+        <v>-5.215324430435811</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.094667863116092</v>
+        <v>2.254863611968486</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.54145926183196</v>
+        <v>0.6524784378545775</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.666225365555734</v>
+        <v>4.732836871169305</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762289</v>
+        <v>3.623960959762295</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.615719834549423</v>
+        <v>-5.215230462418439</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.093884117235131</v>
+        <v>2.254079866087524</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.541829123179278</v>
+        <v>0.6528482992018955</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.665625949276214</v>
+        <v>4.732237454889785</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884081</v>
+        <v>3.800870306884088</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.759320998572808</v>
+        <v>-5.358831626441824</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.03067563757013</v>
+        <v>2.190871386422524</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.541829123179278</v>
+        <v>0.6528482992018955</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.659857935220568</v>
+        <v>4.726469440834139</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129644</v>
+        <v>3.671015692129652</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.75837257545477</v>
+        <v>-5.357883203323786</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.031055006817346</v>
+        <v>2.191250755669739</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.541829123179278</v>
+        <v>0.6528482992018955</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.659857935220568</v>
+        <v>4.726469440834139</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052348</v>
+        <v>3.904173816052355</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.85864239341379</v>
+        <v>-5.458153021282806</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.003674687614829</v>
+        <v>2.163870436467223</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.541829123179278</v>
+        <v>0.6528482992018955</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.67258554320166</v>
+        <v>4.739197048815231</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813491</v>
+        <v>3.740179607813499</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.852650146624979</v>
+        <v>-5.452160774493994</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.008017584754742</v>
+        <v>2.168213333607135</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.541829123179278</v>
+        <v>0.6528482992018955</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.674531541626048</v>
+        <v>4.741143047239619</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.76505079653794</v>
+        <v>3.765050796537947</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.764092185494211</v>
+        <v>-5.363602813363227</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.037094905224818</v>
+        <v>2.197290654077211</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.541829123179278</v>
+        <v>0.6528482992018955</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.668185677643817</v>
+        <v>4.734797183257387</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771812</v>
+        <v>3.758409170771819</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.746333107991137</v>
+        <v>-5.345843735860153</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.043507213665043</v>
+        <v>2.203702962517437</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.541829123179278</v>
+        <v>0.6528482992018955</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.667494355082813</v>
+        <v>4.734105860696383</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.80134059710972</v>
+        <v>3.801340597109725</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.495608021949182</v>
+        <v>-5.246213584811085</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.156579433990412</v>
+        <v>2.25633720884565</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.7925542092212328</v>
+        <v>0.7524784502509629</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.830711592616573</v>
+        <v>4.80666613723441</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843994</v>
+        <v>3.798465546844</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.545007530638193</v>
+        <v>-5.295613093500096</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.325973896013533</v>
+        <v>2.425731670868772</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.8028130426529775</v>
+        <v>0.7627372836827077</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.026021158174346</v>
+        <v>5.001975702792183</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351859</v>
+        <v>3.772186508351863</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.338323056995817</v>
+        <v>-5.08892861985772</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.395836358573346</v>
+        <v>2.495594133428585</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.009497516295353</v>
+        <v>0.9694217573250833</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.137220515462633</v>
+        <v>5.113175060080471</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551272</v>
+        <v>3.763392838551273</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.372479951993343</v>
+        <v>-5.123085514855246</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.38417511422844</v>
+        <v>2.483932889083679</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.9259137467545407</v>
+        <v>0.8858379877842708</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.089071767392251</v>
+        <v>5.065026312010088</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.80559056504111</v>
+        <v>3.805590565041115</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.279890472931887</v>
+        <v>-5.03049603579379</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.774708019842691</v>
+        <v>2.87446579469793</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.9259137467545407</v>
+        <v>0.8858379877842708</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.442568881381918</v>
+        <v>5.418523425999756</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497402</v>
+        <v>3.832164354497406</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.353051076705031</v>
+        <v>-5.103656639566934</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.750006889900536</v>
+        <v>2.849764664755775</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8978925467202976</v>
+        <v>0.8578167877500278</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.430319272928475</v>
+        <v>5.406273817546313</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492294</v>
+        <v>3.858310890492299</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.300834766908689</v>
+        <v>-5.051440329770593</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.8207233551426</v>
+        <v>2.920481129997839</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8978925467202976</v>
+        <v>0.8578167877500278</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.480149214252003</v>
+        <v>5.45610375886984</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436475</v>
+        <v>3.84493559643648</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.268937249823444</v>
+        <v>-5.019542812685347</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.842296332186709</v>
+        <v>2.942054107041948</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.9297900638055434</v>
+        <v>0.8897143048352736</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.508101694713162</v>
+        <v>5.484056239330999</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039484</v>
+        <v>3.84837686603949</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.283692574023584</v>
+        <v>-5.034298136885488</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.83203178654585</v>
+        <v>2.931789561401089</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.9297900638055434</v>
+        <v>0.8897143048352736</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.503739278752358</v>
+        <v>5.479693823370196</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524478</v>
+        <v>3.868153115524485</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.234227950653673</v>
+        <v>-4.984833513515576</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.842742139310094</v>
+        <v>2.942499914165333</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.9792546871754551</v>
+        <v>0.9391789282051852</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.524342556190585</v>
+        <v>5.500297100808423</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867952</v>
+        <v>3.849040239867959</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.071119958500057</v>
+        <v>-4.821725521361961</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.904393003886475</v>
+        <v>3.004150778741714</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.14236267932907</v>
+        <v>1.102286920358801</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.618615019197689</v>
+        <v>5.594569563815527</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232966</v>
+        <v>3.870204928232975</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.05047686769883</v>
+        <v>-4.801082430560733</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.921697276898094</v>
+        <v>3.021455051753333</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.14236267932907</v>
+        <v>1.102286920358801</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.627662055888817</v>
+        <v>5.603616600506655</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.85553443717967</v>
+        <v>3.855534437179679</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.113184784173388</v>
+        <v>-4.863790347035291</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.897471575294392</v>
+        <v>2.997229350149631</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.079654762854513</v>
+        <v>1.039579003884243</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.590894770990204</v>
+        <v>5.566849315608042</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967718</v>
+        <v>3.884687848967726</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.065176660329695</v>
+        <v>-4.815782223191598</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.879584241622222</v>
+        <v>2.979342016477461</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.079654762854513</v>
+        <v>1.039579003884243</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.553804187780556</v>
+        <v>5.529758732398394</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.89536235701861</v>
+        <v>3.895362357018617</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.889768314928409</v>
+        <v>-4.736956566008008</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.953679833340687</v>
+        <v>3.014804532908848</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.255063108255799</v>
+        <v>1.118404661067833</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.662981448579278</v>
+        <v>5.580986380266499</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075132</v>
+        <v>3.89161098107514</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.697833513674535</v>
+        <v>-4.545021764754134</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.025352846449273</v>
+        <v>3.086477546017434</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.255063108255799</v>
+        <v>1.118404661067833</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.657880541186315</v>
+        <v>5.575885472873535</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435442</v>
+        <v>3.87243249343545</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.579660135656608</v>
+        <v>-4.426848386736207</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.067976107045539</v>
+        <v>3.1291008066137</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.373236486273727</v>
+        <v>1.236578039085761</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.724138477386167</v>
+        <v>5.642143409073388</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917728</v>
+        <v>3.859571723917738</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.466245452873877</v>
+        <v>-4.313433703953476</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.142430573021659</v>
+        <v>3.203555272589819</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.486651169056458</v>
+        <v>1.349992721868492</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.821275879918833</v>
+        <v>5.739280811606053</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013635</v>
+        <v>3.828006274013644</v>
       </c>
       <c r="C2104" t="n">
         <v>4.922845401496135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.439196415180623</v>
+        <v>-4.286384666260222</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.146810411110137</v>
+        <v>3.207935110678298</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.513700206749712</v>
+        <v>1.377041759561746</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.831065525545962</v>
+        <v>5.749070457233183</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263771</v>
+        <v>3.823987445263776</v>
       </c>
       <c r="C2105" t="n">
         <v>4.922845401496135</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.445229695367393</v>
+        <v>-4.292417946446992</v>
       </c>
       <c r="E2105" t="n">
-        <v>3.144397099035429</v>
+        <v>3.20552179860359</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.513700206749712</v>
+        <v>1.377041759561746</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.831065525545962</v>
+        <v>5.749070457233183</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.86075709904484</v>
+        <v>3.928146139784144</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.926483568638547</v>
+        <v>5.149635851011775</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.531699836281179</v>
+        <v>-4.420517011782134</v>
       </c>
       <c r="E2106" t="n">
-        <v>3.113447209812327</v>
+        <v>3.381072621985173</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.490480208720284</v>
+        <v>1.248942694226604</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.820771693870718</v>
+        <v>5.899001467547738</v>
       </c>
     </row>
   </sheetData>
